--- a/school_2/1) walls/walls_sh2.xlsx
+++ b/school_2/1) walls/walls_sh2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16056" windowHeight="8520"/>
   </bookViews>
   <sheets>
     <sheet name="10.3отк" sheetId="30" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3371" uniqueCount="1225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="1225">
   <si>
     <t>Указать название организации (на бланке организации)</t>
   </si>
@@ -11945,12 +11945,6 @@
     <t>1-3 эт. Дверные откосы. Уменьшение дверных проемов. /файерборд</t>
   </si>
   <si>
-    <t>1-2 эт. Дверные откосы. Уменьшение дверных проемов. / файерборд, на мет. каркас.</t>
-  </si>
-  <si>
-    <t>Устройство проемов из файерборд /  в 2 слоя</t>
-  </si>
-  <si>
     <t>Устройство проемов из файерборд / в 2 слоя</t>
   </si>
   <si>
@@ -11978,57 +11972,21 @@
     <t>п.м</t>
   </si>
   <si>
-    <t xml:space="preserve">Штукатурка стен сухими смесями с установкой маяков с предварительной огрунтовкой </t>
-  </si>
-  <si>
     <t>СТ-2.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Подготовка поверхности СКБ </t>
-  </si>
-  <si>
-    <t>Подготовка поверхности СКБ</t>
-  </si>
-  <si>
     <t>1 эт</t>
   </si>
   <si>
-    <t>двери</t>
-  </si>
-  <si>
     <t>2 эт</t>
   </si>
   <si>
     <t>3 эт</t>
   </si>
   <si>
-    <t>витражи</t>
-  </si>
-  <si>
-    <t>окна</t>
-  </si>
-  <si>
-    <t>окна высокие</t>
-  </si>
-  <si>
-    <t>Кол-во откосов, шт</t>
-  </si>
-  <si>
-    <t>Верхняя плоскость, м2</t>
-  </si>
-  <si>
-    <t>Боковые плоскости, м2</t>
-  </si>
-  <si>
     <t>эт.</t>
   </si>
   <si>
-    <t>Сумма</t>
-  </si>
-  <si>
-    <t>1-3 эт. Откосы</t>
-  </si>
-  <si>
     <t>Устройство проемов из файерборд / в 1 слои</t>
   </si>
   <si>
@@ -12057,6 +12015,52 @@
   </si>
   <si>
     <t>Выравнивание поверхностей откосов толщ. до 5 мм с предварительной огрунтовкой поверхности (финишная шпаклевка)</t>
+  </si>
+  <si>
+    <t>Устройство откосов из ГКЛ на клеевом составе / в 2 слой</t>
+  </si>
+  <si>
+    <t>1-3 эт.</t>
+  </si>
+  <si>
+    <t>Устройство дверных откосов.</t>
+  </si>
+  <si>
+    <t>верхняя пл-ть,
+общая, м2</t>
+  </si>
+  <si>
+    <t>боковая пл-тьь,
+общая, м2</t>
+  </si>
+  <si>
+    <t>Итог, м2</t>
+  </si>
+  <si>
+    <t>Устройство витражных откосов.</t>
+  </si>
+  <si>
+    <t>Устройство оконных откосов. (средняя высота = 2.5 м)</t>
+  </si>
+  <si>
+    <t>Устройство оконных откосов. (средняя высота = 6.8 м)</t>
+  </si>
+  <si>
+    <t>1-3 эт. Откосы, витражи
+файерборд</t>
+  </si>
+  <si>
+    <t>1-3 эт. Откосы, окна + мин вата 50 мм. Файерборд</t>
+  </si>
+  <si>
+    <t>1-3 эт. Откосы, двери
+файерборд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Выравнивание поверхностей откосов толщ. до 5 мм с предварительной огрунтовкой поверхности </t>
+  </si>
+  <si>
+    <t>Выравнивание поверхностей откосов толщ. до 5 мм с предварительной огрунтовкой поверхности (</t>
   </si>
 </sst>
 </file>
@@ -12377,12 +12381,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -12629,17 +12633,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -12650,7 +12643,7 @@
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="285">
+  <cellXfs count="308">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -13160,29 +13153,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -13190,17 +13162,107 @@
     <xf numFmtId="0" fontId="30" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="30" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="30" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13208,11 +13270,32 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13236,24 +13319,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -13288,6 +13353,12 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -13346,14 +13417,20 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -13372,21 +13449,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -13424,9 +13486,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -13446,6 +13505,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14794,42 +14856,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="112"/>
     <col min="2" max="2" width="11.21875" style="112" customWidth="1"/>
-    <col min="3" max="3" width="12.109375" style="112" customWidth="1"/>
-    <col min="4" max="4" width="11.5546875" style="112" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="112" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="112"/>
+    <col min="3" max="3" width="17.109375" style="112" customWidth="1"/>
+    <col min="4" max="4" width="23.21875" style="112" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="112" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="112" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="112"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="193" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
+      <c r="A1" s="222" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="222"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="188" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="203" t="s">
+      <c r="C2" s="224"/>
+      <c r="D2" s="224"/>
+      <c r="E2" s="226" t="s">
         <v>814</v>
       </c>
-      <c r="F2" s="204"/>
+      <c r="F2" s="227"/>
       <c r="G2" s="37" t="s">
         <v>10</v>
       </c>
@@ -14837,401 +14900,615 @@
         <v>830</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="189">
+    <row r="3" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="195">
         <v>1</v>
       </c>
-      <c r="B3" s="200" t="s">
+      <c r="B3" s="225" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C3" s="225"/>
+      <c r="D3" s="225"/>
+      <c r="E3" s="228" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F3" s="229"/>
+      <c r="G3" s="196" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="199">
+        <f>E15</f>
+        <v>138.97999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="190">
+        <f>A3+1</f>
+        <v>2</v>
+      </c>
+      <c r="B4" s="230" t="s">
+        <v>734</v>
+      </c>
+      <c r="C4" s="230"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="217" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F4" s="218"/>
+      <c r="G4" s="193" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="194">
+        <f>E22+E27</f>
+        <v>643.45000000000005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="191">
+        <f t="shared" ref="A5:A8" si="0">A4+1</f>
+        <v>3</v>
+      </c>
+      <c r="B5" s="219" t="s">
+        <v>734</v>
+      </c>
+      <c r="C5" s="219"/>
+      <c r="D5" s="219"/>
+      <c r="E5" s="220" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F5" s="221"/>
+      <c r="G5" s="128" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="129">
+        <f>E34</f>
+        <v>144.40800000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="192">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="205" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C6" s="205"/>
+      <c r="D6" s="205"/>
+      <c r="E6" s="206" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F6" s="207"/>
+      <c r="G6" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="142">
+        <f>SUM(H3:H5)</f>
+        <v>926.83800000000008</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="192">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B7" s="205" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C7" s="205"/>
+      <c r="D7" s="205"/>
+      <c r="E7" s="206" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F7" s="207"/>
+      <c r="G7" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="142">
+        <f>H6</f>
+        <v>926.83800000000008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="192">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B8" s="205" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C8" s="205"/>
+      <c r="D8" s="205"/>
+      <c r="E8" s="206" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F8" s="207"/>
+      <c r="G8" s="115" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="142">
+        <f>H6</f>
+        <v>926.83800000000008</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="208"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="216" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B10" s="216"/>
+      <c r="C10" s="216"/>
+      <c r="D10" s="216"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
+    </row>
+    <row r="11" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="195" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B11" s="195" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="196" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D11" s="196" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E11" s="195" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F11" s="208"/>
+      <c r="G11" s="208"/>
+      <c r="H11" s="208"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="195" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B12" s="195">
+        <v>33</v>
+      </c>
+      <c r="C12" s="197">
+        <v>35.79</v>
+      </c>
+      <c r="D12" s="197">
+        <f>B12*2*3.8*0.13</f>
+        <v>32.603999999999999</v>
+      </c>
+      <c r="E12" s="197">
+        <f>SUM(C12:D12)</f>
+        <v>68.394000000000005</v>
+      </c>
+      <c r="F12" s="208"/>
+      <c r="G12" s="208"/>
+      <c r="H12" s="208"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="195" t="s">
         <v>1198</v>
       </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200"/>
-      <c r="E3" s="205" t="s">
+      <c r="B13" s="195">
+        <v>17</v>
+      </c>
+      <c r="C13" s="197">
+        <v>13.03</v>
+      </c>
+      <c r="D13" s="197">
+        <f t="shared" ref="D13:D14" si="1">B13*2*3.8*0.13</f>
+        <v>16.795999999999999</v>
+      </c>
+      <c r="E13" s="197">
+        <f t="shared" ref="E13:E14" si="2">SUM(C13:D13)</f>
+        <v>29.826000000000001</v>
+      </c>
+      <c r="F13" s="208"/>
+      <c r="G13" s="208"/>
+      <c r="H13" s="208"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="195" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B14" s="195">
+        <v>25</v>
+      </c>
+      <c r="C14" s="197">
+        <v>16.059999999999999</v>
+      </c>
+      <c r="D14" s="197">
+        <f t="shared" si="1"/>
+        <v>24.7</v>
+      </c>
+      <c r="E14" s="197">
+        <f t="shared" si="2"/>
+        <v>40.76</v>
+      </c>
+      <c r="F14" s="208"/>
+      <c r="G14" s="208"/>
+      <c r="H14" s="208"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="210" t="s">
+        <v>843</v>
+      </c>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="197">
+        <f>SUM(E12:E14)</f>
+        <v>138.97999999999999</v>
+      </c>
+      <c r="F15" s="208"/>
+      <c r="G15" s="208"/>
+      <c r="H15" s="208"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="215"/>
+      <c r="B16" s="215"/>
+      <c r="C16" s="215"/>
+      <c r="D16" s="215"/>
+      <c r="E16" s="215"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="208"/>
+      <c r="H16" s="208"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="211" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B17" s="211"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="211"/>
+      <c r="E17" s="211"/>
+      <c r="F17" s="208"/>
+      <c r="G17" s="208"/>
+      <c r="H17" s="208"/>
+    </row>
+    <row r="18" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="190" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B18" s="190" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="193" t="s">
         <v>1214</v>
       </c>
-      <c r="F3" s="206"/>
-      <c r="G3" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="116">
-        <v>842.04</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="140">
-        <v>2</v>
-      </c>
-      <c r="B4" s="200" t="s">
+      <c r="D18" s="193" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E18" s="190" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F18" s="208"/>
+      <c r="G18" s="208"/>
+      <c r="H18" s="208"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="190" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B19" s="190">
+        <v>93</v>
+      </c>
+      <c r="C19" s="201">
+        <v>46.6</v>
+      </c>
+      <c r="D19" s="201">
+        <f>B19*2*2.5*0.25</f>
+        <v>116.25</v>
+      </c>
+      <c r="E19" s="201">
+        <f>SUM(C19:D19)</f>
+        <v>162.85</v>
+      </c>
+      <c r="F19" s="208"/>
+      <c r="G19" s="208"/>
+      <c r="H19" s="208"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="190" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B20" s="190">
+        <v>121</v>
+      </c>
+      <c r="C20" s="201">
+        <v>62.53</v>
+      </c>
+      <c r="D20" s="201">
+        <f t="shared" ref="D20:D21" si="3">B20*2*2.5*0.25</f>
+        <v>151.25</v>
+      </c>
+      <c r="E20" s="201">
+        <f t="shared" ref="E20:E21" si="4">SUM(C20:D20)</f>
+        <v>213.78</v>
+      </c>
+      <c r="F20" s="208"/>
+      <c r="G20" s="208"/>
+      <c r="H20" s="208"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="190" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B21" s="190">
+        <v>128</v>
+      </c>
+      <c r="C21" s="201">
+        <v>62.37</v>
+      </c>
+      <c r="D21" s="201">
+        <f t="shared" si="3"/>
+        <v>160</v>
+      </c>
+      <c r="E21" s="201">
+        <f t="shared" si="4"/>
+        <v>222.37</v>
+      </c>
+      <c r="F21" s="208"/>
+      <c r="G21" s="208"/>
+      <c r="H21" s="208"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="212" t="s">
+        <v>843</v>
+      </c>
+      <c r="B22" s="212"/>
+      <c r="C22" s="212"/>
+      <c r="D22" s="212"/>
+      <c r="E22" s="201">
+        <f>SUM(E19:E21)</f>
+        <v>599</v>
+      </c>
+      <c r="F22" s="208"/>
+      <c r="G22" s="208"/>
+      <c r="H22" s="208"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="215"/>
+      <c r="B23" s="215"/>
+      <c r="C23" s="215"/>
+      <c r="D23" s="215"/>
+      <c r="E23" s="215"/>
+      <c r="F23" s="208"/>
+      <c r="G23" s="208"/>
+      <c r="H23" s="208"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="213" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B24" s="213"/>
+      <c r="C24" s="213"/>
+      <c r="D24" s="213"/>
+      <c r="E24" s="213"/>
+      <c r="F24" s="208"/>
+      <c r="G24" s="208"/>
+      <c r="H24" s="208"/>
+    </row>
+    <row r="25" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="203" t="s">
         <v>1200</v>
       </c>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200"/>
-      <c r="E4" s="205" t="s">
-        <v>1116</v>
-      </c>
-      <c r="F4" s="206"/>
-      <c r="G4" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="142">
-        <f>H3</f>
-        <v>842.04</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="140">
-        <v>3</v>
-      </c>
-      <c r="B5" s="200" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C5" s="200"/>
-      <c r="D5" s="200"/>
-      <c r="E5" s="205" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F5" s="206"/>
-      <c r="G5" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="142">
-        <f>H4</f>
-        <v>842.04</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="195"/>
-      <c r="B6" s="195"/>
-      <c r="C6" s="195"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="195"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
-      <c r="H6" s="195"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="196" t="s">
-        <v>1209</v>
-      </c>
-      <c r="B7" s="196"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="194"/>
-      <c r="G7" s="195"/>
-      <c r="H7" s="195"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="190" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B8" s="190" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C8" s="190" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D8" s="190" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E8" s="190" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F8" s="194"/>
-      <c r="G8" s="195"/>
-      <c r="H8" s="195"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="190" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B9" s="190">
-        <v>70</v>
-      </c>
-      <c r="C9" s="190"/>
-      <c r="D9" s="190">
-        <v>91</v>
-      </c>
-      <c r="E9" s="190"/>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="195"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="190" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B10" s="190">
-        <v>52</v>
-      </c>
-      <c r="C10" s="190">
-        <v>16</v>
-      </c>
-      <c r="D10" s="190">
-        <v>122</v>
-      </c>
-      <c r="E10" s="190">
+      <c r="B25" s="203" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="202" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D25" s="202" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E25" s="203" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F25" s="208"/>
+      <c r="G25" s="208"/>
+      <c r="H25" s="208"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="203" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B26" s="203">
         <v>23</v>
       </c>
-      <c r="F10" s="194"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="195"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="190" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B11" s="190">
-        <v>37</v>
-      </c>
-      <c r="C11" s="190">
-        <v>7</v>
-      </c>
-      <c r="D11" s="190">
-        <v>122</v>
-      </c>
-      <c r="E11" s="190"/>
-      <c r="F11" s="194"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="197" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B12" s="197"/>
-      <c r="C12" s="197"/>
-      <c r="D12" s="197"/>
-      <c r="E12" s="197"/>
-      <c r="F12" s="194"/>
-      <c r="G12" s="195"/>
-      <c r="H12" s="195"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="191" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B13" s="191" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C13" s="191" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D13" s="191" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E13" s="191" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F13" s="194"/>
-      <c r="G13" s="195"/>
-      <c r="H13" s="195"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="191" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B14" s="191">
-        <v>17.649999999999999</v>
-      </c>
-      <c r="C14" s="191"/>
-      <c r="D14" s="191">
-        <v>46.5</v>
-      </c>
-      <c r="E14" s="191"/>
-      <c r="F14" s="194"/>
-      <c r="G14" s="195"/>
-      <c r="H14" s="195"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="191" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B15" s="191">
-        <v>12.2</v>
-      </c>
-      <c r="C15" s="191">
-        <v>12.3</v>
-      </c>
-      <c r="D15" s="191">
-        <v>62.3</v>
-      </c>
-      <c r="E15" s="191">
+      <c r="C26" s="204">
         <v>15.7</v>
       </c>
-      <c r="F15" s="194"/>
-      <c r="G15" s="195"/>
-      <c r="H15" s="195"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="191" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B16" s="191">
-        <v>6.9</v>
-      </c>
-      <c r="C16" s="191">
-        <v>4.3</v>
-      </c>
-      <c r="D16" s="191">
-        <v>57.7</v>
-      </c>
-      <c r="E16" s="191"/>
-      <c r="F16" s="194"/>
-      <c r="G16" s="195"/>
-      <c r="H16" s="195"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="198" t="s">
-        <v>1211</v>
-      </c>
-      <c r="B17" s="198"/>
-      <c r="C17" s="198"/>
-      <c r="D17" s="198"/>
-      <c r="E17" s="198"/>
-      <c r="F17" s="194"/>
-      <c r="G17" s="195"/>
-      <c r="H17" s="195"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="127" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B18" s="127" t="s">
-        <v>1203</v>
-      </c>
-      <c r="C18" s="127" t="s">
-        <v>1206</v>
-      </c>
-      <c r="D18" s="127" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E18" s="127" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F18" s="194"/>
-      <c r="G18" s="195"/>
-      <c r="H18" s="195"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="127" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B19" s="127">
-        <f>B9*2*2.1*0.13</f>
-        <v>38.22</v>
-      </c>
-      <c r="C19" s="127"/>
-      <c r="D19" s="127">
-        <f>D9*2*2.5*0.25</f>
-        <v>113.75</v>
-      </c>
-      <c r="E19" s="127"/>
-      <c r="F19" s="194"/>
-      <c r="G19" s="195"/>
-      <c r="H19" s="195"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="127" t="s">
-        <v>1204</v>
-      </c>
-      <c r="B20" s="127">
-        <f>B10*2*2.1*0.13</f>
-        <v>28.392000000000003</v>
-      </c>
-      <c r="C20" s="127">
-        <f>C10*2*3.8*0.13</f>
-        <v>15.808</v>
-      </c>
-      <c r="D20" s="127">
-        <f>D10*2*2.5*0.25</f>
-        <v>152.5</v>
-      </c>
-      <c r="E20" s="127">
-        <f>E10*2*6.8*0.25</f>
-        <v>78.2</v>
-      </c>
-      <c r="F20" s="194"/>
-      <c r="G20" s="195"/>
-      <c r="H20" s="195"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="127" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B21" s="127">
-        <f>B11*2*2.1*0.13</f>
-        <v>20.202000000000002</v>
-      </c>
-      <c r="C21" s="127">
-        <f>C11*2*3.8*0.13</f>
-        <v>6.9159999999999995</v>
-      </c>
-      <c r="D21" s="127">
-        <f>D11*2*2.5*0.25</f>
-        <v>152.5</v>
-      </c>
-      <c r="E21" s="127"/>
-      <c r="F21" s="194"/>
-      <c r="G21" s="195"/>
-      <c r="H21" s="195"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="189" t="s">
+      <c r="D26" s="204">
+        <f t="shared" ref="D26" si="5">B26*2*2.5*0.25</f>
+        <v>28.75</v>
+      </c>
+      <c r="E26" s="204">
+        <f t="shared" ref="E26" si="6">SUM(C26:D26)</f>
+        <v>44.45</v>
+      </c>
+      <c r="F26" s="208"/>
+      <c r="G26" s="208"/>
+      <c r="H26" s="208"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="214" t="s">
+        <v>843</v>
+      </c>
+      <c r="B27" s="214"/>
+      <c r="C27" s="214"/>
+      <c r="D27" s="214"/>
+      <c r="E27" s="204">
+        <f>SUM(E26:E26)</f>
+        <v>44.45</v>
+      </c>
+      <c r="F27" s="208"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="208"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="215"/>
+      <c r="B28" s="215"/>
+      <c r="C28" s="215"/>
+      <c r="D28" s="215"/>
+      <c r="E28" s="215"/>
+      <c r="F28" s="208"/>
+      <c r="G28" s="208"/>
+      <c r="H28" s="208"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="223" t="s">
         <v>1213</v>
       </c>
-      <c r="B22" s="189">
-        <f>SUM(B14:B21)</f>
-        <v>123.56399999999999</v>
-      </c>
-      <c r="C22" s="189">
-        <f>SUM(C14:C21)</f>
-        <v>39.323999999999998</v>
-      </c>
-      <c r="D22" s="189">
-        <f>SUM(D14:D21)</f>
-        <v>585.25</v>
-      </c>
-      <c r="E22" s="189">
-        <f>SUM(E14:E21)</f>
-        <v>93.9</v>
-      </c>
-      <c r="F22" s="194"/>
-      <c r="G22" s="195"/>
-      <c r="H22" s="195"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="201"/>
-      <c r="B23" s="201"/>
-      <c r="C23" s="202"/>
-      <c r="D23" s="189" t="s">
+      <c r="B29" s="223"/>
+      <c r="C29" s="223"/>
+      <c r="D29" s="223"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="208"/>
+      <c r="G29" s="208"/>
+      <c r="H29" s="208"/>
+    </row>
+    <row r="30" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="191" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B30" s="191" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="128" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D30" s="128" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E30" s="191" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F30" s="208"/>
+      <c r="G30" s="208"/>
+      <c r="H30" s="208"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="191" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B31" s="191">
+        <v>76</v>
+      </c>
+      <c r="C31" s="198">
+        <v>18.2</v>
+      </c>
+      <c r="D31" s="198">
+        <f>B31*2*2.1*0.13</f>
+        <v>41.496000000000002</v>
+      </c>
+      <c r="E31" s="198">
+        <f>SUM(C31:D31)</f>
+        <v>59.695999999999998</v>
+      </c>
+      <c r="F31" s="208"/>
+      <c r="G31" s="208"/>
+      <c r="H31" s="208"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="191" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B32" s="191">
+        <v>51</v>
+      </c>
+      <c r="C32" s="198">
+        <v>12.14</v>
+      </c>
+      <c r="D32" s="198">
+        <f t="shared" ref="D32:D33" si="7">B32*2*2.1*0.13</f>
+        <v>27.846000000000004</v>
+      </c>
+      <c r="E32" s="198">
+        <f t="shared" ref="E32:E33" si="8">SUM(C32:D32)</f>
+        <v>39.986000000000004</v>
+      </c>
+      <c r="F32" s="208"/>
+      <c r="G32" s="208"/>
+      <c r="H32" s="208"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="191" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B33" s="191">
+        <v>61</v>
+      </c>
+      <c r="C33" s="198">
+        <v>11.42</v>
+      </c>
+      <c r="D33" s="198">
+        <f t="shared" si="7"/>
+        <v>33.305999999999997</v>
+      </c>
+      <c r="E33" s="198">
+        <f t="shared" si="8"/>
+        <v>44.725999999999999</v>
+      </c>
+      <c r="F33" s="208"/>
+      <c r="G33" s="208"/>
+      <c r="H33" s="208"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="209" t="s">
         <v>843</v>
       </c>
-      <c r="E23" s="189">
-        <f>SUM(B22:E22)</f>
-        <v>842.0379999999999</v>
-      </c>
-      <c r="F23" s="194"/>
-      <c r="G23" s="195"/>
-      <c r="H23" s="195"/>
+      <c r="B34" s="209"/>
+      <c r="C34" s="209"/>
+      <c r="D34" s="209"/>
+      <c r="E34" s="200">
+        <f>SUM(E31:E33)</f>
+        <v>144.40800000000002</v>
+      </c>
+      <c r="F34" s="208"/>
+      <c r="G34" s="208"/>
+      <c r="H34" s="208"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="F7:H23"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="B5:D5"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="F10:H34"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -15252,13 +15529,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
     </row>
     <row r="2" spans="1:5" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -15331,11 +15608,11 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="201"/>
-      <c r="B6" s="201"/>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
+      <c r="A6" s="257"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="257"/>
+      <c r="E6" s="257"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -15362,26 +15639,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -15393,12 +15670,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1111</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="115" t="s">
         <v>1075</v>
       </c>
@@ -15410,12 +15687,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="206" t="s">
         <v>1111</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="206"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="207"/>
       <c r="F4" s="115" t="s">
         <v>1075</v>
       </c>
@@ -15424,13 +15701,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
+      <c r="A5" s="257"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="139" t="s">
@@ -15448,8 +15725,8 @@
       <c r="E6" s="139" t="s">
         <v>1109</v>
       </c>
-      <c r="F6" s="194"/>
-      <c r="G6" s="195"/>
+      <c r="F6" s="256"/>
+      <c r="G6" s="208"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="114">
@@ -15468,8 +15745,8 @@
         <f>C7*D7-29.76</f>
         <v>6622.08</v>
       </c>
-      <c r="F7" s="194"/>
-      <c r="G7" s="195"/>
+      <c r="F7" s="256"/>
+      <c r="G7" s="208"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="114">
@@ -15488,8 +15765,8 @@
         <f t="shared" ref="E8" si="0">C8*D8</f>
         <v>127.92</v>
       </c>
-      <c r="F8" s="194"/>
-      <c r="G8" s="195"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="208"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D9" s="139" t="s">
@@ -15499,8 +15776,8 @@
         <f>SUM(E7:E8)</f>
         <v>6750</v>
       </c>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -15531,26 +15808,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -15562,12 +15839,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1110</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -15579,12 +15856,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="206" t="s">
         <v>1110</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="206"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="207"/>
       <c r="F4" s="115" t="s">
         <v>19</v>
       </c>
@@ -15596,12 +15873,12 @@
       <c r="A5" s="114">
         <v>3</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="206" t="s">
         <v>1110</v>
       </c>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="206"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="115" t="s">
         <v>19</v>
       </c>
@@ -15637,26 +15914,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -15668,12 +15945,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1076</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="115" t="s">
         <v>1075</v>
       </c>
@@ -15685,12 +15962,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="206" t="s">
         <v>1076</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="206"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="207"/>
       <c r="F4" s="141" t="s">
         <v>1075</v>
       </c>
@@ -15702,12 +15979,12 @@
       <c r="A5" s="114">
         <v>3</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="206" t="s">
         <v>1076</v>
       </c>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="206"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="115" t="s">
         <v>1075</v>
       </c>
@@ -15731,8 +16008,8 @@
       <c r="E6" s="139" t="s">
         <v>1109</v>
       </c>
-      <c r="F6" s="239"/>
-      <c r="G6" s="207"/>
+      <c r="F6" s="265"/>
+      <c r="G6" s="237"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="139">
@@ -15752,8 +16029,8 @@
         <f t="shared" ref="E7:E8" si="0">C7*D7</f>
         <v>24.11</v>
       </c>
-      <c r="F7" s="194"/>
-      <c r="G7" s="195"/>
+      <c r="F7" s="256"/>
+      <c r="G7" s="208"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="139">
@@ -15773,8 +16050,8 @@
         <f t="shared" si="0"/>
         <v>35.580000000000005</v>
       </c>
-      <c r="F8" s="194"/>
-      <c r="G8" s="195"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="208"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="139">
@@ -15794,8 +16071,8 @@
         <f>C9*D9-10.8</f>
         <v>56.480000000000004</v>
       </c>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="208"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="139">
@@ -15815,8 +16092,8 @@
         <f>C10*D10</f>
         <v>54.33</v>
       </c>
-      <c r="F10" s="194"/>
-      <c r="G10" s="195"/>
+      <c r="F10" s="256"/>
+      <c r="G10" s="208"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="139">
@@ -15836,8 +16113,8 @@
         <f t="shared" ref="E11:E25" si="1">C11*D11</f>
         <v>21.8</v>
       </c>
-      <c r="F11" s="194"/>
-      <c r="G11" s="195"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="208"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="139">
@@ -15857,8 +16134,8 @@
         <f t="shared" si="1"/>
         <v>243.55</v>
       </c>
-      <c r="F12" s="194"/>
-      <c r="G12" s="195"/>
+      <c r="F12" s="256"/>
+      <c r="G12" s="208"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="139">
@@ -15878,8 +16155,8 @@
         <f t="shared" si="1"/>
         <v>97.42</v>
       </c>
-      <c r="F13" s="194"/>
-      <c r="G13" s="195"/>
+      <c r="F13" s="256"/>
+      <c r="G13" s="208"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="139">
@@ -15899,8 +16176,8 @@
         <f t="shared" si="1"/>
         <v>55.730000000000004</v>
       </c>
-      <c r="F14" s="194"/>
-      <c r="G14" s="195"/>
+      <c r="F14" s="256"/>
+      <c r="G14" s="208"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="139"/>
@@ -15913,8 +16190,8 @@
         <f>SUM(E7:E14)</f>
         <v>589</v>
       </c>
-      <c r="F15" s="194"/>
-      <c r="G15" s="195"/>
+      <c r="F15" s="256"/>
+      <c r="G15" s="208"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="139">
@@ -15934,8 +16211,8 @@
         <f t="shared" si="1"/>
         <v>15.149999999999999</v>
       </c>
-      <c r="F16" s="194"/>
-      <c r="G16" s="195"/>
+      <c r="F16" s="256"/>
+      <c r="G16" s="208"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="139">
@@ -15955,8 +16232,8 @@
         <f t="shared" si="1"/>
         <v>39.18</v>
       </c>
-      <c r="F17" s="194"/>
-      <c r="G17" s="195"/>
+      <c r="F17" s="256"/>
+      <c r="G17" s="208"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="139">
@@ -15976,8 +16253,8 @@
         <f t="shared" si="1"/>
         <v>21.35</v>
       </c>
-      <c r="F18" s="194"/>
-      <c r="G18" s="195"/>
+      <c r="F18" s="256"/>
+      <c r="G18" s="208"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="139">
@@ -15997,8 +16274,8 @@
         <f t="shared" si="1"/>
         <v>23.419999999999998</v>
       </c>
-      <c r="F19" s="194"/>
-      <c r="G19" s="195"/>
+      <c r="F19" s="256"/>
+      <c r="G19" s="208"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="139">
@@ -16018,8 +16295,8 @@
         <f t="shared" si="1"/>
         <v>21.349999999999998</v>
       </c>
-      <c r="F20" s="194"/>
-      <c r="G20" s="195"/>
+      <c r="F20" s="256"/>
+      <c r="G20" s="208"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="139">
@@ -16039,8 +16316,8 @@
         <f>C21*D21-13.44</f>
         <v>108.67999999999999</v>
       </c>
-      <c r="F21" s="194"/>
-      <c r="G21" s="195"/>
+      <c r="F21" s="256"/>
+      <c r="G21" s="208"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="139">
@@ -16060,8 +16337,8 @@
         <f t="shared" si="1"/>
         <v>30.529999999999998</v>
       </c>
-      <c r="F22" s="194"/>
-      <c r="G22" s="195"/>
+      <c r="F22" s="256"/>
+      <c r="G22" s="208"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="139">
@@ -16081,8 +16358,8 @@
         <f t="shared" si="1"/>
         <v>27.089999999999996</v>
       </c>
-      <c r="F23" s="194"/>
-      <c r="G23" s="195"/>
+      <c r="F23" s="256"/>
+      <c r="G23" s="208"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="139">
@@ -16102,8 +16379,8 @@
         <f t="shared" si="1"/>
         <v>57.79</v>
       </c>
-      <c r="F24" s="194"/>
-      <c r="G24" s="195"/>
+      <c r="F24" s="256"/>
+      <c r="G24" s="208"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="139">
@@ -16123,8 +16400,8 @@
         <f t="shared" si="1"/>
         <v>28.46</v>
       </c>
-      <c r="F25" s="194"/>
-      <c r="G25" s="195"/>
+      <c r="F25" s="256"/>
+      <c r="G25" s="208"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="139"/>
@@ -16137,8 +16414,8 @@
         <f>SUM(E16:E25)</f>
         <v>372.99999999999994</v>
       </c>
-      <c r="F26" s="194"/>
-      <c r="G26" s="195"/>
+      <c r="F26" s="256"/>
+      <c r="G26" s="208"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="139">
@@ -16158,8 +16435,8 @@
         <f t="shared" ref="E27:E36" si="2">C27*D27</f>
         <v>33.06</v>
       </c>
-      <c r="F27" s="194"/>
-      <c r="G27" s="195"/>
+      <c r="F27" s="256"/>
+      <c r="G27" s="208"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="139">
@@ -16179,8 +16456,8 @@
         <f>C28*D28-7.92</f>
         <v>31.259999999999998</v>
       </c>
-      <c r="F28" s="194"/>
-      <c r="G28" s="195"/>
+      <c r="F28" s="256"/>
+      <c r="G28" s="208"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="139">
@@ -16200,8 +16477,8 @@
         <f t="shared" si="2"/>
         <v>19.97</v>
       </c>
-      <c r="F29" s="194"/>
-      <c r="G29" s="195"/>
+      <c r="F29" s="256"/>
+      <c r="G29" s="208"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="139">
@@ -16221,8 +16498,8 @@
         <f t="shared" si="2"/>
         <v>21.44</v>
       </c>
-      <c r="F30" s="194"/>
-      <c r="G30" s="195"/>
+      <c r="F30" s="256"/>
+      <c r="G30" s="208"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="139">
@@ -16242,8 +16519,8 @@
         <f t="shared" si="2"/>
         <v>21.349999999999998</v>
       </c>
-      <c r="F31" s="194"/>
-      <c r="G31" s="195"/>
+      <c r="F31" s="256"/>
+      <c r="G31" s="208"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="139">
@@ -16263,8 +16540,8 @@
         <f t="shared" si="2"/>
         <v>183.17999999999998</v>
       </c>
-      <c r="F32" s="194"/>
-      <c r="G32" s="195"/>
+      <c r="F32" s="256"/>
+      <c r="G32" s="208"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="139">
@@ -16284,8 +16561,8 @@
         <f t="shared" si="2"/>
         <v>30.56</v>
       </c>
-      <c r="F33" s="194"/>
-      <c r="G33" s="195"/>
+      <c r="F33" s="256"/>
+      <c r="G33" s="208"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="139">
@@ -16305,8 +16582,8 @@
         <f t="shared" si="2"/>
         <v>27.089999999999996</v>
       </c>
-      <c r="F34" s="194"/>
-      <c r="G34" s="195"/>
+      <c r="F34" s="256"/>
+      <c r="G34" s="208"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="139">
@@ -16326,8 +16603,8 @@
         <f t="shared" si="2"/>
         <v>28.46</v>
       </c>
-      <c r="F35" s="194"/>
-      <c r="G35" s="195"/>
+      <c r="F35" s="256"/>
+      <c r="G35" s="208"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="139">
@@ -16347,8 +16624,8 @@
         <f t="shared" si="2"/>
         <v>29.839999999999996</v>
       </c>
-      <c r="F36" s="194"/>
-      <c r="G36" s="195"/>
+      <c r="F36" s="256"/>
+      <c r="G36" s="208"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="139">
@@ -16368,8 +16645,8 @@
         <f>C37*D37</f>
         <v>57.79</v>
       </c>
-      <c r="F37" s="194"/>
-      <c r="G37" s="195"/>
+      <c r="F37" s="256"/>
+      <c r="G37" s="208"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="139"/>
@@ -16382,8 +16659,8 @@
         <f>SUM(E27:E37)</f>
         <v>483.99999999999994</v>
       </c>
-      <c r="F38" s="194"/>
-      <c r="G38" s="195"/>
+      <c r="F38" s="256"/>
+      <c r="G38" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -16442,43 +16719,43 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="243" t="s">
+      <c r="A2" s="269" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="243"/>
-      <c r="C2" s="243"/>
-      <c r="D2" s="243"/>
-      <c r="E2" s="243"/>
-      <c r="F2" s="243"/>
-      <c r="G2" s="243"/>
-      <c r="H2" s="243"/>
-      <c r="I2" s="243"/>
+      <c r="B2" s="269"/>
+      <c r="C2" s="269"/>
+      <c r="D2" s="269"/>
+      <c r="E2" s="269"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="269"/>
+      <c r="H2" s="269"/>
+      <c r="I2" s="269"/>
     </row>
     <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="244" t="s">
+      <c r="A3" s="270" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="244"/>
-      <c r="C3" s="244"/>
-      <c r="D3" s="244"/>
-      <c r="E3" s="244"/>
-      <c r="F3" s="244"/>
-      <c r="G3" s="244"/>
-      <c r="H3" s="244"/>
-      <c r="I3" s="244"/>
+      <c r="B3" s="270"/>
+      <c r="C3" s="270"/>
+      <c r="D3" s="270"/>
+      <c r="E3" s="270"/>
+      <c r="F3" s="270"/>
+      <c r="G3" s="270"/>
+      <c r="H3" s="270"/>
+      <c r="I3" s="270"/>
     </row>
     <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="245" t="s">
+      <c r="A4" s="271" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="245"/>
-      <c r="C4" s="245"/>
-      <c r="D4" s="245"/>
-      <c r="E4" s="245"/>
-      <c r="F4" s="245"/>
-      <c r="G4" s="245"/>
-      <c r="H4" s="245"/>
-      <c r="I4" s="245"/>
+      <c r="B4" s="271"/>
+      <c r="C4" s="271"/>
+      <c r="D4" s="271"/>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="271"/>
     </row>
     <row r="5" spans="1:11" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="56" t="s">
@@ -27699,15 +27976,15 @@
       <c r="B501" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="C501" s="240" t="s">
+      <c r="C501" s="266" t="s">
         <v>778</v>
       </c>
-      <c r="D501" s="241"/>
-      <c r="E501" s="241"/>
-      <c r="F501" s="241"/>
-      <c r="G501" s="241"/>
-      <c r="H501" s="241"/>
-      <c r="I501" s="242"/>
+      <c r="D501" s="267"/>
+      <c r="E501" s="267"/>
+      <c r="F501" s="267"/>
+      <c r="G501" s="267"/>
+      <c r="H501" s="267"/>
+      <c r="I501" s="268"/>
     </row>
     <row r="502" spans="1:9" ht="54" x14ac:dyDescent="0.3">
       <c r="A502" s="4" t="s">
@@ -27743,15 +28020,15 @@
       <c r="B503" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C503" s="240" t="s">
+      <c r="C503" s="266" t="s">
         <v>787</v>
       </c>
-      <c r="D503" s="241"/>
-      <c r="E503" s="241"/>
-      <c r="F503" s="241"/>
-      <c r="G503" s="241"/>
-      <c r="H503" s="241"/>
-      <c r="I503" s="242"/>
+      <c r="D503" s="267"/>
+      <c r="E503" s="267"/>
+      <c r="F503" s="267"/>
+      <c r="G503" s="267"/>
+      <c r="H503" s="267"/>
+      <c r="I503" s="268"/>
     </row>
     <row r="504" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A504" s="4" t="s">
@@ -27760,15 +28037,15 @@
       <c r="B504" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="C504" s="240" t="s">
+      <c r="C504" s="266" t="s">
         <v>790</v>
       </c>
-      <c r="D504" s="241"/>
-      <c r="E504" s="241"/>
-      <c r="F504" s="241"/>
-      <c r="G504" s="241"/>
-      <c r="H504" s="241"/>
-      <c r="I504" s="242"/>
+      <c r="D504" s="267"/>
+      <c r="E504" s="267"/>
+      <c r="F504" s="267"/>
+      <c r="G504" s="267"/>
+      <c r="H504" s="267"/>
+      <c r="I504" s="268"/>
     </row>
     <row r="505" spans="1:9" ht="36" x14ac:dyDescent="0.3">
       <c r="A505" s="4" t="s">
@@ -27804,15 +28081,15 @@
       <c r="B506" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="C506" s="240" t="s">
+      <c r="C506" s="266" t="s">
         <v>798</v>
       </c>
-      <c r="D506" s="241"/>
-      <c r="E506" s="241"/>
-      <c r="F506" s="241"/>
-      <c r="G506" s="241"/>
-      <c r="H506" s="241"/>
-      <c r="I506" s="242"/>
+      <c r="D506" s="267"/>
+      <c r="E506" s="267"/>
+      <c r="F506" s="267"/>
+      <c r="G506" s="267"/>
+      <c r="H506" s="267"/>
+      <c r="I506" s="268"/>
     </row>
     <row r="507" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A507" s="4" t="s">
@@ -27821,15 +28098,15 @@
       <c r="B507" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="C507" s="240" t="s">
+      <c r="C507" s="266" t="s">
         <v>801</v>
       </c>
-      <c r="D507" s="241"/>
-      <c r="E507" s="241"/>
-      <c r="F507" s="241"/>
-      <c r="G507" s="241"/>
-      <c r="H507" s="241"/>
-      <c r="I507" s="242"/>
+      <c r="D507" s="267"/>
+      <c r="E507" s="267"/>
+      <c r="F507" s="267"/>
+      <c r="G507" s="267"/>
+      <c r="H507" s="267"/>
+      <c r="I507" s="268"/>
     </row>
     <row r="508" spans="1:9" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A508" s="4" t="s">
@@ -27838,15 +28115,15 @@
       <c r="B508" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="C508" s="240" t="s">
+      <c r="C508" s="266" t="s">
         <v>778</v>
       </c>
-      <c r="D508" s="241"/>
-      <c r="E508" s="241"/>
-      <c r="F508" s="241"/>
-      <c r="G508" s="241"/>
-      <c r="H508" s="241"/>
-      <c r="I508" s="242"/>
+      <c r="D508" s="267"/>
+      <c r="E508" s="267"/>
+      <c r="F508" s="267"/>
+      <c r="G508" s="267"/>
+      <c r="H508" s="267"/>
+      <c r="I508" s="268"/>
     </row>
     <row r="509" spans="1:9" ht="90" x14ac:dyDescent="0.3">
       <c r="A509" s="4" t="s">
@@ -32817,26 +33094,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -32848,12 +33125,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1081</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -32865,12 +33142,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="206" t="s">
         <v>1081</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="206"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="207"/>
       <c r="F4" s="141" t="s">
         <v>19</v>
       </c>
@@ -32882,12 +33159,12 @@
       <c r="A5" s="114">
         <v>3</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="206" t="s">
         <v>1081</v>
       </c>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="206"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="115" t="s">
         <v>19</v>
       </c>
@@ -32899,12 +33176,12 @@
       <c r="A6" s="140">
         <v>4</v>
       </c>
-      <c r="B6" s="246" t="s">
+      <c r="B6" s="272" t="s">
         <v>1081</v>
       </c>
-      <c r="C6" s="247"/>
-      <c r="D6" s="247"/>
-      <c r="E6" s="248"/>
+      <c r="C6" s="273"/>
+      <c r="D6" s="273"/>
+      <c r="E6" s="274"/>
       <c r="F6" s="141" t="s">
         <v>19</v>
       </c>
@@ -32941,26 +33218,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -32972,12 +33249,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1070</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -32989,12 +33266,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="246" t="s">
+      <c r="B4" s="272" t="s">
         <v>1070</v>
       </c>
-      <c r="C4" s="247"/>
-      <c r="D4" s="247"/>
-      <c r="E4" s="248"/>
+      <c r="C4" s="273"/>
+      <c r="D4" s="273"/>
+      <c r="E4" s="274"/>
       <c r="F4" s="141" t="s">
         <v>19</v>
       </c>
@@ -33029,26 +33306,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -33060,12 +33337,12 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1070</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="115" t="s">
         <v>19</v>
       </c>
@@ -33078,12 +33355,12 @@
       <c r="A4" s="127">
         <v>2</v>
       </c>
-      <c r="B4" s="251" t="s">
+      <c r="B4" s="220" t="s">
         <v>1076</v>
       </c>
-      <c r="C4" s="252"/>
-      <c r="D4" s="252"/>
-      <c r="E4" s="253"/>
+      <c r="C4" s="277"/>
+      <c r="D4" s="277"/>
+      <c r="E4" s="221"/>
       <c r="F4" s="128" t="s">
         <v>1075</v>
       </c>
@@ -33092,13 +33369,13 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
+      <c r="A5" s="257"/>
+      <c r="B5" s="257"/>
+      <c r="C5" s="257"/>
+      <c r="D5" s="257"/>
+      <c r="E5" s="257"/>
+      <c r="F5" s="257"/>
+      <c r="G5" s="257"/>
     </row>
     <row r="6" spans="1:7" s="120" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="122" t="s">
@@ -33107,11 +33384,11 @@
       <c r="B6" s="123" t="s">
         <v>1077</v>
       </c>
-      <c r="C6" s="249"/>
-      <c r="D6" s="250"/>
-      <c r="E6" s="250"/>
-      <c r="F6" s="250"/>
-      <c r="G6" s="250"/>
+      <c r="C6" s="275"/>
+      <c r="D6" s="276"/>
+      <c r="E6" s="276"/>
+      <c r="F6" s="276"/>
+      <c r="G6" s="276"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="124">
@@ -33121,11 +33398,11 @@
         <f>7.72-0.525</f>
         <v>7.1949999999999994</v>
       </c>
-      <c r="C7" s="249"/>
-      <c r="D7" s="250"/>
-      <c r="E7" s="250"/>
-      <c r="F7" s="250"/>
-      <c r="G7" s="250"/>
+      <c r="C7" s="275"/>
+      <c r="D7" s="276"/>
+      <c r="E7" s="276"/>
+      <c r="F7" s="276"/>
+      <c r="G7" s="276"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="124">
@@ -33135,11 +33412,11 @@
         <f>0.6125*3.15-1.8821*1.1*0.25</f>
         <v>1.4117975</v>
       </c>
-      <c r="C8" s="249"/>
-      <c r="D8" s="250"/>
-      <c r="E8" s="250"/>
-      <c r="F8" s="250"/>
-      <c r="G8" s="250"/>
+      <c r="C8" s="275"/>
+      <c r="D8" s="276"/>
+      <c r="E8" s="276"/>
+      <c r="F8" s="276"/>
+      <c r="G8" s="276"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="124">
@@ -33149,11 +33426,11 @@
         <f>0.696*3.15-0.7*2.1*0.12*4</f>
         <v>1.4867999999999997</v>
       </c>
-      <c r="C9" s="249"/>
-      <c r="D9" s="250"/>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
+      <c r="C9" s="275"/>
+      <c r="D9" s="276"/>
+      <c r="E9" s="276"/>
+      <c r="F9" s="276"/>
+      <c r="G9" s="276"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="124">
@@ -33163,11 +33440,11 @@
         <f>0.5625*3.15-0.156</f>
         <v>1.615875</v>
       </c>
-      <c r="C10" s="249"/>
-      <c r="D10" s="250"/>
-      <c r="E10" s="250"/>
-      <c r="F10" s="250"/>
-      <c r="G10" s="250"/>
+      <c r="C10" s="275"/>
+      <c r="D10" s="276"/>
+      <c r="E10" s="276"/>
+      <c r="F10" s="276"/>
+      <c r="G10" s="276"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="124">
@@ -33177,11 +33454,11 @@
         <f>0.4188*3.15--0.7*2.1*0.12*2</f>
         <v>1.6720200000000001</v>
       </c>
-      <c r="C11" s="249"/>
-      <c r="D11" s="250"/>
-      <c r="E11" s="250"/>
-      <c r="F11" s="250"/>
-      <c r="G11" s="250"/>
+      <c r="C11" s="275"/>
+      <c r="D11" s="276"/>
+      <c r="E11" s="276"/>
+      <c r="F11" s="276"/>
+      <c r="G11" s="276"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="124">
@@ -33191,11 +33468,11 @@
         <f>0.45*3.15-1*2.2*0.25</f>
         <v>0.86749999999999994</v>
       </c>
-      <c r="C12" s="249"/>
-      <c r="D12" s="250"/>
-      <c r="E12" s="250"/>
-      <c r="F12" s="250"/>
-      <c r="G12" s="250"/>
+      <c r="C12" s="275"/>
+      <c r="D12" s="276"/>
+      <c r="E12" s="276"/>
+      <c r="F12" s="276"/>
+      <c r="G12" s="276"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="124">
@@ -33205,11 +33482,11 @@
         <f>0.125*3.15+0.0375*3.15</f>
         <v>0.51187499999999997</v>
       </c>
-      <c r="C13" s="249"/>
-      <c r="D13" s="250"/>
-      <c r="E13" s="250"/>
-      <c r="F13" s="250"/>
-      <c r="G13" s="250"/>
+      <c r="C13" s="275"/>
+      <c r="D13" s="276"/>
+      <c r="E13" s="276"/>
+      <c r="F13" s="276"/>
+      <c r="G13" s="276"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="134">
@@ -33219,11 +33496,11 @@
         <f>0.45*3.15-1*2.2*0.25</f>
         <v>0.86749999999999994</v>
       </c>
-      <c r="C14" s="249"/>
-      <c r="D14" s="250"/>
-      <c r="E14" s="250"/>
-      <c r="F14" s="250"/>
-      <c r="G14" s="250"/>
+      <c r="C14" s="275"/>
+      <c r="D14" s="276"/>
+      <c r="E14" s="276"/>
+      <c r="F14" s="276"/>
+      <c r="G14" s="276"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="134">
@@ -33233,11 +33510,11 @@
         <f>3.9*3.15*0.25-0.25*2.1</f>
         <v>2.5462500000000001</v>
       </c>
-      <c r="C15" s="249"/>
-      <c r="D15" s="250"/>
-      <c r="E15" s="250"/>
-      <c r="F15" s="250"/>
-      <c r="G15" s="250"/>
+      <c r="C15" s="275"/>
+      <c r="D15" s="276"/>
+      <c r="E15" s="276"/>
+      <c r="F15" s="276"/>
+      <c r="G15" s="276"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="134">
@@ -33247,11 +33524,11 @@
         <f>0.9875*3.15-0.294*2.1+0.4*3.15-0.03</f>
         <v>3.7232250000000007</v>
       </c>
-      <c r="C16" s="249"/>
-      <c r="D16" s="250"/>
-      <c r="E16" s="250"/>
-      <c r="F16" s="250"/>
-      <c r="G16" s="250"/>
+      <c r="C16" s="275"/>
+      <c r="D16" s="276"/>
+      <c r="E16" s="276"/>
+      <c r="F16" s="276"/>
+      <c r="G16" s="276"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="114" t="s">
@@ -33261,11 +33538,11 @@
         <f>SUM(B7:B16)</f>
         <v>21.897842499999996</v>
       </c>
-      <c r="C17" s="249"/>
-      <c r="D17" s="250"/>
-      <c r="E17" s="250"/>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
+      <c r="C17" s="275"/>
+      <c r="D17" s="276"/>
+      <c r="E17" s="276"/>
+      <c r="F17" s="276"/>
+      <c r="G17" s="276"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -33302,30 +33579,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
     </row>
     <row r="2" spans="1:9" s="164" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="186" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="220" t="s">
+      <c r="B2" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
       <c r="H2" s="37" t="s">
         <v>10</v>
       </c>
@@ -33337,14 +33614,14 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="218" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
+      <c r="B3" s="231" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="231"/>
       <c r="H3" s="115" t="s">
         <v>15</v>
       </c>
@@ -33357,14 +33634,14 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="218" t="s">
-        <v>1219</v>
-      </c>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
+      <c r="B4" s="231" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C4" s="231"/>
+      <c r="D4" s="231"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="231"/>
+      <c r="G4" s="231"/>
       <c r="H4" s="115" t="s">
         <v>15</v>
       </c>
@@ -33377,14 +33654,14 @@
       <c r="A5" s="140">
         <v>3</v>
       </c>
-      <c r="B5" s="218" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C5" s="218"/>
-      <c r="D5" s="218"/>
-      <c r="E5" s="218"/>
-      <c r="F5" s="218"/>
-      <c r="G5" s="218"/>
+      <c r="B5" s="231" t="s">
+        <v>1210</v>
+      </c>
+      <c r="C5" s="231"/>
+      <c r="D5" s="231"/>
+      <c r="E5" s="231"/>
+      <c r="F5" s="231"/>
+      <c r="G5" s="231"/>
       <c r="H5" s="115" t="s">
         <v>15</v>
       </c>
@@ -33397,14 +33674,14 @@
       <c r="A6" s="140">
         <v>4</v>
       </c>
-      <c r="B6" s="218" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C6" s="218"/>
-      <c r="D6" s="218"/>
-      <c r="E6" s="218"/>
-      <c r="F6" s="218"/>
-      <c r="G6" s="218"/>
+      <c r="B6" s="231" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C6" s="231"/>
+      <c r="D6" s="231"/>
+      <c r="E6" s="231"/>
+      <c r="F6" s="231"/>
+      <c r="G6" s="231"/>
       <c r="H6" s="115" t="s">
         <v>15</v>
       </c>
@@ -33417,14 +33694,14 @@
       <c r="A7" s="140">
         <v>5</v>
       </c>
-      <c r="B7" s="218" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C7" s="218"/>
-      <c r="D7" s="218"/>
-      <c r="E7" s="218"/>
-      <c r="F7" s="218"/>
-      <c r="G7" s="218"/>
+      <c r="B7" s="231" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C7" s="231"/>
+      <c r="D7" s="231"/>
+      <c r="E7" s="231"/>
+      <c r="F7" s="231"/>
+      <c r="G7" s="231"/>
       <c r="H7" s="115" t="s">
         <v>15</v>
       </c>
@@ -33437,14 +33714,14 @@
       <c r="A8" s="140">
         <v>6</v>
       </c>
-      <c r="B8" s="218" t="s">
-        <v>1222</v>
-      </c>
-      <c r="C8" s="218"/>
-      <c r="D8" s="218"/>
-      <c r="E8" s="218"/>
-      <c r="F8" s="218"/>
-      <c r="G8" s="218"/>
+      <c r="B8" s="231" t="s">
+        <v>1208</v>
+      </c>
+      <c r="C8" s="231"/>
+      <c r="D8" s="231"/>
+      <c r="E8" s="231"/>
+      <c r="F8" s="231"/>
+      <c r="G8" s="231"/>
       <c r="H8" s="115" t="s">
         <v>15</v>
       </c>
@@ -33457,14 +33734,14 @@
       <c r="A9" s="140">
         <v>7</v>
       </c>
-      <c r="B9" s="218" t="s">
-        <v>1223</v>
-      </c>
-      <c r="C9" s="218"/>
-      <c r="D9" s="218"/>
-      <c r="E9" s="218"/>
-      <c r="F9" s="218"/>
-      <c r="G9" s="218"/>
+      <c r="B9" s="231" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C9" s="231"/>
+      <c r="D9" s="231"/>
+      <c r="E9" s="231"/>
+      <c r="F9" s="231"/>
+      <c r="G9" s="231"/>
       <c r="H9" s="115" t="s">
         <v>15</v>
       </c>
@@ -33474,32 +33751,32 @@
       </c>
     </row>
     <row r="10" spans="1:9" s="164" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="215"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="217"/>
-      <c r="D10" s="210"/>
-      <c r="E10" s="211"/>
-      <c r="F10" s="211"/>
-      <c r="G10" s="211"/>
-      <c r="H10" s="211"/>
-      <c r="I10" s="211"/>
+      <c r="A10" s="232"/>
+      <c r="B10" s="233"/>
+      <c r="C10" s="234"/>
+      <c r="D10" s="240"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="176" t="s">
         <v>829</v>
       </c>
       <c r="B11" s="176" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C11" s="176" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D11" s="212"/>
-      <c r="E11" s="213"/>
-      <c r="F11" s="213"/>
-      <c r="G11" s="213"/>
-      <c r="H11" s="213"/>
-      <c r="I11" s="213"/>
+        <v>1189</v>
+      </c>
+      <c r="D11" s="242"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
+      <c r="H11" s="243"/>
+      <c r="I11" s="243"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="176">
@@ -33512,12 +33789,12 @@
         <f>C18+I18+C25+C32</f>
         <v>631.9</v>
       </c>
-      <c r="D12" s="212"/>
-      <c r="E12" s="213"/>
-      <c r="F12" s="213"/>
-      <c r="G12" s="213"/>
-      <c r="H12" s="213"/>
-      <c r="I12" s="213"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="243"/>
+      <c r="F12" s="243"/>
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="176">
@@ -33530,12 +33807,12 @@
         <f>C19+I19+C26+C33</f>
         <v>559.50399999999991</v>
       </c>
-      <c r="D13" s="212"/>
-      <c r="E13" s="213"/>
-      <c r="F13" s="213"/>
-      <c r="G13" s="213"/>
-      <c r="H13" s="213"/>
-      <c r="I13" s="213"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="243"/>
+      <c r="F13" s="243"/>
+      <c r="G13" s="243"/>
+      <c r="H13" s="243"/>
+      <c r="I13" s="243"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="176">
@@ -33548,65 +33825,65 @@
         <f>C20+I20+C27+C34</f>
         <v>497.18099999999998</v>
       </c>
-      <c r="D14" s="212"/>
-      <c r="E14" s="213"/>
-      <c r="F14" s="213"/>
-      <c r="G14" s="213"/>
-      <c r="H14" s="213"/>
-      <c r="I14" s="213"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="243"/>
+      <c r="F14" s="243"/>
+      <c r="G14" s="243"/>
+      <c r="H14" s="243"/>
+      <c r="I14" s="243"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="208" t="s">
+      <c r="A15" s="238" t="s">
         <v>843</v>
       </c>
-      <c r="B15" s="208"/>
+      <c r="B15" s="238"/>
       <c r="C15" s="176">
         <f>SUM(C12:C14)</f>
         <v>1688.585</v>
       </c>
-      <c r="D15" s="212"/>
-      <c r="E15" s="213"/>
-      <c r="F15" s="213"/>
-      <c r="G15" s="213"/>
-      <c r="H15" s="213"/>
-      <c r="I15" s="213"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="243"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="243"/>
+      <c r="I15" s="243"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="209" t="s">
+      <c r="A16" s="239" t="s">
         <v>1042</v>
       </c>
-      <c r="B16" s="209"/>
-      <c r="C16" s="209"/>
-      <c r="D16" s="195"/>
-      <c r="E16" s="195"/>
-      <c r="F16" s="195"/>
-      <c r="G16" s="214" t="s">
-        <v>1199</v>
-      </c>
-      <c r="H16" s="214"/>
-      <c r="I16" s="214"/>
+      <c r="B16" s="239"/>
+      <c r="C16" s="239"/>
+      <c r="D16" s="208"/>
+      <c r="E16" s="208"/>
+      <c r="F16" s="208"/>
+      <c r="G16" s="244" t="s">
+        <v>1196</v>
+      </c>
+      <c r="H16" s="244"/>
+      <c r="I16" s="244"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="176" t="s">
         <v>829</v>
       </c>
       <c r="B17" s="176" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C17" s="176" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D17" s="195"/>
-      <c r="E17" s="195"/>
-      <c r="F17" s="195"/>
+        <v>1189</v>
+      </c>
+      <c r="D17" s="208"/>
+      <c r="E17" s="208"/>
+      <c r="F17" s="208"/>
       <c r="G17" s="176" t="s">
         <v>829</v>
       </c>
       <c r="H17" s="176" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="I17" s="176" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
@@ -33620,9 +33897,9 @@
         <f>3.38*8+(1.5*4 + 1.1*4)*3.3+(6.8+9.19)*3.3</f>
         <v>114.12699999999998</v>
       </c>
-      <c r="D18" s="195"/>
-      <c r="E18" s="195"/>
-      <c r="F18" s="195"/>
+      <c r="D18" s="208"/>
+      <c r="E18" s="208"/>
+      <c r="F18" s="208"/>
       <c r="G18" s="176">
         <v>1</v>
       </c>
@@ -33645,9 +33922,9 @@
         <f>8*2.8+7.2*3.3</f>
         <v>46.16</v>
       </c>
-      <c r="D19" s="195"/>
-      <c r="E19" s="195"/>
-      <c r="F19" s="195"/>
+      <c r="D19" s="208"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="208"/>
       <c r="G19" s="176">
         <v>2</v>
       </c>
@@ -33670,9 +33947,9 @@
         <f>3.38*7.8+4.2*4</f>
         <v>43.164000000000001</v>
       </c>
-      <c r="D20" s="195"/>
-      <c r="E20" s="195"/>
-      <c r="F20" s="195"/>
+      <c r="D20" s="208"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="208"/>
       <c r="G20" s="176">
         <v>3</v>
       </c>
@@ -33685,66 +33962,66 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="208" t="s">
+      <c r="A21" s="238" t="s">
         <v>843</v>
       </c>
-      <c r="B21" s="208"/>
+      <c r="B21" s="238"/>
       <c r="C21" s="176">
         <f>SUM(C18:C20)</f>
         <v>203.45099999999996</v>
       </c>
-      <c r="D21" s="195"/>
-      <c r="E21" s="195"/>
-      <c r="F21" s="195"/>
-      <c r="G21" s="208" t="s">
+      <c r="D21" s="208"/>
+      <c r="E21" s="208"/>
+      <c r="F21" s="208"/>
+      <c r="G21" s="238" t="s">
         <v>843</v>
       </c>
-      <c r="H21" s="208"/>
+      <c r="H21" s="238"/>
       <c r="I21" s="176">
         <f>SUM(I18:I20)</f>
         <v>37.827999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="215"/>
-      <c r="B22" s="216"/>
-      <c r="C22" s="217"/>
-      <c r="D22" s="195"/>
-      <c r="E22" s="195"/>
-      <c r="F22" s="195"/>
-      <c r="G22" s="207"/>
-      <c r="H22" s="207"/>
-      <c r="I22" s="207"/>
+      <c r="A22" s="232"/>
+      <c r="B22" s="233"/>
+      <c r="C22" s="234"/>
+      <c r="D22" s="208"/>
+      <c r="E22" s="208"/>
+      <c r="F22" s="208"/>
+      <c r="G22" s="237"/>
+      <c r="H22" s="237"/>
+      <c r="I22" s="237"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="209" t="s">
+      <c r="A23" s="239" t="s">
         <v>878</v>
       </c>
-      <c r="B23" s="209"/>
-      <c r="C23" s="209"/>
-      <c r="D23" s="195"/>
-      <c r="E23" s="195"/>
-      <c r="F23" s="195"/>
-      <c r="G23" s="195"/>
-      <c r="H23" s="195"/>
-      <c r="I23" s="195"/>
+      <c r="B23" s="239"/>
+      <c r="C23" s="239"/>
+      <c r="D23" s="208"/>
+      <c r="E23" s="208"/>
+      <c r="F23" s="208"/>
+      <c r="G23" s="208"/>
+      <c r="H23" s="208"/>
+      <c r="I23" s="208"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="176" t="s">
         <v>829</v>
       </c>
       <c r="B24" s="176" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C24" s="176" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D24" s="195"/>
-      <c r="E24" s="195"/>
-      <c r="F24" s="195"/>
-      <c r="G24" s="195"/>
-      <c r="H24" s="195"/>
-      <c r="I24" s="195"/>
+        <v>1189</v>
+      </c>
+      <c r="D24" s="208"/>
+      <c r="E24" s="208"/>
+      <c r="F24" s="208"/>
+      <c r="G24" s="208"/>
+      <c r="H24" s="208"/>
+      <c r="I24" s="208"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="176">
@@ -33757,12 +34034,12 @@
         <f>0.62*8+1.1*4+6.9*0.7+(6.8+9.19)*0.7</f>
         <v>25.382999999999996</v>
       </c>
-      <c r="D25" s="195"/>
-      <c r="E25" s="195"/>
-      <c r="F25" s="195"/>
-      <c r="G25" s="195"/>
-      <c r="H25" s="195"/>
-      <c r="I25" s="195"/>
+      <c r="D25" s="208"/>
+      <c r="E25" s="208"/>
+      <c r="F25" s="208"/>
+      <c r="G25" s="208"/>
+      <c r="H25" s="208"/>
+      <c r="I25" s="208"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="176">
@@ -33775,12 +34052,12 @@
         <f>2.2*0.7</f>
         <v>1.54</v>
       </c>
-      <c r="D26" s="195"/>
-      <c r="E26" s="195"/>
-      <c r="F26" s="195"/>
-      <c r="G26" s="195"/>
-      <c r="H26" s="195"/>
-      <c r="I26" s="195"/>
+      <c r="D26" s="208"/>
+      <c r="E26" s="208"/>
+      <c r="F26" s="208"/>
+      <c r="G26" s="208"/>
+      <c r="H26" s="208"/>
+      <c r="I26" s="208"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="176">
@@ -33793,69 +34070,69 @@
         <f>2.16*4+0.62*7.8+0.7*1.8+5*4+4*0.62+12.1*0.7</f>
         <v>45.686</v>
       </c>
-      <c r="D27" s="195"/>
-      <c r="E27" s="195"/>
-      <c r="F27" s="195"/>
-      <c r="G27" s="195"/>
-      <c r="H27" s="195"/>
-      <c r="I27" s="195"/>
+      <c r="D27" s="208"/>
+      <c r="E27" s="208"/>
+      <c r="F27" s="208"/>
+      <c r="G27" s="208"/>
+      <c r="H27" s="208"/>
+      <c r="I27" s="208"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="208" t="s">
+      <c r="A28" s="238" t="s">
         <v>843</v>
       </c>
-      <c r="B28" s="208"/>
+      <c r="B28" s="238"/>
       <c r="C28" s="176">
         <f>SUM(C25:C27)</f>
         <v>72.608999999999995</v>
       </c>
-      <c r="D28" s="195"/>
-      <c r="E28" s="195"/>
-      <c r="F28" s="195"/>
-      <c r="G28" s="195"/>
-      <c r="H28" s="195"/>
-      <c r="I28" s="195"/>
+      <c r="D28" s="208"/>
+      <c r="E28" s="208"/>
+      <c r="F28" s="208"/>
+      <c r="G28" s="208"/>
+      <c r="H28" s="208"/>
+      <c r="I28" s="208"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="215"/>
-      <c r="B29" s="216"/>
-      <c r="C29" s="217"/>
-      <c r="D29" s="195"/>
-      <c r="E29" s="195"/>
-      <c r="F29" s="195"/>
-      <c r="G29" s="195"/>
-      <c r="H29" s="195"/>
-      <c r="I29" s="195"/>
+      <c r="A29" s="232"/>
+      <c r="B29" s="233"/>
+      <c r="C29" s="234"/>
+      <c r="D29" s="208"/>
+      <c r="E29" s="208"/>
+      <c r="F29" s="208"/>
+      <c r="G29" s="208"/>
+      <c r="H29" s="208"/>
+      <c r="I29" s="208"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="209" t="s">
+      <c r="A30" s="239" t="s">
         <v>941</v>
       </c>
-      <c r="B30" s="209"/>
-      <c r="C30" s="209"/>
-      <c r="D30" s="195"/>
-      <c r="E30" s="195"/>
-      <c r="F30" s="195"/>
-      <c r="G30" s="195"/>
-      <c r="H30" s="195"/>
-      <c r="I30" s="195"/>
+      <c r="B30" s="239"/>
+      <c r="C30" s="239"/>
+      <c r="D30" s="208"/>
+      <c r="E30" s="208"/>
+      <c r="F30" s="208"/>
+      <c r="G30" s="208"/>
+      <c r="H30" s="208"/>
+      <c r="I30" s="208"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="176" t="s">
         <v>829</v>
       </c>
       <c r="B31" s="176" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C31" s="176" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D31" s="195"/>
-      <c r="E31" s="195"/>
-      <c r="F31" s="195"/>
-      <c r="G31" s="195"/>
-      <c r="H31" s="195"/>
-      <c r="I31" s="195"/>
+        <v>1189</v>
+      </c>
+      <c r="D31" s="208"/>
+      <c r="E31" s="208"/>
+      <c r="F31" s="208"/>
+      <c r="G31" s="208"/>
+      <c r="H31" s="208"/>
+      <c r="I31" s="208"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="176">
@@ -33868,12 +34145,12 @@
         <f>3.38*3+6.9*3.3+16.25*12.2+7.75*12.2+12.3*8+15.25*4</f>
         <v>485.11</v>
       </c>
-      <c r="D32" s="195"/>
-      <c r="E32" s="195"/>
-      <c r="F32" s="195"/>
-      <c r="G32" s="195"/>
-      <c r="H32" s="195"/>
-      <c r="I32" s="195"/>
+      <c r="D32" s="208"/>
+      <c r="E32" s="208"/>
+      <c r="F32" s="208"/>
+      <c r="G32" s="208"/>
+      <c r="H32" s="208"/>
+      <c r="I32" s="208"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="176">
@@ -33886,12 +34163,12 @@
         <f>4*15.2+1.6*8+1.3*3.38+4.2*4+12.14*3.3+14.35*4+5.6*8+24.13*4+17.3*9.1+2.2*3.3</f>
         <v>498.26599999999996</v>
       </c>
-      <c r="D33" s="195"/>
-      <c r="E33" s="195"/>
-      <c r="F33" s="195"/>
-      <c r="G33" s="195"/>
-      <c r="H33" s="195"/>
-      <c r="I33" s="195"/>
+      <c r="D33" s="208"/>
+      <c r="E33" s="208"/>
+      <c r="F33" s="208"/>
+      <c r="G33" s="208"/>
+      <c r="H33" s="208"/>
+      <c r="I33" s="208"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="176">
@@ -33904,41 +34181,31 @@
         <f>6*4+24.77*3.3+24.3*3.3+36.5*4+1.8*3.3+4*3.38+12.1*3.3</f>
         <v>391.32099999999997</v>
       </c>
-      <c r="D34" s="195"/>
-      <c r="E34" s="195"/>
-      <c r="F34" s="195"/>
-      <c r="G34" s="195"/>
-      <c r="H34" s="195"/>
-      <c r="I34" s="195"/>
+      <c r="D34" s="208"/>
+      <c r="E34" s="208"/>
+      <c r="F34" s="208"/>
+      <c r="G34" s="208"/>
+      <c r="H34" s="208"/>
+      <c r="I34" s="208"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="208" t="s">
+      <c r="A35" s="238" t="s">
         <v>843</v>
       </c>
-      <c r="B35" s="208"/>
+      <c r="B35" s="238"/>
       <c r="C35" s="176">
         <f>SUM(C32:C34)</f>
         <v>1374.6969999999999</v>
       </c>
-      <c r="D35" s="195"/>
-      <c r="E35" s="195"/>
-      <c r="F35" s="195"/>
-      <c r="G35" s="195"/>
-      <c r="H35" s="195"/>
-      <c r="I35" s="195"/>
+      <c r="D35" s="208"/>
+      <c r="E35" s="208"/>
+      <c r="F35" s="208"/>
+      <c r="G35" s="208"/>
+      <c r="H35" s="208"/>
+      <c r="I35" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="B9:G9"/>
     <mergeCell ref="G22:I35"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A16:C16"/>
@@ -33953,6 +34220,16 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="B9:G9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -33978,19 +34255,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
     </row>
     <row r="2" spans="1:11" s="119" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
@@ -33999,17 +34276,17 @@
       <c r="B2" s="37" t="s">
         <v>1079</v>
       </c>
-      <c r="C2" s="203" t="s">
+      <c r="C2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="235"/>
-      <c r="E2" s="235"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="203" t="s">
+      <c r="D2" s="261"/>
+      <c r="E2" s="261"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="226" t="s">
         <v>814</v>
       </c>
-      <c r="H2" s="235"/>
-      <c r="I2" s="204"/>
+      <c r="H2" s="261"/>
+      <c r="I2" s="227"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -34024,17 +34301,17 @@
       <c r="B3" s="114">
         <v>72</v>
       </c>
-      <c r="C3" s="205" t="s">
+      <c r="C3" s="206" t="s">
         <v>1072</v>
       </c>
-      <c r="D3" s="234"/>
-      <c r="E3" s="234"/>
-      <c r="F3" s="206"/>
-      <c r="G3" s="254" t="s">
+      <c r="D3" s="260"/>
+      <c r="E3" s="260"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="282" t="s">
         <v>1071</v>
       </c>
-      <c r="H3" s="255"/>
-      <c r="I3" s="256"/>
+      <c r="H3" s="283"/>
+      <c r="I3" s="284"/>
       <c r="J3" s="115" t="s">
         <v>15</v>
       </c>
@@ -34049,17 +34326,17 @@
       <c r="B4" s="127">
         <v>78</v>
       </c>
-      <c r="C4" s="251" t="s">
+      <c r="C4" s="220" t="s">
         <v>1072</v>
       </c>
-      <c r="D4" s="252"/>
-      <c r="E4" s="252"/>
-      <c r="F4" s="253"/>
-      <c r="G4" s="257" t="s">
+      <c r="D4" s="277"/>
+      <c r="E4" s="277"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="285" t="s">
         <v>1073</v>
       </c>
-      <c r="H4" s="258"/>
-      <c r="I4" s="259"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="287"/>
       <c r="J4" s="128" t="s">
         <v>15</v>
       </c>
@@ -34074,17 +34351,17 @@
       <c r="B5" s="114">
         <v>84</v>
       </c>
-      <c r="C5" s="205" t="s">
+      <c r="C5" s="206" t="s">
         <v>1072</v>
       </c>
-      <c r="D5" s="234"/>
-      <c r="E5" s="234"/>
-      <c r="F5" s="206"/>
-      <c r="G5" s="254" t="s">
+      <c r="D5" s="260"/>
+      <c r="E5" s="260"/>
+      <c r="F5" s="207"/>
+      <c r="G5" s="282" t="s">
         <v>1071</v>
       </c>
-      <c r="H5" s="255"/>
-      <c r="I5" s="256"/>
+      <c r="H5" s="283"/>
+      <c r="I5" s="284"/>
       <c r="J5" s="115" t="s">
         <v>15</v>
       </c>
@@ -34099,17 +34376,17 @@
       <c r="B6" s="127">
         <v>90</v>
       </c>
-      <c r="C6" s="251" t="s">
+      <c r="C6" s="220" t="s">
         <v>1072</v>
       </c>
-      <c r="D6" s="252"/>
-      <c r="E6" s="252"/>
-      <c r="F6" s="253"/>
-      <c r="G6" s="257" t="s">
+      <c r="D6" s="277"/>
+      <c r="E6" s="277"/>
+      <c r="F6" s="221"/>
+      <c r="G6" s="285" t="s">
         <v>1073</v>
       </c>
-      <c r="H6" s="258"/>
-      <c r="I6" s="259"/>
+      <c r="H6" s="286"/>
+      <c r="I6" s="287"/>
       <c r="J6" s="128" t="s">
         <v>15</v>
       </c>
@@ -34124,17 +34401,17 @@
       <c r="B7" s="114">
         <v>96</v>
       </c>
-      <c r="C7" s="205" t="s">
+      <c r="C7" s="206" t="s">
         <v>1072</v>
       </c>
-      <c r="D7" s="234"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="206"/>
-      <c r="G7" s="254" t="s">
+      <c r="D7" s="260"/>
+      <c r="E7" s="260"/>
+      <c r="F7" s="207"/>
+      <c r="G7" s="282" t="s">
         <v>1071</v>
       </c>
-      <c r="H7" s="255"/>
-      <c r="I7" s="256"/>
+      <c r="H7" s="283"/>
+      <c r="I7" s="284"/>
       <c r="J7" s="115" t="s">
         <v>15</v>
       </c>
@@ -34149,17 +34426,17 @@
       <c r="B8" s="127">
         <v>102</v>
       </c>
-      <c r="C8" s="251" t="s">
+      <c r="C8" s="220" t="s">
         <v>1072</v>
       </c>
-      <c r="D8" s="252"/>
-      <c r="E8" s="252"/>
-      <c r="F8" s="253"/>
-      <c r="G8" s="257" t="s">
+      <c r="D8" s="277"/>
+      <c r="E8" s="277"/>
+      <c r="F8" s="221"/>
+      <c r="G8" s="285" t="s">
         <v>1073</v>
       </c>
-      <c r="H8" s="258"/>
-      <c r="I8" s="259"/>
+      <c r="H8" s="286"/>
+      <c r="I8" s="287"/>
       <c r="J8" s="128" t="s">
         <v>15</v>
       </c>
@@ -34168,17 +34445,17 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="201"/>
-      <c r="B9" s="201"/>
-      <c r="C9" s="201"/>
-      <c r="D9" s="201"/>
-      <c r="E9" s="201"/>
-      <c r="F9" s="201"/>
-      <c r="G9" s="201"/>
-      <c r="H9" s="201"/>
-      <c r="I9" s="201"/>
-      <c r="J9" s="201"/>
-      <c r="K9" s="201"/>
+      <c r="A9" s="257"/>
+      <c r="B9" s="257"/>
+      <c r="C9" s="257"/>
+      <c r="D9" s="257"/>
+      <c r="E9" s="257"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="257"/>
+      <c r="H9" s="257"/>
+      <c r="I9" s="257"/>
+      <c r="J9" s="257"/>
+      <c r="K9" s="257"/>
     </row>
     <row r="10" spans="1:11" s="120" customFormat="1" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="122" t="s">
@@ -34190,7 +34467,7 @@
       <c r="C10" s="130" t="s">
         <v>1074</v>
       </c>
-      <c r="D10" s="262"/>
+      <c r="D10" s="280"/>
       <c r="E10" s="123" t="s">
         <v>829</v>
       </c>
@@ -34200,10 +34477,10 @@
       <c r="G10" s="130" t="s">
         <v>1074</v>
       </c>
-      <c r="H10" s="222"/>
-      <c r="I10" s="222"/>
-      <c r="J10" s="222"/>
-      <c r="K10" s="222"/>
+      <c r="H10" s="246"/>
+      <c r="I10" s="246"/>
+      <c r="J10" s="246"/>
+      <c r="K10" s="246"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="124">
@@ -34215,7 +34492,7 @@
       <c r="C11" s="125">
         <v>3.24</v>
       </c>
-      <c r="D11" s="262"/>
+      <c r="D11" s="280"/>
       <c r="E11" s="121">
         <v>28</v>
       </c>
@@ -34225,10 +34502,10 @@
       <c r="G11" s="125">
         <v>19.399999999999999</v>
       </c>
-      <c r="H11" s="222"/>
-      <c r="I11" s="222"/>
-      <c r="J11" s="222"/>
-      <c r="K11" s="222"/>
+      <c r="H11" s="246"/>
+      <c r="I11" s="246"/>
+      <c r="J11" s="246"/>
+      <c r="K11" s="246"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="124">
@@ -34240,7 +34517,7 @@
       <c r="C12" s="125">
         <v>34.08</v>
       </c>
-      <c r="D12" s="262"/>
+      <c r="D12" s="280"/>
       <c r="E12" s="121">
         <v>29</v>
       </c>
@@ -34250,10 +34527,10 @@
       <c r="G12" s="125">
         <v>19.399999999999999</v>
       </c>
-      <c r="H12" s="222"/>
-      <c r="I12" s="222"/>
-      <c r="J12" s="222"/>
-      <c r="K12" s="222"/>
+      <c r="H12" s="246"/>
+      <c r="I12" s="246"/>
+      <c r="J12" s="246"/>
+      <c r="K12" s="246"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="124">
@@ -34265,7 +34542,7 @@
       <c r="C13" s="125">
         <v>7.68</v>
       </c>
-      <c r="D13" s="262"/>
+      <c r="D13" s="280"/>
       <c r="E13" s="121">
         <v>30</v>
       </c>
@@ -34275,10 +34552,10 @@
       <c r="G13" s="125">
         <v>48.199999999999996</v>
       </c>
-      <c r="H13" s="222"/>
-      <c r="I13" s="222"/>
-      <c r="J13" s="222"/>
-      <c r="K13" s="222"/>
+      <c r="H13" s="246"/>
+      <c r="I13" s="246"/>
+      <c r="J13" s="246"/>
+      <c r="K13" s="246"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="124">
@@ -34290,7 +34567,7 @@
       <c r="C14" s="125">
         <v>17.16</v>
       </c>
-      <c r="D14" s="262"/>
+      <c r="D14" s="280"/>
       <c r="E14" s="121">
         <v>31</v>
       </c>
@@ -34300,10 +34577,10 @@
       <c r="G14" s="125">
         <v>35</v>
       </c>
-      <c r="H14" s="222"/>
-      <c r="I14" s="222"/>
-      <c r="J14" s="222"/>
-      <c r="K14" s="222"/>
+      <c r="H14" s="246"/>
+      <c r="I14" s="246"/>
+      <c r="J14" s="246"/>
+      <c r="K14" s="246"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="124">
@@ -34315,7 +34592,7 @@
       <c r="C15" s="125">
         <v>32.4</v>
       </c>
-      <c r="D15" s="262"/>
+      <c r="D15" s="280"/>
       <c r="E15" s="121">
         <v>32</v>
       </c>
@@ -34325,10 +34602,10 @@
       <c r="G15" s="125">
         <v>18.2</v>
       </c>
-      <c r="H15" s="222"/>
-      <c r="I15" s="222"/>
-      <c r="J15" s="222"/>
-      <c r="K15" s="222"/>
+      <c r="H15" s="246"/>
+      <c r="I15" s="246"/>
+      <c r="J15" s="246"/>
+      <c r="K15" s="246"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="124">
@@ -34340,7 +34617,7 @@
       <c r="C16" s="125">
         <v>19.2</v>
       </c>
-      <c r="D16" s="262"/>
+      <c r="D16" s="280"/>
       <c r="E16" s="121">
         <v>33</v>
       </c>
@@ -34350,10 +34627,10 @@
       <c r="G16" s="125">
         <v>9.1999999999999993</v>
       </c>
-      <c r="H16" s="222"/>
-      <c r="I16" s="222"/>
-      <c r="J16" s="222"/>
-      <c r="K16" s="222"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="124">
@@ -34365,7 +34642,7 @@
       <c r="C17" s="125">
         <v>32.4</v>
       </c>
-      <c r="D17" s="262"/>
+      <c r="D17" s="280"/>
       <c r="E17" s="121">
         <v>34</v>
       </c>
@@ -34375,10 +34652,10 @@
       <c r="G17" s="125">
         <v>21.8</v>
       </c>
-      <c r="H17" s="222"/>
-      <c r="I17" s="222"/>
-      <c r="J17" s="222"/>
-      <c r="K17" s="222"/>
+      <c r="H17" s="246"/>
+      <c r="I17" s="246"/>
+      <c r="J17" s="246"/>
+      <c r="K17" s="246"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="124">
@@ -34390,7 +34667,7 @@
       <c r="C18" s="125">
         <v>49.199999999999996</v>
       </c>
-      <c r="D18" s="262"/>
+      <c r="D18" s="280"/>
       <c r="E18" s="121">
         <v>35</v>
       </c>
@@ -34400,10 +34677,10 @@
       <c r="G18" s="125">
         <v>24.2</v>
       </c>
-      <c r="H18" s="222"/>
-      <c r="I18" s="222"/>
-      <c r="J18" s="222"/>
-      <c r="K18" s="222"/>
+      <c r="H18" s="246"/>
+      <c r="I18" s="246"/>
+      <c r="J18" s="246"/>
+      <c r="K18" s="246"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="124">
@@ -34415,7 +34692,7 @@
       <c r="C19" s="125">
         <v>15.6</v>
       </c>
-      <c r="D19" s="262"/>
+      <c r="D19" s="280"/>
       <c r="E19" s="121">
         <v>36</v>
       </c>
@@ -34425,10 +34702,10 @@
       <c r="G19" s="125">
         <v>42.199999999999996</v>
       </c>
-      <c r="H19" s="222"/>
-      <c r="I19" s="222"/>
-      <c r="J19" s="222"/>
-      <c r="K19" s="222"/>
+      <c r="H19" s="246"/>
+      <c r="I19" s="246"/>
+      <c r="J19" s="246"/>
+      <c r="K19" s="246"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="124">
@@ -34440,7 +34717,7 @@
       <c r="C20" s="125">
         <v>21.599999999999998</v>
       </c>
-      <c r="D20" s="262"/>
+      <c r="D20" s="280"/>
       <c r="E20" s="121">
         <v>37</v>
       </c>
@@ -34450,10 +34727,10 @@
       <c r="G20" s="125">
         <v>1.7599999999999998</v>
       </c>
-      <c r="H20" s="222"/>
-      <c r="I20" s="222"/>
-      <c r="J20" s="222"/>
-      <c r="K20" s="222"/>
+      <c r="H20" s="246"/>
+      <c r="I20" s="246"/>
+      <c r="J20" s="246"/>
+      <c r="K20" s="246"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="124">
@@ -34465,7 +34742,7 @@
       <c r="C21" s="125">
         <v>8.4</v>
       </c>
-      <c r="D21" s="262"/>
+      <c r="D21" s="280"/>
       <c r="E21" s="121">
         <v>38</v>
       </c>
@@ -34475,10 +34752,10 @@
       <c r="G21" s="125">
         <v>29</v>
       </c>
-      <c r="H21" s="222"/>
-      <c r="I21" s="222"/>
-      <c r="J21" s="222"/>
-      <c r="K21" s="222"/>
+      <c r="H21" s="246"/>
+      <c r="I21" s="246"/>
+      <c r="J21" s="246"/>
+      <c r="K21" s="246"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="124">
@@ -34490,7 +34767,7 @@
       <c r="C22" s="125">
         <v>4.8</v>
       </c>
-      <c r="D22" s="262"/>
+      <c r="D22" s="280"/>
       <c r="E22" s="121">
         <v>39</v>
       </c>
@@ -34500,10 +34777,10 @@
       <c r="G22" s="125">
         <v>23</v>
       </c>
-      <c r="H22" s="222"/>
-      <c r="I22" s="222"/>
-      <c r="J22" s="222"/>
-      <c r="K22" s="222"/>
+      <c r="H22" s="246"/>
+      <c r="I22" s="246"/>
+      <c r="J22" s="246"/>
+      <c r="K22" s="246"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="124">
@@ -34515,7 +34792,7 @@
       <c r="C23" s="125">
         <v>20.04</v>
       </c>
-      <c r="D23" s="262"/>
+      <c r="D23" s="280"/>
       <c r="E23" s="121">
         <v>40</v>
       </c>
@@ -34525,10 +34802,10 @@
       <c r="G23" s="125">
         <v>14.839999999999998</v>
       </c>
-      <c r="H23" s="222"/>
-      <c r="I23" s="222"/>
-      <c r="J23" s="222"/>
-      <c r="K23" s="222"/>
+      <c r="H23" s="246"/>
+      <c r="I23" s="246"/>
+      <c r="J23" s="246"/>
+      <c r="K23" s="246"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="124">
@@ -34540,7 +34817,7 @@
       <c r="C24" s="125">
         <v>19.2</v>
       </c>
-      <c r="D24" s="262"/>
+      <c r="D24" s="280"/>
       <c r="E24" s="121">
         <v>41</v>
       </c>
@@ -34550,10 +34827,10 @@
       <c r="G24" s="125">
         <v>2.5999999999999996</v>
       </c>
-      <c r="H24" s="222"/>
-      <c r="I24" s="222"/>
-      <c r="J24" s="222"/>
-      <c r="K24" s="222"/>
+      <c r="H24" s="246"/>
+      <c r="I24" s="246"/>
+      <c r="J24" s="246"/>
+      <c r="K24" s="246"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="124">
@@ -34565,7 +34842,7 @@
       <c r="C25" s="125">
         <v>42</v>
       </c>
-      <c r="D25" s="262"/>
+      <c r="D25" s="280"/>
       <c r="E25" s="121">
         <v>42</v>
       </c>
@@ -34575,10 +34852,10 @@
       <c r="G25" s="125">
         <v>27.4</v>
       </c>
-      <c r="H25" s="222"/>
-      <c r="I25" s="222"/>
-      <c r="J25" s="222"/>
-      <c r="K25" s="222"/>
+      <c r="H25" s="246"/>
+      <c r="I25" s="246"/>
+      <c r="J25" s="246"/>
+      <c r="K25" s="246"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="124">
@@ -34590,7 +34867,7 @@
       <c r="C26" s="125">
         <v>27.599999999999998</v>
       </c>
-      <c r="D26" s="262"/>
+      <c r="D26" s="280"/>
       <c r="E26" s="121">
         <v>43</v>
       </c>
@@ -34600,10 +34877,10 @@
       <c r="G26" s="125">
         <v>19.399999999999999</v>
       </c>
-      <c r="H26" s="222"/>
-      <c r="I26" s="222"/>
-      <c r="J26" s="222"/>
-      <c r="K26" s="222"/>
+      <c r="H26" s="246"/>
+      <c r="I26" s="246"/>
+      <c r="J26" s="246"/>
+      <c r="K26" s="246"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="124">
@@ -34615,7 +34892,7 @@
       <c r="C27" s="125">
         <v>26.4</v>
       </c>
-      <c r="D27" s="262"/>
+      <c r="D27" s="280"/>
       <c r="E27" s="121">
         <v>44</v>
       </c>
@@ -34625,10 +34902,10 @@
       <c r="G27" s="126">
         <v>4.5</v>
       </c>
-      <c r="H27" s="222"/>
-      <c r="I27" s="222"/>
-      <c r="J27" s="222"/>
-      <c r="K27" s="222"/>
+      <c r="H27" s="246"/>
+      <c r="I27" s="246"/>
+      <c r="J27" s="246"/>
+      <c r="K27" s="246"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="124">
@@ -34640,7 +34917,7 @@
       <c r="C28" s="125">
         <v>16.8</v>
       </c>
-      <c r="D28" s="262"/>
+      <c r="D28" s="280"/>
       <c r="E28" s="121">
         <v>45</v>
       </c>
@@ -34650,10 +34927,10 @@
       <c r="G28" s="125">
         <v>6.4399999999999995</v>
       </c>
-      <c r="H28" s="222"/>
-      <c r="I28" s="222"/>
-      <c r="J28" s="222"/>
-      <c r="K28" s="222"/>
+      <c r="H28" s="246"/>
+      <c r="I28" s="246"/>
+      <c r="J28" s="246"/>
+      <c r="K28" s="246"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="124">
@@ -34665,7 +34942,7 @@
       <c r="C29" s="125">
         <v>8.4</v>
       </c>
-      <c r="D29" s="262"/>
+      <c r="D29" s="280"/>
       <c r="E29" s="121">
         <v>46</v>
       </c>
@@ -34675,10 +34952,10 @@
       <c r="G29" s="125">
         <v>30.2</v>
       </c>
-      <c r="H29" s="222"/>
-      <c r="I29" s="222"/>
-      <c r="J29" s="222"/>
-      <c r="K29" s="222"/>
+      <c r="H29" s="246"/>
+      <c r="I29" s="246"/>
+      <c r="J29" s="246"/>
+      <c r="K29" s="246"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="124">
@@ -34690,7 +34967,7 @@
       <c r="C30" s="125">
         <v>108</v>
       </c>
-      <c r="D30" s="262"/>
+      <c r="D30" s="280"/>
       <c r="E30" s="121">
         <v>47</v>
       </c>
@@ -34700,10 +34977,10 @@
       <c r="G30" s="125">
         <v>23.24</v>
       </c>
-      <c r="H30" s="222"/>
-      <c r="I30" s="222"/>
-      <c r="J30" s="222"/>
-      <c r="K30" s="222"/>
+      <c r="H30" s="246"/>
+      <c r="I30" s="246"/>
+      <c r="J30" s="246"/>
+      <c r="K30" s="246"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="124">
@@ -34715,7 +34992,7 @@
       <c r="C31" s="125">
         <v>12.360000000000001</v>
       </c>
-      <c r="D31" s="262"/>
+      <c r="D31" s="280"/>
       <c r="E31" s="121">
         <v>48</v>
       </c>
@@ -34725,10 +35002,10 @@
       <c r="G31" s="125">
         <v>5.24</v>
       </c>
-      <c r="H31" s="222"/>
-      <c r="I31" s="222"/>
-      <c r="J31" s="222"/>
-      <c r="K31" s="222"/>
+      <c r="H31" s="246"/>
+      <c r="I31" s="246"/>
+      <c r="J31" s="246"/>
+      <c r="K31" s="246"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="124">
@@ -34740,7 +35017,7 @@
       <c r="C32" s="125">
         <v>7.68</v>
       </c>
-      <c r="D32" s="262"/>
+      <c r="D32" s="280"/>
       <c r="E32" s="121">
         <v>49</v>
       </c>
@@ -34750,10 +35027,10 @@
       <c r="G32" s="125">
         <v>9.7999999999999989</v>
       </c>
-      <c r="H32" s="222"/>
-      <c r="I32" s="222"/>
-      <c r="J32" s="222"/>
-      <c r="K32" s="222"/>
+      <c r="H32" s="246"/>
+      <c r="I32" s="246"/>
+      <c r="J32" s="246"/>
+      <c r="K32" s="246"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="124">
@@ -34765,7 +35042,7 @@
       <c r="C33" s="125">
         <v>36</v>
       </c>
-      <c r="D33" s="262"/>
+      <c r="D33" s="280"/>
       <c r="E33" s="121">
         <v>50</v>
       </c>
@@ -34775,10 +35052,10 @@
       <c r="G33" s="125">
         <v>9.7999999999999989</v>
       </c>
-      <c r="H33" s="222"/>
-      <c r="I33" s="222"/>
-      <c r="J33" s="222"/>
-      <c r="K33" s="222"/>
+      <c r="H33" s="246"/>
+      <c r="I33" s="246"/>
+      <c r="J33" s="246"/>
+      <c r="K33" s="246"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="138"/>
@@ -34787,7 +35064,7 @@
         <f>SUM(C11:C33)</f>
         <v>570.24</v>
       </c>
-      <c r="D34" s="262"/>
+      <c r="D34" s="280"/>
       <c r="E34" s="121">
         <v>51</v>
       </c>
@@ -34797,16 +35074,16 @@
       <c r="G34" s="125">
         <v>20.599999999999998</v>
       </c>
-      <c r="H34" s="222"/>
-      <c r="I34" s="222"/>
-      <c r="J34" s="222"/>
-      <c r="K34" s="222"/>
+      <c r="H34" s="246"/>
+      <c r="I34" s="246"/>
+      <c r="J34" s="246"/>
+      <c r="K34" s="246"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A35" s="263"/>
-      <c r="B35" s="263"/>
-      <c r="C35" s="263"/>
-      <c r="D35" s="262"/>
+      <c r="A35" s="281"/>
+      <c r="B35" s="281"/>
+      <c r="C35" s="281"/>
+      <c r="D35" s="280"/>
       <c r="E35" s="121">
         <v>52</v>
       </c>
@@ -34816,16 +35093,16 @@
       <c r="G35" s="125">
         <v>8.6</v>
       </c>
-      <c r="H35" s="222"/>
-      <c r="I35" s="222"/>
-      <c r="J35" s="222"/>
-      <c r="K35" s="222"/>
+      <c r="H35" s="246"/>
+      <c r="I35" s="246"/>
+      <c r="J35" s="246"/>
+      <c r="K35" s="246"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A36" s="263"/>
-      <c r="B36" s="263"/>
-      <c r="C36" s="263"/>
-      <c r="D36" s="262"/>
+      <c r="A36" s="281"/>
+      <c r="B36" s="281"/>
+      <c r="C36" s="281"/>
+      <c r="D36" s="280"/>
       <c r="E36" s="121">
         <v>54</v>
       </c>
@@ -34835,16 +35112,16 @@
       <c r="G36" s="125">
         <v>9.7999999999999989</v>
       </c>
-      <c r="H36" s="222"/>
-      <c r="I36" s="222"/>
-      <c r="J36" s="222"/>
-      <c r="K36" s="222"/>
+      <c r="H36" s="246"/>
+      <c r="I36" s="246"/>
+      <c r="J36" s="246"/>
+      <c r="K36" s="246"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A37" s="263"/>
-      <c r="B37" s="263"/>
-      <c r="C37" s="263"/>
-      <c r="D37" s="262"/>
+      <c r="A37" s="281"/>
+      <c r="B37" s="281"/>
+      <c r="C37" s="281"/>
+      <c r="D37" s="280"/>
       <c r="E37" s="121">
         <v>55</v>
       </c>
@@ -34854,59 +35131,47 @@
       <c r="G37" s="125">
         <v>7.6400000000000006</v>
       </c>
-      <c r="H37" s="222"/>
-      <c r="I37" s="222"/>
-      <c r="J37" s="222"/>
-      <c r="K37" s="222"/>
+      <c r="H37" s="246"/>
+      <c r="I37" s="246"/>
+      <c r="J37" s="246"/>
+      <c r="K37" s="246"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="260"/>
-      <c r="B38" s="260"/>
-      <c r="C38" s="260"/>
-      <c r="D38" s="260"/>
-      <c r="E38" s="260"/>
-      <c r="F38" s="261"/>
+      <c r="A38" s="278"/>
+      <c r="B38" s="278"/>
+      <c r="C38" s="278"/>
+      <c r="D38" s="278"/>
+      <c r="E38" s="278"/>
+      <c r="F38" s="279"/>
       <c r="G38" s="125">
         <f>SUM(G11:G37)</f>
         <v>491.46</v>
       </c>
-      <c r="H38" s="222"/>
-      <c r="I38" s="222"/>
-      <c r="J38" s="222"/>
-      <c r="K38" s="222"/>
+      <c r="H38" s="246"/>
+      <c r="I38" s="246"/>
+      <c r="J38" s="246"/>
+      <c r="K38" s="246"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="264" t="s">
+      <c r="A39" s="209" t="s">
         <v>1080</v>
       </c>
-      <c r="B39" s="264"/>
-      <c r="C39" s="264"/>
+      <c r="B39" s="209"/>
+      <c r="C39" s="209"/>
       <c r="D39" s="139">
         <f>C34+G38</f>
         <v>1061.7</v>
       </c>
-      <c r="E39" s="194"/>
-      <c r="F39" s="222"/>
-      <c r="G39" s="222"/>
-      <c r="H39" s="222"/>
-      <c r="I39" s="222"/>
-      <c r="J39" s="222"/>
-      <c r="K39" s="222"/>
+      <c r="E39" s="256"/>
+      <c r="F39" s="246"/>
+      <c r="G39" s="246"/>
+      <c r="H39" s="246"/>
+      <c r="I39" s="246"/>
+      <c r="J39" s="246"/>
+      <c r="K39" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="H10:K39"/>
-    <mergeCell ref="A9:K9"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="D10:D37"/>
-    <mergeCell ref="A35:C37"/>
-    <mergeCell ref="E39:G39"/>
-    <mergeCell ref="A39:C39"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C6:F6"/>
     <mergeCell ref="C8:F8"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -34917,6 +35182,18 @@
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="G7:I7"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="H10:K39"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="D10:D37"/>
+    <mergeCell ref="A35:C37"/>
+    <mergeCell ref="E39:G39"/>
+    <mergeCell ref="A39:C39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -34942,17 +35219,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -34960,18 +35237,18 @@
       <c r="A2" s="36" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="271" t="s">
+      <c r="B2" s="294" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
-      <c r="F2" s="272"/>
-      <c r="G2" s="273"/>
-      <c r="H2" s="274" t="s">
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="295"/>
+      <c r="F2" s="295"/>
+      <c r="G2" s="296"/>
+      <c r="H2" s="297" t="s">
         <v>814</v>
       </c>
-      <c r="I2" s="275"/>
+      <c r="I2" s="298"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -34983,16 +35260,16 @@
       <c r="A3" s="107">
         <v>1</v>
       </c>
-      <c r="B3" s="266"/>
-      <c r="C3" s="267"/>
-      <c r="D3" s="267"/>
-      <c r="E3" s="267"/>
-      <c r="F3" s="267"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="B3" s="289"/>
+      <c r="C3" s="290"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
+      <c r="F3" s="290"/>
+      <c r="G3" s="291"/>
+      <c r="H3" s="292" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="270"/>
+      <c r="I3" s="293"/>
       <c r="J3" s="107" t="s">
         <v>15</v>
       </c>
@@ -35002,35 +35279,35 @@
       <c r="A4" s="107">
         <v>2</v>
       </c>
-      <c r="B4" s="266">
+      <c r="B4" s="289">
         <v>2</v>
       </c>
-      <c r="C4" s="267"/>
-      <c r="D4" s="267"/>
-      <c r="E4" s="267"/>
-      <c r="F4" s="267"/>
-      <c r="G4" s="268"/>
-      <c r="H4" s="269" t="s">
+      <c r="C4" s="290"/>
+      <c r="D4" s="290"/>
+      <c r="E4" s="290"/>
+      <c r="F4" s="290"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="292" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="270"/>
+      <c r="I4" s="293"/>
       <c r="J4" s="107" t="s">
         <v>15</v>
       </c>
       <c r="K4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="265"/>
-      <c r="B5" s="265"/>
-      <c r="C5" s="265"/>
-      <c r="D5" s="265"/>
-      <c r="E5" s="265"/>
-      <c r="F5" s="265"/>
-      <c r="G5" s="265"/>
-      <c r="H5" s="265"/>
-      <c r="I5" s="265"/>
-      <c r="J5" s="265"/>
-      <c r="K5" s="265"/>
+      <c r="A5" s="288"/>
+      <c r="B5" s="288"/>
+      <c r="C5" s="288"/>
+      <c r="D5" s="288"/>
+      <c r="E5" s="288"/>
+      <c r="F5" s="288"/>
+      <c r="G5" s="288"/>
+      <c r="H5" s="288"/>
+      <c r="I5" s="288"/>
+      <c r="J5" s="288"/>
+      <c r="K5" s="288"/>
     </row>
     <row r="6" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A6" s="41" t="s">
@@ -35567,30 +35844,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="277" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="277"/>
-      <c r="J1" s="277"/>
+      <c r="A1" s="307" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="307"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="307"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="307"/>
+      <c r="G1" s="307"/>
+      <c r="H1" s="307"/>
+      <c r="I1" s="307"/>
+      <c r="J1" s="307"/>
     </row>
     <row r="2" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="299" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="276"/>
-      <c r="D2" s="276"/>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
+      <c r="C2" s="299"/>
+      <c r="D2" s="299"/>
+      <c r="E2" s="299"/>
+      <c r="F2" s="299"/>
       <c r="G2" s="79" t="s">
         <v>814</v>
       </c>
@@ -35606,13 +35883,13 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="299" t="s">
         <v>254</v>
       </c>
-      <c r="C3" s="276"/>
-      <c r="D3" s="276"/>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="299"/>
       <c r="G3" s="88" t="s">
         <v>418</v>
       </c>
@@ -35631,13 +35908,13 @@
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="276" t="s">
+      <c r="B4" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="276"/>
-      <c r="D4" s="276"/>
-      <c r="E4" s="276"/>
-      <c r="F4" s="276"/>
+      <c r="C4" s="299"/>
+      <c r="D4" s="299"/>
+      <c r="E4" s="299"/>
+      <c r="F4" s="299"/>
       <c r="G4" s="100" t="s">
         <v>531</v>
       </c>
@@ -35654,13 +35931,13 @@
       <c r="A5" s="79">
         <v>3</v>
       </c>
-      <c r="B5" s="276" t="s">
+      <c r="B5" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="276"/>
-      <c r="D5" s="276"/>
-      <c r="E5" s="276"/>
-      <c r="F5" s="276"/>
+      <c r="C5" s="299"/>
+      <c r="D5" s="299"/>
+      <c r="E5" s="299"/>
+      <c r="F5" s="299"/>
       <c r="G5" s="88" t="s">
         <v>539</v>
       </c>
@@ -35677,13 +35954,13 @@
       <c r="A6" s="79">
         <v>4</v>
       </c>
-      <c r="B6" s="276" t="s">
+      <c r="B6" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="276"/>
-      <c r="D6" s="276"/>
-      <c r="E6" s="276"/>
-      <c r="F6" s="276"/>
+      <c r="C6" s="299"/>
+      <c r="D6" s="299"/>
+      <c r="E6" s="299"/>
+      <c r="F6" s="299"/>
       <c r="G6" s="100" t="s">
         <v>546</v>
       </c>
@@ -35700,13 +35977,13 @@
       <c r="A7" s="79">
         <v>5</v>
       </c>
-      <c r="B7" s="276" t="s">
+      <c r="B7" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="276"/>
-      <c r="D7" s="276"/>
-      <c r="E7" s="276"/>
-      <c r="F7" s="276"/>
+      <c r="C7" s="299"/>
+      <c r="D7" s="299"/>
+      <c r="E7" s="299"/>
+      <c r="F7" s="299"/>
       <c r="G7" s="88" t="s">
         <v>553</v>
       </c>
@@ -35723,13 +36000,13 @@
       <c r="A8" s="79">
         <v>6</v>
       </c>
-      <c r="B8" s="276" t="s">
+      <c r="B8" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C8" s="276"/>
-      <c r="D8" s="276"/>
-      <c r="E8" s="276"/>
-      <c r="F8" s="276"/>
+      <c r="C8" s="299"/>
+      <c r="D8" s="299"/>
+      <c r="E8" s="299"/>
+      <c r="F8" s="299"/>
       <c r="G8" s="100" t="s">
         <v>560</v>
       </c>
@@ -35746,12 +36023,12 @@
       <c r="A9" s="79">
         <v>7</v>
       </c>
-      <c r="B9" s="278" t="s">
+      <c r="B9" s="300" t="s">
         <v>1060</v>
       </c>
-      <c r="C9" s="279"/>
-      <c r="D9" s="279"/>
-      <c r="E9" s="280"/>
+      <c r="C9" s="301"/>
+      <c r="D9" s="301"/>
+      <c r="E9" s="302"/>
       <c r="F9" s="79" t="s">
         <v>1058</v>
       </c>
@@ -35770,16 +36047,16 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="281"/>
-      <c r="B10" s="281"/>
-      <c r="C10" s="281"/>
-      <c r="D10" s="281"/>
-      <c r="E10" s="281"/>
-      <c r="F10" s="281"/>
-      <c r="G10" s="281"/>
-      <c r="H10" s="281"/>
-      <c r="I10" s="281"/>
-      <c r="J10" s="282"/>
+      <c r="A10" s="303"/>
+      <c r="B10" s="303"/>
+      <c r="C10" s="303"/>
+      <c r="D10" s="303"/>
+      <c r="E10" s="303"/>
+      <c r="F10" s="303"/>
+      <c r="G10" s="303"/>
+      <c r="H10" s="303"/>
+      <c r="I10" s="303"/>
+      <c r="J10" s="304"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="83" t="s">
@@ -35794,7 +36071,7 @@
       <c r="D11" s="86" t="s">
         <v>830</v>
       </c>
-      <c r="E11" s="284"/>
+      <c r="E11" s="306"/>
       <c r="F11" s="79" t="s">
         <v>1054</v>
       </c>
@@ -35807,7 +36084,7 @@
       <c r="I11" s="79" t="s">
         <v>830</v>
       </c>
-      <c r="J11" s="283"/>
+      <c r="J11" s="305"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="92">
@@ -35822,7 +36099,7 @@
       <c r="D12" s="95">
         <v>11.7</v>
       </c>
-      <c r="E12" s="284"/>
+      <c r="E12" s="306"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -35835,7 +36112,7 @@
       <c r="I12" s="93">
         <v>33</v>
       </c>
-      <c r="J12" s="283"/>
+      <c r="J12" s="305"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="102">
@@ -35850,7 +36127,7 @@
       <c r="D13" s="101">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E13" s="284"/>
+      <c r="E13" s="306"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -35863,7 +36140,7 @@
       <c r="I13" s="93">
         <v>14.1</v>
       </c>
-      <c r="J13" s="283"/>
+      <c r="J13" s="305"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="92">
@@ -35878,7 +36155,7 @@
       <c r="D14" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E14" s="284"/>
+      <c r="E14" s="306"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -35891,7 +36168,7 @@
       <c r="I14" s="93">
         <v>8.1</v>
       </c>
-      <c r="J14" s="283"/>
+      <c r="J14" s="305"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="102">
@@ -35906,7 +36183,7 @@
       <c r="D15" s="101">
         <v>2.6</v>
       </c>
-      <c r="E15" s="284"/>
+      <c r="E15" s="306"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -35919,7 +36196,7 @@
       <c r="I15" s="93">
         <v>65.8</v>
       </c>
-      <c r="J15" s="283"/>
+      <c r="J15" s="305"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="92">
@@ -35934,7 +36211,7 @@
       <c r="D16" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E16" s="284"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -35947,7 +36224,7 @@
       <c r="I16" s="93">
         <v>2.6</v>
       </c>
-      <c r="J16" s="283"/>
+      <c r="J16" s="305"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="92">
@@ -35962,7 +36239,7 @@
       <c r="D17" s="95">
         <v>11.7</v>
       </c>
-      <c r="E17" s="284"/>
+      <c r="E17" s="306"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -35975,7 +36252,7 @@
       <c r="I17" s="93">
         <v>13.6</v>
       </c>
-      <c r="J17" s="283"/>
+      <c r="J17" s="305"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="102">
@@ -35990,7 +36267,7 @@
       <c r="D18" s="101">
         <v>31.6</v>
       </c>
-      <c r="E18" s="284"/>
+      <c r="E18" s="306"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -36003,7 +36280,7 @@
       <c r="I18" s="93">
         <v>5.8</v>
       </c>
-      <c r="J18" s="283"/>
+      <c r="J18" s="305"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="92">
@@ -36018,7 +36295,7 @@
       <c r="D19" s="95">
         <v>5.9</v>
       </c>
-      <c r="E19" s="284"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -36031,7 +36308,7 @@
       <c r="I19" s="93">
         <v>67.8</v>
       </c>
-      <c r="J19" s="283"/>
+      <c r="J19" s="305"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="92">
@@ -36046,7 +36323,7 @@
       <c r="D20" s="95">
         <v>36.9</v>
       </c>
-      <c r="E20" s="284"/>
+      <c r="E20" s="306"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -36059,7 +36336,7 @@
       <c r="I20" s="93">
         <v>1.8</v>
       </c>
-      <c r="J20" s="283"/>
+      <c r="J20" s="305"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="92">
@@ -36074,7 +36351,7 @@
       <c r="D21" s="95">
         <v>33.9</v>
       </c>
-      <c r="E21" s="284"/>
+      <c r="E21" s="306"/>
       <c r="F21" s="93">
         <v>3</v>
       </c>
@@ -36087,7 +36364,7 @@
       <c r="I21" s="93">
         <v>35.4</v>
       </c>
-      <c r="J21" s="283"/>
+      <c r="J21" s="305"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="92">
@@ -36102,7 +36379,7 @@
       <c r="D22" s="95">
         <v>11.9</v>
       </c>
-      <c r="E22" s="284"/>
+      <c r="E22" s="306"/>
       <c r="F22" s="93">
         <v>3</v>
       </c>
@@ -36115,7 +36392,7 @@
       <c r="I22" s="93">
         <v>5.9</v>
       </c>
-      <c r="J22" s="283"/>
+      <c r="J22" s="305"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="102">
@@ -36130,7 +36407,7 @@
       <c r="D23" s="101">
         <v>5.7</v>
       </c>
-      <c r="E23" s="284"/>
+      <c r="E23" s="306"/>
       <c r="F23" s="93">
         <v>3</v>
       </c>
@@ -36143,7 +36420,7 @@
       <c r="I23" s="93">
         <v>29.5</v>
       </c>
-      <c r="J23" s="283"/>
+      <c r="J23" s="305"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="92">
@@ -36158,7 +36435,7 @@
       <c r="D24" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E24" s="284"/>
+      <c r="E24" s="306"/>
       <c r="F24" s="93">
         <v>3</v>
       </c>
@@ -36171,7 +36448,7 @@
       <c r="I24" s="93">
         <v>36.9</v>
       </c>
-      <c r="J24" s="283"/>
+      <c r="J24" s="305"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="102">
@@ -36186,7 +36463,7 @@
       <c r="D25" s="101">
         <v>1.8</v>
       </c>
-      <c r="E25" s="284"/>
+      <c r="E25" s="306"/>
       <c r="F25" s="93">
         <v>3</v>
       </c>
@@ -36199,7 +36476,7 @@
       <c r="I25" s="93">
         <v>36.5</v>
       </c>
-      <c r="J25" s="283"/>
+      <c r="J25" s="305"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="92">
@@ -36214,7 +36491,7 @@
       <c r="D26" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E26" s="284"/>
+      <c r="E26" s="306"/>
       <c r="F26" s="96">
         <v>3</v>
       </c>
@@ -36227,7 +36504,7 @@
       <c r="I26" s="96">
         <v>29.5</v>
       </c>
-      <c r="J26" s="283"/>
+      <c r="J26" s="305"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="102">
@@ -36242,7 +36519,7 @@
       <c r="D27" s="101">
         <v>44.2</v>
       </c>
-      <c r="E27" s="284"/>
+      <c r="E27" s="306"/>
       <c r="F27" s="98">
         <v>3</v>
       </c>
@@ -36256,22 +36533,22 @@
         <f>1.08*13.5</f>
         <v>14.580000000000002</v>
       </c>
-      <c r="J27" s="283"/>
+      <c r="J27" s="305"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="A10:I10"/>
     <mergeCell ref="J10:J27"/>
     <mergeCell ref="E11:E27"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -36298,29 +36575,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="277" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="277"/>
-      <c r="C1" s="277"/>
-      <c r="D1" s="277"/>
-      <c r="E1" s="277"/>
-      <c r="F1" s="277"/>
-      <c r="G1" s="277"/>
-      <c r="H1" s="277"/>
-      <c r="I1" s="277"/>
+      <c r="A1" s="307" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="307"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="307"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="307"/>
+      <c r="G1" s="307"/>
+      <c r="H1" s="307"/>
+      <c r="I1" s="307"/>
     </row>
     <row r="2" spans="1:9" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" s="79" t="s">
         <v>815</v>
       </c>
-      <c r="B2" s="276" t="s">
+      <c r="B2" s="299" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="276"/>
-      <c r="D2" s="276"/>
-      <c r="E2" s="276"/>
-      <c r="F2" s="276"/>
+      <c r="C2" s="299"/>
+      <c r="D2" s="299"/>
+      <c r="E2" s="299"/>
+      <c r="F2" s="299"/>
       <c r="G2" s="79" t="s">
         <v>814</v>
       </c>
@@ -36335,13 +36612,13 @@
       <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="276" t="s">
+      <c r="B3" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="276"/>
-      <c r="D3" s="276"/>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
+      <c r="C3" s="299"/>
+      <c r="D3" s="299"/>
+      <c r="E3" s="299"/>
+      <c r="F3" s="299"/>
       <c r="G3" s="90" t="s">
         <v>531</v>
       </c>
@@ -36357,13 +36634,13 @@
       <c r="A4" s="79">
         <v>2</v>
       </c>
-      <c r="B4" s="276" t="s">
+      <c r="B4" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C4" s="276"/>
-      <c r="D4" s="276"/>
-      <c r="E4" s="276"/>
-      <c r="F4" s="276"/>
+      <c r="C4" s="299"/>
+      <c r="D4" s="299"/>
+      <c r="E4" s="299"/>
+      <c r="F4" s="299"/>
       <c r="G4" s="88" t="s">
         <v>539</v>
       </c>
@@ -36379,13 +36656,13 @@
       <c r="A5" s="79">
         <v>3</v>
       </c>
-      <c r="B5" s="276" t="s">
+      <c r="B5" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C5" s="276"/>
-      <c r="D5" s="276"/>
-      <c r="E5" s="276"/>
-      <c r="F5" s="276"/>
+      <c r="C5" s="299"/>
+      <c r="D5" s="299"/>
+      <c r="E5" s="299"/>
+      <c r="F5" s="299"/>
       <c r="G5" s="90" t="s">
         <v>546</v>
       </c>
@@ -36401,13 +36678,13 @@
       <c r="A6" s="79">
         <v>4</v>
       </c>
-      <c r="B6" s="276" t="s">
+      <c r="B6" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C6" s="276"/>
-      <c r="D6" s="276"/>
-      <c r="E6" s="276"/>
-      <c r="F6" s="276"/>
+      <c r="C6" s="299"/>
+      <c r="D6" s="299"/>
+      <c r="E6" s="299"/>
+      <c r="F6" s="299"/>
       <c r="G6" s="88" t="s">
         <v>553</v>
       </c>
@@ -36423,13 +36700,13 @@
       <c r="A7" s="79">
         <v>5</v>
       </c>
-      <c r="B7" s="276" t="s">
+      <c r="B7" s="299" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="276"/>
-      <c r="D7" s="276"/>
-      <c r="E7" s="276"/>
-      <c r="F7" s="276"/>
+      <c r="C7" s="299"/>
+      <c r="D7" s="299"/>
+      <c r="E7" s="299"/>
+      <c r="F7" s="299"/>
       <c r="G7" s="90" t="s">
         <v>560</v>
       </c>
@@ -36442,15 +36719,15 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="281"/>
-      <c r="B8" s="281"/>
-      <c r="C8" s="281"/>
-      <c r="D8" s="281"/>
-      <c r="E8" s="281"/>
-      <c r="F8" s="281"/>
-      <c r="G8" s="281"/>
-      <c r="H8" s="281"/>
-      <c r="I8" s="281"/>
+      <c r="A8" s="303"/>
+      <c r="B8" s="303"/>
+      <c r="C8" s="303"/>
+      <c r="D8" s="303"/>
+      <c r="E8" s="303"/>
+      <c r="F8" s="303"/>
+      <c r="G8" s="303"/>
+      <c r="H8" s="303"/>
+      <c r="I8" s="303"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="83" t="s">
@@ -36465,7 +36742,7 @@
       <c r="D9" s="86" t="s">
         <v>830</v>
       </c>
-      <c r="E9" s="284"/>
+      <c r="E9" s="306"/>
       <c r="F9" s="79" t="s">
         <v>1054</v>
       </c>
@@ -36492,7 +36769,7 @@
       <c r="D10" s="82">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E10" s="284"/>
+      <c r="E10" s="306"/>
       <c r="F10" s="93">
         <v>3</v>
       </c>
@@ -36519,7 +36796,7 @@
       <c r="D11" s="95">
         <v>66.400000000000006</v>
       </c>
-      <c r="E11" s="284"/>
+      <c r="E11" s="306"/>
       <c r="F11" s="93">
         <v>3</v>
       </c>
@@ -36546,7 +36823,7 @@
       <c r="D12" s="95">
         <v>33.299999999999997</v>
       </c>
-      <c r="E12" s="284"/>
+      <c r="E12" s="306"/>
       <c r="F12" s="93">
         <v>3</v>
       </c>
@@ -36573,7 +36850,7 @@
       <c r="D13" s="82">
         <v>31.6</v>
       </c>
-      <c r="E13" s="284"/>
+      <c r="E13" s="306"/>
       <c r="F13" s="93">
         <v>3</v>
       </c>
@@ -36600,7 +36877,7 @@
       <c r="D14" s="95">
         <v>5.9</v>
       </c>
-      <c r="E14" s="284"/>
+      <c r="E14" s="306"/>
       <c r="F14" s="93">
         <v>3</v>
       </c>
@@ -36627,7 +36904,7 @@
       <c r="D15" s="95">
         <v>36.9</v>
       </c>
-      <c r="E15" s="284"/>
+      <c r="E15" s="306"/>
       <c r="F15" s="93">
         <v>3</v>
       </c>
@@ -36654,7 +36931,7 @@
       <c r="D16" s="95">
         <v>33.9</v>
       </c>
-      <c r="E16" s="284"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="93">
         <v>3</v>
       </c>
@@ -36681,7 +36958,7 @@
       <c r="D17" s="82">
         <v>5.7</v>
       </c>
-      <c r="E17" s="284"/>
+      <c r="E17" s="306"/>
       <c r="F17" s="93">
         <v>3</v>
       </c>
@@ -36708,7 +36985,7 @@
       <c r="D18" s="95">
         <v>65.099999999999994</v>
       </c>
-      <c r="E18" s="284"/>
+      <c r="E18" s="306"/>
       <c r="F18" s="93">
         <v>3</v>
       </c>
@@ -36735,7 +37012,7 @@
       <c r="D19" s="95">
         <v>38.299999999999997</v>
       </c>
-      <c r="E19" s="284"/>
+      <c r="E19" s="306"/>
       <c r="F19" s="93">
         <v>3</v>
       </c>
@@ -36762,7 +37039,7 @@
       <c r="D20" s="82">
         <v>44.2</v>
       </c>
-      <c r="E20" s="284"/>
+      <c r="E20" s="306"/>
       <c r="F20" s="93">
         <v>3</v>
       </c>
@@ -36864,17 +37141,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
       <c r="J1" s="35"/>
       <c r="K1" s="35"/>
     </row>
@@ -36882,18 +37159,18 @@
       <c r="A2" s="36" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="271" t="s">
+      <c r="B2" s="294" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="272"/>
-      <c r="D2" s="272"/>
-      <c r="E2" s="272"/>
-      <c r="F2" s="272"/>
-      <c r="G2" s="273"/>
-      <c r="H2" s="274" t="s">
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="295"/>
+      <c r="F2" s="295"/>
+      <c r="G2" s="296"/>
+      <c r="H2" s="297" t="s">
         <v>814</v>
       </c>
-      <c r="I2" s="275"/>
+      <c r="I2" s="298"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -36905,33 +37182,33 @@
       <c r="A3" s="39">
         <v>1</v>
       </c>
-      <c r="B3" s="266"/>
-      <c r="C3" s="267"/>
-      <c r="D3" s="267"/>
-      <c r="E3" s="267"/>
-      <c r="F3" s="267"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="269" t="s">
+      <c r="B3" s="289"/>
+      <c r="C3" s="290"/>
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
+      <c r="F3" s="290"/>
+      <c r="G3" s="291"/>
+      <c r="H3" s="292" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="270"/>
+      <c r="I3" s="293"/>
       <c r="J3" s="39" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="40"/>
     </row>
     <row r="4" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="265"/>
-      <c r="B4" s="265"/>
-      <c r="C4" s="265"/>
-      <c r="D4" s="265"/>
-      <c r="E4" s="265"/>
-      <c r="F4" s="265"/>
-      <c r="G4" s="265"/>
-      <c r="H4" s="265"/>
-      <c r="I4" s="265"/>
-      <c r="J4" s="265"/>
-      <c r="K4" s="265"/>
+      <c r="A4" s="288"/>
+      <c r="B4" s="288"/>
+      <c r="C4" s="288"/>
+      <c r="D4" s="288"/>
+      <c r="E4" s="288"/>
+      <c r="F4" s="288"/>
+      <c r="G4" s="288"/>
+      <c r="H4" s="288"/>
+      <c r="I4" s="288"/>
+      <c r="J4" s="288"/>
+      <c r="K4" s="288"/>
     </row>
     <row r="5" spans="1:11" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" s="41" t="s">
@@ -38112,141 +38389,141 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
+      <c r="K1" s="248"/>
+      <c r="L1" s="248"/>
+      <c r="M1" s="248"/>
+      <c r="N1" s="248"/>
+      <c r="O1" s="248"/>
+      <c r="P1" s="248"/>
+      <c r="Q1" s="248"/>
     </row>
     <row r="2" spans="1:17" s="164" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="182" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="220" t="s">
+      <c r="B2" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
       <c r="G2" s="37" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="117" t="s">
         <v>830</v>
       </c>
-      <c r="I2" s="224"/>
-      <c r="J2" s="224"/>
-      <c r="K2" s="224"/>
-      <c r="L2" s="224"/>
-      <c r="M2" s="224"/>
-      <c r="N2" s="224"/>
-      <c r="O2" s="224"/>
-      <c r="P2" s="224"/>
-      <c r="Q2" s="224"/>
+      <c r="I2" s="248"/>
+      <c r="J2" s="248"/>
+      <c r="K2" s="248"/>
+      <c r="L2" s="248"/>
+      <c r="M2" s="248"/>
+      <c r="N2" s="248"/>
+      <c r="O2" s="248"/>
+      <c r="P2" s="248"/>
+      <c r="Q2" s="248"/>
     </row>
     <row r="3" spans="1:17" s="164" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="218" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
+      <c r="B3" s="231" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
       <c r="G3" s="115" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="H3" s="165">
         <f>B39+E19+H41+K39+N39+Q37</f>
         <v>5679</v>
       </c>
-      <c r="I3" s="224"/>
-      <c r="J3" s="224"/>
-      <c r="K3" s="224"/>
-      <c r="L3" s="224"/>
-      <c r="M3" s="224"/>
-      <c r="N3" s="224"/>
-      <c r="O3" s="224"/>
-      <c r="P3" s="224"/>
-      <c r="Q3" s="224"/>
+      <c r="I3" s="248"/>
+      <c r="J3" s="248"/>
+      <c r="K3" s="248"/>
+      <c r="L3" s="248"/>
+      <c r="M3" s="248"/>
+      <c r="N3" s="248"/>
+      <c r="O3" s="248"/>
+      <c r="P3" s="248"/>
+      <c r="Q3" s="248"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="223"/>
-      <c r="B4" s="223"/>
-      <c r="C4" s="223"/>
-      <c r="D4" s="223"/>
-      <c r="E4" s="223"/>
-      <c r="F4" s="223"/>
-      <c r="G4" s="223"/>
-      <c r="H4" s="223"/>
-      <c r="I4" s="223"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="223"/>
-      <c r="L4" s="223"/>
-      <c r="M4" s="223"/>
-      <c r="N4" s="223"/>
-      <c r="O4" s="223"/>
-      <c r="P4" s="223"/>
-      <c r="Q4" s="223"/>
+      <c r="A4" s="247"/>
+      <c r="B4" s="247"/>
+      <c r="C4" s="247"/>
+      <c r="D4" s="247"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="247"/>
+      <c r="I4" s="247"/>
+      <c r="J4" s="247"/>
+      <c r="K4" s="247"/>
+      <c r="L4" s="247"/>
+      <c r="M4" s="247"/>
+      <c r="N4" s="247"/>
+      <c r="O4" s="247"/>
+      <c r="P4" s="247"/>
+      <c r="Q4" s="247"/>
     </row>
     <row r="5" spans="1:17" s="183" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="B5" s="114" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C5" s="221"/>
+        <v>1195</v>
+      </c>
+      <c r="C5" s="245"/>
       <c r="D5" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="E5" s="114" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F5" s="221"/>
+        <v>1195</v>
+      </c>
+      <c r="F5" s="245"/>
       <c r="G5" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="H5" s="114" t="s">
-        <v>1197</v>
-      </c>
-      <c r="I5" s="221"/>
+        <v>1195</v>
+      </c>
+      <c r="I5" s="245"/>
       <c r="J5" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="K5" s="114" t="s">
-        <v>1197</v>
-      </c>
-      <c r="L5" s="221"/>
+        <v>1195</v>
+      </c>
+      <c r="L5" s="245"/>
       <c r="M5" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="N5" s="114" t="s">
-        <v>1197</v>
-      </c>
-      <c r="O5" s="221"/>
+        <v>1195</v>
+      </c>
+      <c r="O5" s="245"/>
       <c r="P5" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="Q5" s="114" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -38256,35 +38533,35 @@
       <c r="B6" s="185">
         <v>7</v>
       </c>
-      <c r="C6" s="221"/>
+      <c r="C6" s="245"/>
       <c r="D6" s="185">
         <v>1112</v>
       </c>
       <c r="E6" s="185">
         <v>8</v>
       </c>
-      <c r="F6" s="221"/>
+      <c r="F6" s="245"/>
       <c r="G6" s="185">
         <v>2001</v>
       </c>
       <c r="H6" s="185">
         <v>22.8</v>
       </c>
-      <c r="I6" s="221"/>
+      <c r="I6" s="245"/>
       <c r="J6" s="185">
         <v>2036</v>
       </c>
       <c r="K6" s="185">
         <v>88.8</v>
       </c>
-      <c r="L6" s="221"/>
+      <c r="L6" s="245"/>
       <c r="M6" s="185">
         <v>3001</v>
       </c>
       <c r="N6" s="185">
         <v>40</v>
       </c>
-      <c r="O6" s="221"/>
+      <c r="O6" s="245"/>
       <c r="P6" s="185">
         <v>3034</v>
       </c>
@@ -38299,35 +38576,35 @@
       <c r="B7" s="185">
         <v>4</v>
       </c>
-      <c r="C7" s="221"/>
+      <c r="C7" s="245"/>
       <c r="D7" s="185">
         <v>1062</v>
       </c>
       <c r="E7" s="185">
         <v>34</v>
       </c>
-      <c r="F7" s="221"/>
+      <c r="F7" s="245"/>
       <c r="G7" s="185">
         <v>2002</v>
       </c>
       <c r="H7" s="185">
         <v>57.599999999999994</v>
       </c>
-      <c r="I7" s="221"/>
+      <c r="I7" s="245"/>
       <c r="J7" s="185">
         <v>2037</v>
       </c>
       <c r="K7" s="185">
         <v>151.19999999999999</v>
       </c>
-      <c r="L7" s="221"/>
+      <c r="L7" s="245"/>
       <c r="M7" s="185">
         <v>3002</v>
       </c>
       <c r="N7" s="185">
         <v>40</v>
       </c>
-      <c r="O7" s="221"/>
+      <c r="O7" s="245"/>
       <c r="P7" s="185">
         <v>3035</v>
       </c>
@@ -38342,35 +38619,35 @@
       <c r="B8" s="185">
         <v>3</v>
       </c>
-      <c r="C8" s="221"/>
+      <c r="C8" s="245"/>
       <c r="D8" s="185">
         <v>1061</v>
       </c>
       <c r="E8" s="185">
         <v>24</v>
       </c>
-      <c r="F8" s="221"/>
+      <c r="F8" s="245"/>
       <c r="G8" s="185">
         <v>2003</v>
       </c>
       <c r="H8" s="185">
         <v>112.8</v>
       </c>
-      <c r="I8" s="221"/>
+      <c r="I8" s="245"/>
       <c r="J8" s="185">
         <v>2038</v>
       </c>
       <c r="K8" s="185">
         <v>57.599999999999994</v>
       </c>
-      <c r="L8" s="221"/>
+      <c r="L8" s="245"/>
       <c r="M8" s="185">
         <v>3003</v>
       </c>
       <c r="N8" s="185">
         <v>36</v>
       </c>
-      <c r="O8" s="221"/>
+      <c r="O8" s="245"/>
       <c r="P8" s="185">
         <v>3036</v>
       </c>
@@ -38385,35 +38662,35 @@
       <c r="B9" s="185">
         <v>20</v>
       </c>
-      <c r="C9" s="221"/>
+      <c r="C9" s="245"/>
       <c r="D9" s="185">
         <v>1067</v>
       </c>
       <c r="E9" s="185">
         <v>15</v>
       </c>
-      <c r="F9" s="221"/>
+      <c r="F9" s="245"/>
       <c r="G9" s="185">
         <v>2004</v>
       </c>
       <c r="H9" s="185">
         <v>45.6</v>
       </c>
-      <c r="I9" s="221"/>
+      <c r="I9" s="245"/>
       <c r="J9" s="185">
         <v>2039</v>
       </c>
       <c r="K9" s="185">
         <v>50.4</v>
       </c>
-      <c r="L9" s="221"/>
+      <c r="L9" s="245"/>
       <c r="M9" s="185">
         <v>3004</v>
       </c>
       <c r="N9" s="185">
         <v>88</v>
       </c>
-      <c r="O9" s="221"/>
+      <c r="O9" s="245"/>
       <c r="P9" s="185">
         <v>3037</v>
       </c>
@@ -38428,35 +38705,35 @@
       <c r="B10" s="185">
         <v>9</v>
       </c>
-      <c r="C10" s="221"/>
+      <c r="C10" s="245"/>
       <c r="D10" s="185">
         <v>1073</v>
       </c>
       <c r="E10" s="185">
         <v>21</v>
       </c>
-      <c r="F10" s="221"/>
+      <c r="F10" s="245"/>
       <c r="G10" s="185">
         <v>2005</v>
       </c>
       <c r="H10" s="185">
         <v>40.799999999999997</v>
       </c>
-      <c r="I10" s="221"/>
+      <c r="I10" s="245"/>
       <c r="J10" s="185">
         <v>2040</v>
       </c>
       <c r="K10" s="185">
         <v>36</v>
       </c>
-      <c r="L10" s="221"/>
+      <c r="L10" s="245"/>
       <c r="M10" s="185">
         <v>3005</v>
       </c>
       <c r="N10" s="185">
         <v>17</v>
       </c>
-      <c r="O10" s="221"/>
+      <c r="O10" s="245"/>
       <c r="P10" s="185">
         <v>3038</v>
       </c>
@@ -38471,35 +38748,35 @@
       <c r="B11" s="185">
         <v>2</v>
       </c>
-      <c r="C11" s="221"/>
+      <c r="C11" s="245"/>
       <c r="D11" s="185">
         <v>1070</v>
       </c>
       <c r="E11" s="185">
         <v>9</v>
       </c>
-      <c r="F11" s="221"/>
+      <c r="F11" s="245"/>
       <c r="G11" s="185">
         <v>2006</v>
       </c>
       <c r="H11" s="185">
         <v>9.6</v>
       </c>
-      <c r="I11" s="221"/>
+      <c r="I11" s="245"/>
       <c r="J11" s="185">
         <v>2041</v>
       </c>
       <c r="K11" s="185">
         <v>48</v>
       </c>
-      <c r="L11" s="221"/>
+      <c r="L11" s="245"/>
       <c r="M11" s="185">
         <v>3006</v>
       </c>
       <c r="N11" s="185">
         <v>39</v>
       </c>
-      <c r="O11" s="221"/>
+      <c r="O11" s="245"/>
       <c r="P11" s="185">
         <v>3039</v>
       </c>
@@ -38514,35 +38791,35 @@
       <c r="B12" s="185">
         <v>7</v>
       </c>
-      <c r="C12" s="221"/>
+      <c r="C12" s="245"/>
       <c r="D12" s="185">
         <v>1079</v>
       </c>
       <c r="E12" s="185">
         <v>8</v>
       </c>
-      <c r="F12" s="221"/>
+      <c r="F12" s="245"/>
       <c r="G12" s="185">
         <v>2007</v>
       </c>
       <c r="H12" s="185">
         <v>14.399999999999999</v>
       </c>
-      <c r="I12" s="221"/>
+      <c r="I12" s="245"/>
       <c r="J12" s="185">
         <v>2042</v>
       </c>
       <c r="K12" s="185">
         <v>69.599999999999994</v>
       </c>
-      <c r="L12" s="221"/>
+      <c r="L12" s="245"/>
       <c r="M12" s="185">
         <v>3007</v>
       </c>
       <c r="N12" s="185">
         <v>34</v>
       </c>
-      <c r="O12" s="221"/>
+      <c r="O12" s="245"/>
       <c r="P12" s="185">
         <v>3040</v>
       </c>
@@ -38557,35 +38834,35 @@
       <c r="B13" s="185">
         <v>6</v>
       </c>
-      <c r="C13" s="221"/>
+      <c r="C13" s="245"/>
       <c r="D13" s="185">
         <v>1084</v>
       </c>
       <c r="E13" s="185">
         <v>5</v>
       </c>
-      <c r="F13" s="221"/>
+      <c r="F13" s="245"/>
       <c r="G13" s="185">
         <v>2008</v>
       </c>
       <c r="H13" s="185">
         <v>9.6</v>
       </c>
-      <c r="I13" s="221"/>
+      <c r="I13" s="245"/>
       <c r="J13" s="185">
         <v>2043</v>
       </c>
       <c r="K13" s="185">
         <v>31.2</v>
       </c>
-      <c r="L13" s="221"/>
+      <c r="L13" s="245"/>
       <c r="M13" s="185">
         <v>3008</v>
       </c>
       <c r="N13" s="185">
         <v>2</v>
       </c>
-      <c r="O13" s="221"/>
+      <c r="O13" s="245"/>
       <c r="P13" s="185">
         <v>3041</v>
       </c>
@@ -38600,35 +38877,35 @@
       <c r="B14" s="185">
         <v>15</v>
       </c>
-      <c r="C14" s="221"/>
+      <c r="C14" s="245"/>
       <c r="D14" s="185">
         <v>1080</v>
       </c>
       <c r="E14" s="185">
         <v>15</v>
       </c>
-      <c r="F14" s="221"/>
+      <c r="F14" s="245"/>
       <c r="G14" s="185">
         <v>2009</v>
       </c>
       <c r="H14" s="185">
         <v>31.2</v>
       </c>
-      <c r="I14" s="221"/>
+      <c r="I14" s="245"/>
       <c r="J14" s="185">
         <v>2044</v>
       </c>
       <c r="K14" s="185">
         <v>0</v>
       </c>
-      <c r="L14" s="221"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="185">
         <v>3009</v>
       </c>
       <c r="N14" s="185">
         <v>5</v>
       </c>
-      <c r="O14" s="221"/>
+      <c r="O14" s="245"/>
       <c r="P14" s="185">
         <v>3042</v>
       </c>
@@ -38643,35 +38920,35 @@
       <c r="B15" s="185">
         <v>19</v>
       </c>
-      <c r="C15" s="221"/>
+      <c r="C15" s="245"/>
       <c r="D15" s="185">
         <v>1068</v>
       </c>
       <c r="E15" s="185">
         <v>14</v>
       </c>
-      <c r="F15" s="221"/>
+      <c r="F15" s="245"/>
       <c r="G15" s="185">
         <v>2010</v>
       </c>
       <c r="H15" s="185">
         <v>6</v>
       </c>
-      <c r="I15" s="221"/>
+      <c r="I15" s="245"/>
       <c r="J15" s="185">
         <v>2045</v>
       </c>
       <c r="K15" s="185">
         <v>112.8</v>
       </c>
-      <c r="L15" s="221"/>
+      <c r="L15" s="245"/>
       <c r="M15" s="185">
         <v>3010</v>
       </c>
       <c r="N15" s="185">
         <v>82</v>
       </c>
-      <c r="O15" s="221"/>
+      <c r="O15" s="245"/>
       <c r="P15" s="185">
         <v>3043</v>
       </c>
@@ -38686,35 +38963,35 @@
       <c r="B16" s="185">
         <v>9</v>
       </c>
-      <c r="C16" s="221"/>
+      <c r="C16" s="245"/>
       <c r="D16" s="185">
         <v>1057</v>
       </c>
       <c r="E16" s="185">
         <v>25</v>
       </c>
-      <c r="F16" s="221"/>
+      <c r="F16" s="245"/>
       <c r="G16" s="185">
         <v>2011</v>
       </c>
       <c r="H16" s="185">
         <v>2.4</v>
       </c>
-      <c r="I16" s="221"/>
+      <c r="I16" s="245"/>
       <c r="J16" s="185">
         <v>2046</v>
       </c>
       <c r="K16" s="185">
         <v>148.79999999999998</v>
       </c>
-      <c r="L16" s="221"/>
+      <c r="L16" s="245"/>
       <c r="M16" s="185">
         <v>3011</v>
       </c>
       <c r="N16" s="185">
         <v>60</v>
       </c>
-      <c r="O16" s="221"/>
+      <c r="O16" s="245"/>
       <c r="P16" s="185">
         <v>3044</v>
       </c>
@@ -38729,35 +39006,35 @@
       <c r="B17" s="185">
         <v>4</v>
       </c>
-      <c r="C17" s="221"/>
+      <c r="C17" s="245"/>
       <c r="D17" s="185">
         <v>1048</v>
       </c>
       <c r="E17" s="185">
         <v>18</v>
       </c>
-      <c r="F17" s="221"/>
+      <c r="F17" s="245"/>
       <c r="G17" s="185">
         <v>2012</v>
       </c>
       <c r="H17" s="185">
         <v>74.399999999999991</v>
       </c>
-      <c r="I17" s="221"/>
+      <c r="I17" s="245"/>
       <c r="J17" s="185">
         <v>2047</v>
       </c>
       <c r="K17" s="185">
         <v>14.399999999999999</v>
       </c>
-      <c r="L17" s="221"/>
+      <c r="L17" s="245"/>
       <c r="M17" s="185">
         <v>3012</v>
       </c>
       <c r="N17" s="185">
         <v>126</v>
       </c>
-      <c r="O17" s="221"/>
+      <c r="O17" s="245"/>
       <c r="P17" s="185">
         <v>3045</v>
       </c>
@@ -38772,35 +39049,35 @@
       <c r="B18" s="185">
         <v>27</v>
       </c>
-      <c r="C18" s="221"/>
+      <c r="C18" s="245"/>
       <c r="D18" s="185">
         <v>1045</v>
       </c>
       <c r="E18" s="185">
         <v>23</v>
       </c>
-      <c r="F18" s="221"/>
+      <c r="F18" s="245"/>
       <c r="G18" s="185">
         <v>2013</v>
       </c>
       <c r="H18" s="185">
         <v>52.8</v>
       </c>
-      <c r="I18" s="221"/>
+      <c r="I18" s="245"/>
       <c r="J18" s="185">
         <v>2048</v>
       </c>
       <c r="K18" s="185">
         <v>45.6</v>
       </c>
-      <c r="L18" s="221"/>
+      <c r="L18" s="245"/>
       <c r="M18" s="185">
         <v>3013</v>
       </c>
       <c r="N18" s="185">
         <v>40</v>
       </c>
-      <c r="O18" s="221"/>
+      <c r="O18" s="245"/>
       <c r="P18" s="185">
         <v>3046</v>
       </c>
@@ -38815,7 +39092,7 @@
       <c r="B19" s="185">
         <v>3</v>
       </c>
-      <c r="C19" s="221"/>
+      <c r="C19" s="245"/>
       <c r="D19" s="114" t="s">
         <v>843</v>
       </c>
@@ -38823,28 +39100,28 @@
         <f>SUM(E6:E18)</f>
         <v>219</v>
       </c>
-      <c r="F19" s="221"/>
+      <c r="F19" s="245"/>
       <c r="G19" s="185">
         <v>2014</v>
       </c>
       <c r="H19" s="185">
         <v>57.599999999999994</v>
       </c>
-      <c r="I19" s="221"/>
+      <c r="I19" s="245"/>
       <c r="J19" s="185">
         <v>2049</v>
       </c>
       <c r="K19" s="185">
         <v>96</v>
       </c>
-      <c r="L19" s="221"/>
+      <c r="L19" s="245"/>
       <c r="M19" s="185">
         <v>3014</v>
       </c>
       <c r="N19" s="185">
         <v>56</v>
       </c>
-      <c r="O19" s="221"/>
+      <c r="O19" s="245"/>
       <c r="P19" s="185">
         <v>3047</v>
       </c>
@@ -38859,31 +39136,31 @@
       <c r="B20" s="185">
         <v>3</v>
       </c>
-      <c r="C20" s="221"/>
-      <c r="D20" s="222"/>
-      <c r="E20" s="222"/>
-      <c r="F20" s="221"/>
+      <c r="C20" s="245"/>
+      <c r="D20" s="246"/>
+      <c r="E20" s="246"/>
+      <c r="F20" s="245"/>
       <c r="G20" s="185">
         <v>2015</v>
       </c>
       <c r="H20" s="185">
         <v>52.8</v>
       </c>
-      <c r="I20" s="221"/>
+      <c r="I20" s="245"/>
       <c r="J20" s="185">
         <v>2050</v>
       </c>
       <c r="K20" s="185">
         <v>7.1999999999999993</v>
       </c>
-      <c r="L20" s="221"/>
+      <c r="L20" s="245"/>
       <c r="M20" s="185">
         <v>3015</v>
       </c>
       <c r="N20" s="185">
         <v>12</v>
       </c>
-      <c r="O20" s="221"/>
+      <c r="O20" s="245"/>
       <c r="P20" s="185">
         <v>3048</v>
       </c>
@@ -38898,31 +39175,31 @@
       <c r="B21" s="185">
         <v>3</v>
       </c>
-      <c r="C21" s="221"/>
-      <c r="D21" s="222"/>
-      <c r="E21" s="222"/>
-      <c r="F21" s="221"/>
+      <c r="C21" s="245"/>
+      <c r="D21" s="246"/>
+      <c r="E21" s="246"/>
+      <c r="F21" s="245"/>
       <c r="G21" s="185">
         <v>2016</v>
       </c>
       <c r="H21" s="185">
         <v>48</v>
       </c>
-      <c r="I21" s="221"/>
+      <c r="I21" s="245"/>
       <c r="J21" s="185">
         <v>2053</v>
       </c>
       <c r="K21" s="185">
         <v>14.399999999999999</v>
       </c>
-      <c r="L21" s="221"/>
+      <c r="L21" s="245"/>
       <c r="M21" s="185">
         <v>3016</v>
       </c>
       <c r="N21" s="185">
         <v>35</v>
       </c>
-      <c r="O21" s="221"/>
+      <c r="O21" s="245"/>
       <c r="P21" s="185">
         <v>3049</v>
       </c>
@@ -38937,31 +39214,31 @@
       <c r="B22" s="185">
         <v>3</v>
       </c>
-      <c r="C22" s="221"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="221"/>
+      <c r="C22" s="245"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="246"/>
+      <c r="F22" s="245"/>
       <c r="G22" s="185">
         <v>2017</v>
       </c>
       <c r="H22" s="185">
         <v>151.19999999999999</v>
       </c>
-      <c r="I22" s="221"/>
+      <c r="I22" s="245"/>
       <c r="J22" s="185">
         <v>2054</v>
       </c>
       <c r="K22" s="185">
         <v>3.5999999999999996</v>
       </c>
-      <c r="L22" s="221"/>
+      <c r="L22" s="245"/>
       <c r="M22" s="185">
         <v>3017</v>
       </c>
       <c r="N22" s="185">
         <v>10</v>
       </c>
-      <c r="O22" s="221"/>
+      <c r="O22" s="245"/>
       <c r="P22" s="185">
         <v>3050</v>
       </c>
@@ -38976,31 +39253,31 @@
       <c r="B23" s="185">
         <v>7</v>
       </c>
-      <c r="C23" s="221"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="221"/>
+      <c r="C23" s="245"/>
+      <c r="D23" s="246"/>
+      <c r="E23" s="246"/>
+      <c r="F23" s="245"/>
       <c r="G23" s="185">
         <v>2018</v>
       </c>
       <c r="H23" s="185">
         <v>2.4</v>
       </c>
-      <c r="I23" s="221"/>
+      <c r="I23" s="245"/>
       <c r="J23" s="185">
         <v>2055</v>
       </c>
       <c r="K23" s="185">
         <v>18</v>
       </c>
-      <c r="L23" s="221"/>
+      <c r="L23" s="245"/>
       <c r="M23" s="185">
         <v>3018</v>
       </c>
       <c r="N23" s="185">
         <v>12</v>
       </c>
-      <c r="O23" s="221"/>
+      <c r="O23" s="245"/>
       <c r="P23" s="185">
         <v>3051</v>
       </c>
@@ -39015,31 +39292,31 @@
       <c r="B24" s="185">
         <v>21</v>
       </c>
-      <c r="C24" s="221"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="221"/>
+      <c r="C24" s="245"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="246"/>
+      <c r="F24" s="245"/>
       <c r="G24" s="185">
         <v>2019</v>
       </c>
       <c r="H24" s="185">
         <v>2.4</v>
       </c>
-      <c r="I24" s="221"/>
+      <c r="I24" s="245"/>
       <c r="J24" s="185">
         <v>2056</v>
       </c>
       <c r="K24" s="185">
         <v>9.6</v>
       </c>
-      <c r="L24" s="221"/>
+      <c r="L24" s="245"/>
       <c r="M24" s="185">
         <v>3019</v>
       </c>
       <c r="N24" s="185">
         <v>140</v>
       </c>
-      <c r="O24" s="221"/>
+      <c r="O24" s="245"/>
       <c r="P24" s="185">
         <v>3052</v>
       </c>
@@ -39054,31 +39331,31 @@
       <c r="B25" s="185">
         <v>34</v>
       </c>
-      <c r="C25" s="221"/>
-      <c r="D25" s="222"/>
-      <c r="E25" s="222"/>
-      <c r="F25" s="221"/>
+      <c r="C25" s="245"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="245"/>
       <c r="G25" s="185">
         <v>2020</v>
       </c>
       <c r="H25" s="185">
         <v>15.6</v>
       </c>
-      <c r="I25" s="221"/>
+      <c r="I25" s="245"/>
       <c r="J25" s="185">
         <v>2057</v>
       </c>
       <c r="K25" s="185">
         <v>9.6</v>
       </c>
-      <c r="L25" s="221"/>
+      <c r="L25" s="245"/>
       <c r="M25" s="185">
         <v>3020</v>
       </c>
       <c r="N25" s="185">
         <v>0</v>
       </c>
-      <c r="O25" s="221"/>
+      <c r="O25" s="245"/>
       <c r="P25" s="185">
         <v>3053</v>
       </c>
@@ -39093,31 +39370,31 @@
       <c r="B26" s="185">
         <v>16</v>
       </c>
-      <c r="C26" s="221"/>
-      <c r="D26" s="222"/>
-      <c r="E26" s="222"/>
-      <c r="F26" s="221"/>
+      <c r="C26" s="245"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="245"/>
       <c r="G26" s="185">
         <v>2021</v>
       </c>
       <c r="H26" s="185">
         <v>6</v>
       </c>
-      <c r="I26" s="221"/>
+      <c r="I26" s="245"/>
       <c r="J26" s="185">
         <v>2058</v>
       </c>
       <c r="K26" s="185">
         <v>4.8</v>
       </c>
-      <c r="L26" s="221"/>
+      <c r="L26" s="245"/>
       <c r="M26" s="185">
         <v>3021</v>
       </c>
       <c r="N26" s="185">
         <v>20</v>
       </c>
-      <c r="O26" s="221"/>
+      <c r="O26" s="245"/>
       <c r="P26" s="185">
         <v>3054</v>
       </c>
@@ -39132,31 +39409,31 @@
       <c r="B27" s="185">
         <v>17</v>
       </c>
-      <c r="C27" s="221"/>
-      <c r="D27" s="222"/>
-      <c r="E27" s="222"/>
-      <c r="F27" s="221"/>
+      <c r="C27" s="245"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="245"/>
       <c r="G27" s="185">
         <v>2022</v>
       </c>
       <c r="H27" s="185">
         <v>151.19999999999999</v>
       </c>
-      <c r="I27" s="221"/>
+      <c r="I27" s="245"/>
       <c r="J27" s="185">
         <v>2059</v>
       </c>
       <c r="K27" s="185">
         <v>2.4</v>
       </c>
-      <c r="L27" s="221"/>
+      <c r="L27" s="245"/>
       <c r="M27" s="185">
         <v>3022</v>
       </c>
       <c r="N27" s="185">
         <v>36</v>
       </c>
-      <c r="O27" s="221"/>
+      <c r="O27" s="245"/>
       <c r="P27" s="185">
         <v>3055</v>
       </c>
@@ -39171,31 +39448,31 @@
       <c r="B28" s="185">
         <v>15</v>
       </c>
-      <c r="C28" s="221"/>
-      <c r="D28" s="222"/>
-      <c r="E28" s="222"/>
-      <c r="F28" s="221"/>
+      <c r="C28" s="245"/>
+      <c r="D28" s="246"/>
+      <c r="E28" s="246"/>
+      <c r="F28" s="245"/>
       <c r="G28" s="185">
         <v>2023</v>
       </c>
       <c r="H28" s="185">
         <v>2.4</v>
       </c>
-      <c r="I28" s="221"/>
+      <c r="I28" s="245"/>
       <c r="J28" s="185">
         <v>2060</v>
       </c>
       <c r="K28" s="185">
         <v>4.8</v>
       </c>
-      <c r="L28" s="221"/>
+      <c r="L28" s="245"/>
       <c r="M28" s="185">
         <v>3023</v>
       </c>
       <c r="N28" s="185">
         <v>83</v>
       </c>
-      <c r="O28" s="221"/>
+      <c r="O28" s="245"/>
       <c r="P28" s="185">
         <v>3057</v>
       </c>
@@ -39210,31 +39487,31 @@
       <c r="B29" s="185">
         <v>10</v>
       </c>
-      <c r="C29" s="221"/>
-      <c r="D29" s="222"/>
-      <c r="E29" s="222"/>
-      <c r="F29" s="221"/>
+      <c r="C29" s="245"/>
+      <c r="D29" s="246"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="245"/>
       <c r="G29" s="185">
         <v>2024</v>
       </c>
       <c r="H29" s="185">
         <v>0</v>
       </c>
-      <c r="I29" s="221"/>
+      <c r="I29" s="245"/>
       <c r="J29" s="185">
         <v>2061</v>
       </c>
       <c r="K29" s="185">
         <v>57.599999999999994</v>
       </c>
-      <c r="L29" s="221"/>
+      <c r="L29" s="245"/>
       <c r="M29" s="185">
         <v>3024</v>
       </c>
       <c r="N29" s="185">
         <v>0</v>
       </c>
-      <c r="O29" s="221"/>
+      <c r="O29" s="245"/>
       <c r="P29" s="185">
         <v>3058</v>
       </c>
@@ -39249,31 +39526,31 @@
       <c r="B30" s="185">
         <v>4</v>
       </c>
-      <c r="C30" s="221"/>
-      <c r="D30" s="222"/>
-      <c r="E30" s="222"/>
-      <c r="F30" s="221"/>
+      <c r="C30" s="245"/>
+      <c r="D30" s="246"/>
+      <c r="E30" s="246"/>
+      <c r="F30" s="245"/>
       <c r="G30" s="185">
         <v>2025</v>
       </c>
       <c r="H30" s="185">
         <v>16.8</v>
       </c>
-      <c r="I30" s="221"/>
+      <c r="I30" s="245"/>
       <c r="J30" s="185">
         <v>2062</v>
       </c>
       <c r="K30" s="185">
         <v>43.199999999999996</v>
       </c>
-      <c r="L30" s="221"/>
+      <c r="L30" s="245"/>
       <c r="M30" s="185">
         <v>3025</v>
       </c>
       <c r="N30" s="185">
         <v>5</v>
       </c>
-      <c r="O30" s="221"/>
+      <c r="O30" s="245"/>
       <c r="P30" s="185">
         <v>3059</v>
       </c>
@@ -39288,31 +39565,31 @@
       <c r="B31" s="185">
         <v>8</v>
       </c>
-      <c r="C31" s="221"/>
-      <c r="D31" s="222"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="221"/>
+      <c r="C31" s="245"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="245"/>
       <c r="G31" s="185">
         <v>2026</v>
       </c>
       <c r="H31" s="185">
         <v>2.4</v>
       </c>
-      <c r="I31" s="221"/>
+      <c r="I31" s="245"/>
       <c r="J31" s="185">
         <v>2063</v>
       </c>
       <c r="K31" s="185">
         <v>0</v>
       </c>
-      <c r="L31" s="221"/>
+      <c r="L31" s="245"/>
       <c r="M31" s="185">
         <v>3026</v>
       </c>
       <c r="N31" s="185">
         <v>2</v>
       </c>
-      <c r="O31" s="221"/>
+      <c r="O31" s="245"/>
       <c r="P31" s="185">
         <v>3061</v>
       </c>
@@ -39327,31 +39604,31 @@
       <c r="B32" s="185">
         <v>9</v>
       </c>
-      <c r="C32" s="221"/>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="221"/>
+      <c r="C32" s="245"/>
+      <c r="D32" s="246"/>
+      <c r="E32" s="246"/>
+      <c r="F32" s="245"/>
       <c r="G32" s="185">
         <v>2027</v>
       </c>
       <c r="H32" s="185">
         <v>6</v>
       </c>
-      <c r="I32" s="221"/>
+      <c r="I32" s="245"/>
       <c r="J32" s="185">
         <v>2064</v>
       </c>
       <c r="K32" s="185">
         <v>24</v>
       </c>
-      <c r="L32" s="221"/>
+      <c r="L32" s="245"/>
       <c r="M32" s="185">
         <v>3027</v>
       </c>
       <c r="N32" s="185">
         <v>92</v>
       </c>
-      <c r="O32" s="221"/>
+      <c r="O32" s="245"/>
       <c r="P32" s="185">
         <v>3062</v>
       </c>
@@ -39366,31 +39643,31 @@
       <c r="B33" s="185">
         <v>15</v>
       </c>
-      <c r="C33" s="221"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="221"/>
+      <c r="C33" s="245"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="245"/>
       <c r="G33" s="185">
         <v>2028</v>
       </c>
       <c r="H33" s="185">
         <v>2.4</v>
       </c>
-      <c r="I33" s="221"/>
+      <c r="I33" s="245"/>
       <c r="J33" s="185">
         <v>2065</v>
       </c>
       <c r="K33" s="185">
         <v>2.4</v>
       </c>
-      <c r="L33" s="221"/>
+      <c r="L33" s="245"/>
       <c r="M33" s="185">
         <v>3028</v>
       </c>
       <c r="N33" s="185">
         <v>58</v>
       </c>
-      <c r="O33" s="221"/>
+      <c r="O33" s="245"/>
       <c r="P33" s="185">
         <v>3063</v>
       </c>
@@ -39405,31 +39682,31 @@
       <c r="B34" s="185">
         <v>23</v>
       </c>
-      <c r="C34" s="221"/>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="221"/>
+      <c r="C34" s="245"/>
+      <c r="D34" s="246"/>
+      <c r="E34" s="246"/>
+      <c r="F34" s="245"/>
       <c r="G34" s="185">
         <v>2029</v>
       </c>
       <c r="H34" s="185">
         <v>6</v>
       </c>
-      <c r="I34" s="221"/>
+      <c r="I34" s="245"/>
       <c r="J34" s="185">
         <v>2066</v>
       </c>
       <c r="K34" s="185">
         <v>27.599999999999998</v>
       </c>
-      <c r="L34" s="221"/>
+      <c r="L34" s="245"/>
       <c r="M34" s="185">
         <v>3029</v>
       </c>
       <c r="N34" s="185">
         <v>2</v>
       </c>
-      <c r="O34" s="221"/>
+      <c r="O34" s="245"/>
       <c r="P34" s="185">
         <v>3064</v>
       </c>
@@ -39444,31 +39721,31 @@
       <c r="B35" s="185">
         <v>7</v>
       </c>
-      <c r="C35" s="221"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="221"/>
+      <c r="C35" s="245"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="245"/>
       <c r="G35" s="185">
         <v>2030</v>
       </c>
       <c r="H35" s="185">
         <v>7.1999999999999993</v>
       </c>
-      <c r="I35" s="221"/>
+      <c r="I35" s="245"/>
       <c r="J35" s="185">
         <v>2067</v>
       </c>
       <c r="K35" s="185">
         <v>81.599999999999994</v>
       </c>
-      <c r="L35" s="221"/>
+      <c r="L35" s="245"/>
       <c r="M35" s="185">
         <v>3030</v>
       </c>
       <c r="N35" s="185">
         <v>50</v>
       </c>
-      <c r="O35" s="221"/>
+      <c r="O35" s="245"/>
       <c r="P35" s="185">
         <v>3066</v>
       </c>
@@ -39483,31 +39760,31 @@
       <c r="B36" s="185">
         <v>11</v>
       </c>
-      <c r="C36" s="221"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="221"/>
+      <c r="C36" s="245"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="245"/>
       <c r="G36" s="185">
         <v>2031</v>
       </c>
       <c r="H36" s="185">
         <v>21.599999999999998</v>
       </c>
-      <c r="I36" s="221"/>
+      <c r="I36" s="245"/>
       <c r="J36" s="185">
         <v>2068</v>
       </c>
       <c r="K36" s="185">
         <v>38.4</v>
       </c>
-      <c r="L36" s="221"/>
+      <c r="L36" s="245"/>
       <c r="M36" s="185">
         <v>3031</v>
       </c>
       <c r="N36" s="185">
         <v>54</v>
       </c>
-      <c r="O36" s="221"/>
+      <c r="O36" s="245"/>
       <c r="P36" s="185">
         <v>3067</v>
       </c>
@@ -39522,31 +39799,31 @@
       <c r="B37" s="185">
         <v>3</v>
       </c>
-      <c r="C37" s="221"/>
-      <c r="D37" s="222"/>
-      <c r="E37" s="222"/>
-      <c r="F37" s="221"/>
+      <c r="C37" s="245"/>
+      <c r="D37" s="246"/>
+      <c r="E37" s="246"/>
+      <c r="F37" s="245"/>
       <c r="G37" s="185">
         <v>2032</v>
       </c>
       <c r="H37" s="185">
         <v>45.6</v>
       </c>
-      <c r="I37" s="221"/>
+      <c r="I37" s="245"/>
       <c r="J37" s="185">
         <v>2070</v>
       </c>
       <c r="K37" s="185">
         <v>52.8</v>
       </c>
-      <c r="L37" s="221"/>
+      <c r="L37" s="245"/>
       <c r="M37" s="185">
         <v>3032</v>
       </c>
       <c r="N37" s="185">
         <v>42</v>
       </c>
-      <c r="O37" s="221"/>
+      <c r="O37" s="245"/>
       <c r="P37" s="114" t="s">
         <v>843</v>
       </c>
@@ -39562,33 +39839,33 @@
       <c r="B38" s="185">
         <v>4</v>
       </c>
-      <c r="C38" s="221"/>
-      <c r="D38" s="222"/>
-      <c r="E38" s="222"/>
-      <c r="F38" s="221"/>
+      <c r="C38" s="245"/>
+      <c r="D38" s="246"/>
+      <c r="E38" s="246"/>
+      <c r="F38" s="245"/>
       <c r="G38" s="185">
         <v>2033</v>
       </c>
       <c r="H38" s="185">
         <v>7.1999999999999993</v>
       </c>
-      <c r="I38" s="221"/>
+      <c r="I38" s="245"/>
       <c r="J38" s="185">
         <v>2071</v>
       </c>
       <c r="K38" s="185">
         <v>93.6</v>
       </c>
-      <c r="L38" s="221"/>
+      <c r="L38" s="245"/>
       <c r="M38" s="185">
         <v>3033</v>
       </c>
       <c r="N38" s="185">
         <v>28</v>
       </c>
-      <c r="O38" s="221"/>
-      <c r="P38" s="222"/>
-      <c r="Q38" s="222"/>
+      <c r="O38" s="245"/>
+      <c r="P38" s="246"/>
+      <c r="Q38" s="246"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="114" t="s">
@@ -39598,17 +39875,17 @@
         <f>SUM(B6:B38)</f>
         <v>348</v>
       </c>
-      <c r="C39" s="221"/>
-      <c r="D39" s="222"/>
-      <c r="E39" s="222"/>
-      <c r="F39" s="221"/>
+      <c r="C39" s="245"/>
+      <c r="D39" s="246"/>
+      <c r="E39" s="246"/>
+      <c r="F39" s="245"/>
       <c r="G39" s="185">
         <v>2034</v>
       </c>
       <c r="H39" s="185">
         <v>4.8</v>
       </c>
-      <c r="I39" s="221"/>
+      <c r="I39" s="245"/>
       <c r="J39" s="114" t="s">
         <v>843</v>
       </c>
@@ -39616,7 +39893,7 @@
         <f>SUM(K6:K38)</f>
         <v>1445.9999999999998</v>
       </c>
-      <c r="L39" s="221"/>
+      <c r="L39" s="245"/>
       <c r="M39" s="114" t="s">
         <v>843</v>
       </c>
@@ -39624,40 +39901,40 @@
         <f>SUM(N6:N38)</f>
         <v>1346</v>
       </c>
-      <c r="O39" s="221"/>
-      <c r="P39" s="222"/>
-      <c r="Q39" s="222"/>
+      <c r="O39" s="245"/>
+      <c r="P39" s="246"/>
+      <c r="Q39" s="246"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A40" s="221"/>
-      <c r="B40" s="221"/>
-      <c r="C40" s="221"/>
-      <c r="D40" s="222"/>
-      <c r="E40" s="222"/>
-      <c r="F40" s="221"/>
+      <c r="A40" s="245"/>
+      <c r="B40" s="245"/>
+      <c r="C40" s="245"/>
+      <c r="D40" s="246"/>
+      <c r="E40" s="246"/>
+      <c r="F40" s="245"/>
       <c r="G40" s="185">
         <v>2035</v>
       </c>
       <c r="H40" s="185">
         <v>2.4</v>
       </c>
-      <c r="I40" s="221"/>
-      <c r="J40" s="221"/>
-      <c r="K40" s="221"/>
-      <c r="L40" s="221"/>
-      <c r="M40" s="222"/>
-      <c r="N40" s="222"/>
-      <c r="O40" s="221"/>
-      <c r="P40" s="222"/>
-      <c r="Q40" s="222"/>
+      <c r="I40" s="245"/>
+      <c r="J40" s="245"/>
+      <c r="K40" s="245"/>
+      <c r="L40" s="245"/>
+      <c r="M40" s="246"/>
+      <c r="N40" s="246"/>
+      <c r="O40" s="245"/>
+      <c r="P40" s="246"/>
+      <c r="Q40" s="246"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A41" s="221"/>
-      <c r="B41" s="221"/>
-      <c r="C41" s="221"/>
-      <c r="D41" s="222"/>
-      <c r="E41" s="222"/>
-      <c r="F41" s="221"/>
+      <c r="A41" s="245"/>
+      <c r="B41" s="245"/>
+      <c r="C41" s="245"/>
+      <c r="D41" s="246"/>
+      <c r="E41" s="246"/>
+      <c r="F41" s="245"/>
       <c r="G41" s="114" t="s">
         <v>843</v>
       </c>
@@ -39665,15 +39942,15 @@
         <f>SUM(H6:H40)</f>
         <v>1091.9999999999998</v>
       </c>
-      <c r="I41" s="221"/>
-      <c r="J41" s="221"/>
-      <c r="K41" s="221"/>
-      <c r="L41" s="221"/>
-      <c r="M41" s="222"/>
-      <c r="N41" s="222"/>
-      <c r="O41" s="221"/>
-      <c r="P41" s="222"/>
-      <c r="Q41" s="222"/>
+      <c r="I41" s="245"/>
+      <c r="J41" s="245"/>
+      <c r="K41" s="245"/>
+      <c r="L41" s="245"/>
+      <c r="M41" s="246"/>
+      <c r="N41" s="246"/>
+      <c r="O41" s="245"/>
+      <c r="P41" s="246"/>
+      <c r="Q41" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -39711,24 +39988,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="227" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="227"/>
-      <c r="C1" s="227"/>
-      <c r="D1" s="227"/>
-      <c r="E1" s="227"/>
-      <c r="F1" s="227"/>
+      <c r="A1" s="251" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="251"/>
+      <c r="C1" s="251"/>
+      <c r="D1" s="251"/>
+      <c r="E1" s="251"/>
+      <c r="F1" s="251"/>
     </row>
     <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="181" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="228" t="s">
+      <c r="B2" s="252" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="229"/>
-      <c r="D2" s="229"/>
+      <c r="C2" s="253"/>
+      <c r="D2" s="253"/>
       <c r="E2" s="180" t="s">
         <v>10</v>
       </c>
@@ -39740,11 +40017,11 @@
       <c r="A3" s="178">
         <v>1</v>
       </c>
-      <c r="B3" s="230" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C3" s="231"/>
-      <c r="D3" s="231"/>
+      <c r="B3" s="254" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C3" s="255"/>
+      <c r="D3" s="255"/>
       <c r="E3" s="178" t="s">
         <v>15</v>
       </c>
@@ -39754,26 +40031,26 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="225"/>
-      <c r="B4" s="225"/>
-      <c r="C4" s="225"/>
-      <c r="D4" s="225"/>
-      <c r="E4" s="225"/>
-      <c r="F4" s="225"/>
+      <c r="A4" s="249"/>
+      <c r="B4" s="249"/>
+      <c r="C4" s="249"/>
+      <c r="D4" s="249"/>
+      <c r="E4" s="249"/>
+      <c r="F4" s="249"/>
     </row>
     <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="176" t="s">
         <v>829</v>
       </c>
       <c r="B5" s="176" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="C5" s="176" t="s">
-        <v>1191</v>
-      </c>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
+        <v>1189</v>
+      </c>
+      <c r="D5" s="250"/>
+      <c r="E5" s="250"/>
+      <c r="F5" s="250"/>
     </row>
     <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="176">
@@ -39786,9 +40063,9 @@
         <f>252+660</f>
         <v>912</v>
       </c>
-      <c r="D6" s="226"/>
-      <c r="E6" s="226"/>
-      <c r="F6" s="226"/>
+      <c r="D6" s="250"/>
+      <c r="E6" s="250"/>
+      <c r="F6" s="250"/>
     </row>
     <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="176">
@@ -39801,9 +40078,9 @@
         <f>378+608+322</f>
         <v>1308</v>
       </c>
-      <c r="D7" s="226"/>
-      <c r="E7" s="226"/>
-      <c r="F7" s="226"/>
+      <c r="D7" s="250"/>
+      <c r="E7" s="250"/>
+      <c r="F7" s="250"/>
     </row>
     <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="176">
@@ -39816,22 +40093,22 @@
         <f>12*3*2</f>
         <v>72</v>
       </c>
-      <c r="D8" s="226"/>
-      <c r="E8" s="226"/>
-      <c r="F8" s="226"/>
+      <c r="D8" s="250"/>
+      <c r="E8" s="250"/>
+      <c r="F8" s="250"/>
     </row>
     <row r="9" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="208" t="s">
+      <c r="A9" s="238" t="s">
         <v>843</v>
       </c>
-      <c r="B9" s="208"/>
+      <c r="B9" s="238"/>
       <c r="C9" s="176">
         <f>SUM(C6:C8)</f>
         <v>2292</v>
       </c>
-      <c r="D9" s="226"/>
-      <c r="E9" s="226"/>
-      <c r="F9" s="226"/>
+      <c r="D9" s="250"/>
+      <c r="E9" s="250"/>
+      <c r="F9" s="250"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -39866,34 +40143,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
     </row>
     <row r="2" spans="1:11" s="164" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="170" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="220" t="s">
+      <c r="B2" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="220"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
@@ -39905,16 +40182,16 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="218" t="s">
+      <c r="B3" s="231" t="s">
         <v>1179</v>
       </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="231"/>
+      <c r="I3" s="231"/>
       <c r="J3" s="115" t="s">
         <v>20</v>
       </c>
@@ -39959,67 +40236,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="195"/>
-      <c r="M1" s="195"/>
-      <c r="N1" s="195"/>
-      <c r="O1" s="195"/>
-      <c r="P1" s="195"/>
-      <c r="Q1" s="195"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
+      <c r="I1" s="235"/>
+      <c r="J1" s="235"/>
+      <c r="K1" s="235"/>
+      <c r="L1" s="208"/>
+      <c r="M1" s="208"/>
+      <c r="N1" s="208"/>
+      <c r="O1" s="208"/>
+      <c r="P1" s="208"/>
+      <c r="Q1" s="208"/>
     </row>
     <row r="2" spans="1:17" s="164" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="220" t="s">
+      <c r="B2" s="236" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="220"/>
-      <c r="D2" s="220"/>
-      <c r="E2" s="220"/>
-      <c r="F2" s="220"/>
-      <c r="G2" s="220"/>
-      <c r="H2" s="220"/>
-      <c r="I2" s="220"/>
+      <c r="C2" s="236"/>
+      <c r="D2" s="236"/>
+      <c r="E2" s="236"/>
+      <c r="F2" s="236"/>
+      <c r="G2" s="236"/>
+      <c r="H2" s="236"/>
+      <c r="I2" s="236"/>
       <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
       <c r="K2" s="117" t="s">
         <v>830</v>
       </c>
-      <c r="L2" s="195"/>
-      <c r="M2" s="195"/>
-      <c r="N2" s="195"/>
-      <c r="O2" s="195"/>
-      <c r="P2" s="195"/>
-      <c r="Q2" s="195"/>
+      <c r="L2" s="208"/>
+      <c r="M2" s="208"/>
+      <c r="N2" s="208"/>
+      <c r="O2" s="208"/>
+      <c r="P2" s="208"/>
+      <c r="Q2" s="208"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="218" t="s">
+      <c r="B3" s="231" t="s">
         <v>1134</v>
       </c>
-      <c r="C3" s="218"/>
-      <c r="D3" s="218"/>
-      <c r="E3" s="218"/>
-      <c r="F3" s="218"/>
-      <c r="G3" s="218"/>
-      <c r="H3" s="218"/>
-      <c r="I3" s="218"/>
+      <c r="C3" s="231"/>
+      <c r="D3" s="231"/>
+      <c r="E3" s="231"/>
+      <c r="F3" s="231"/>
+      <c r="G3" s="231"/>
+      <c r="H3" s="231"/>
+      <c r="I3" s="231"/>
       <c r="J3" s="115" t="s">
         <v>19</v>
       </c>
@@ -40027,27 +40304,27 @@
         <f>Q35+N36+K36+H37+B37+E21</f>
         <v>86.995199999999997</v>
       </c>
-      <c r="L3" s="195"/>
-      <c r="M3" s="195"/>
-      <c r="N3" s="195"/>
-      <c r="O3" s="195"/>
-      <c r="P3" s="195"/>
-      <c r="Q3" s="195"/>
+      <c r="L3" s="208"/>
+      <c r="M3" s="208"/>
+      <c r="N3" s="208"/>
+      <c r="O3" s="208"/>
+      <c r="P3" s="208"/>
+      <c r="Q3" s="208"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="218" t="s">
+      <c r="B4" s="231" t="s">
         <v>1135</v>
       </c>
-      <c r="C4" s="218"/>
-      <c r="D4" s="218"/>
-      <c r="E4" s="218"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="218"/>
-      <c r="H4" s="218"/>
-      <c r="I4" s="218"/>
+      <c r="C4" s="231"/>
+      <c r="D4" s="231"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="231"/>
+      <c r="G4" s="231"/>
+      <c r="H4" s="231"/>
+      <c r="I4" s="231"/>
       <c r="J4" s="115" t="s">
         <v>19</v>
       </c>
@@ -40055,55 +40332,55 @@
         <f>292*(0.15*0.15*0.25)</f>
         <v>1.6424999999999998</v>
       </c>
-      <c r="L4" s="195"/>
-      <c r="M4" s="195"/>
-      <c r="N4" s="195"/>
-      <c r="O4" s="195"/>
-      <c r="P4" s="195"/>
-      <c r="Q4" s="195"/>
+      <c r="L4" s="208"/>
+      <c r="M4" s="208"/>
+      <c r="N4" s="208"/>
+      <c r="O4" s="208"/>
+      <c r="P4" s="208"/>
+      <c r="Q4" s="208"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="232" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B5" s="232"/>
-      <c r="C5" s="232"/>
-      <c r="D5" s="232"/>
-      <c r="E5" s="232"/>
-      <c r="F5" s="232"/>
-      <c r="G5" s="232"/>
-      <c r="H5" s="232"/>
-      <c r="I5" s="232"/>
-      <c r="J5" s="233"/>
+      <c r="A5" s="258" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B5" s="258"/>
+      <c r="C5" s="258"/>
+      <c r="D5" s="258"/>
+      <c r="E5" s="258"/>
+      <c r="F5" s="258"/>
+      <c r="G5" s="258"/>
+      <c r="H5" s="258"/>
+      <c r="I5" s="258"/>
+      <c r="J5" s="259"/>
       <c r="K5" s="165">
         <f>SUM(K3:K4)</f>
         <v>88.637699999999995</v>
       </c>
-      <c r="L5" s="195"/>
-      <c r="M5" s="195"/>
-      <c r="N5" s="195"/>
-      <c r="O5" s="195"/>
-      <c r="P5" s="195"/>
-      <c r="Q5" s="195"/>
+      <c r="L5" s="208"/>
+      <c r="M5" s="208"/>
+      <c r="N5" s="208"/>
+      <c r="O5" s="208"/>
+      <c r="P5" s="208"/>
+      <c r="Q5" s="208"/>
     </row>
     <row r="6" spans="1:17" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="201"/>
-      <c r="B6" s="201"/>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
-      <c r="F6" s="201"/>
-      <c r="G6" s="201"/>
-      <c r="H6" s="201"/>
-      <c r="I6" s="201"/>
-      <c r="J6" s="201"/>
-      <c r="K6" s="201"/>
-      <c r="L6" s="195"/>
-      <c r="M6" s="195"/>
-      <c r="N6" s="195"/>
-      <c r="O6" s="195"/>
-      <c r="P6" s="195"/>
-      <c r="Q6" s="195"/>
+      <c r="A6" s="257"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="257"/>
+      <c r="E6" s="257"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="257"/>
+      <c r="I6" s="257"/>
+      <c r="J6" s="257"/>
+      <c r="K6" s="257"/>
+      <c r="L6" s="208"/>
+      <c r="M6" s="208"/>
+      <c r="N6" s="208"/>
+      <c r="O6" s="208"/>
+      <c r="P6" s="208"/>
+      <c r="Q6" s="208"/>
     </row>
     <row r="7" spans="1:17" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="114" t="s">
@@ -40112,35 +40389,35 @@
       <c r="B7" s="115" t="s">
         <v>1138</v>
       </c>
-      <c r="C7" s="194"/>
+      <c r="C7" s="256"/>
       <c r="D7" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="E7" s="115" t="s">
         <v>1138</v>
       </c>
-      <c r="F7" s="194"/>
+      <c r="F7" s="256"/>
       <c r="G7" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="H7" s="115" t="s">
         <v>1138</v>
       </c>
-      <c r="I7" s="194"/>
+      <c r="I7" s="256"/>
       <c r="J7" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="K7" s="115" t="s">
         <v>1138</v>
       </c>
-      <c r="L7" s="221"/>
+      <c r="L7" s="245"/>
       <c r="M7" s="114" t="s">
         <v>1133</v>
       </c>
       <c r="N7" s="168" t="s">
         <v>1138</v>
       </c>
-      <c r="O7" s="194"/>
+      <c r="O7" s="256"/>
       <c r="P7" s="114" t="s">
         <v>1133</v>
       </c>
@@ -40155,35 +40432,35 @@
       <c r="B8" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C8" s="194"/>
+      <c r="C8" s="256"/>
       <c r="D8" s="114" t="s">
         <v>1178</v>
       </c>
       <c r="E8" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="F8" s="194"/>
+      <c r="F8" s="256"/>
       <c r="G8" s="114" t="s">
         <v>834</v>
       </c>
       <c r="H8" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I8" s="194"/>
+      <c r="I8" s="256"/>
       <c r="J8" s="114" t="s">
         <v>855</v>
       </c>
       <c r="K8" s="114">
         <v>1.13472</v>
       </c>
-      <c r="L8" s="221"/>
+      <c r="L8" s="245"/>
       <c r="M8" s="114" t="s">
         <v>971</v>
       </c>
       <c r="N8" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O8" s="194"/>
+      <c r="O8" s="256"/>
       <c r="P8" s="114" t="s">
         <v>1003</v>
       </c>
@@ -40198,35 +40475,35 @@
       <c r="B9" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="C9" s="194"/>
+      <c r="C9" s="256"/>
       <c r="D9" s="114" t="s">
         <v>1166</v>
       </c>
       <c r="E9" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="F9" s="194"/>
+      <c r="F9" s="256"/>
       <c r="G9" s="114" t="s">
         <v>836</v>
       </c>
       <c r="H9" s="114">
         <v>0.75647999999999993</v>
       </c>
-      <c r="I9" s="194"/>
+      <c r="I9" s="256"/>
       <c r="J9" s="114" t="s">
         <v>839</v>
       </c>
       <c r="K9" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="L9" s="221"/>
+      <c r="L9" s="245"/>
       <c r="M9" s="114" t="s">
         <v>972</v>
       </c>
       <c r="N9" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O9" s="194"/>
+      <c r="O9" s="256"/>
       <c r="P9" s="114" t="s">
         <v>1005</v>
       </c>
@@ -40241,35 +40518,35 @@
       <c r="B10" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C10" s="194"/>
+      <c r="C10" s="256"/>
       <c r="D10" s="114" t="s">
         <v>1167</v>
       </c>
       <c r="E10" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="F10" s="194"/>
+      <c r="F10" s="256"/>
       <c r="G10" s="114" t="s">
         <v>838</v>
       </c>
       <c r="H10" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I10" s="194"/>
+      <c r="I10" s="256"/>
       <c r="J10" s="114" t="s">
         <v>856</v>
       </c>
       <c r="K10" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="L10" s="221"/>
+      <c r="L10" s="245"/>
       <c r="M10" s="114" t="s">
         <v>973</v>
       </c>
       <c r="N10" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O10" s="194"/>
+      <c r="O10" s="256"/>
       <c r="P10" s="114" t="s">
         <v>1006</v>
       </c>
@@ -40284,35 +40561,35 @@
       <c r="B11" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C11" s="194"/>
+      <c r="C11" s="256"/>
       <c r="D11" s="114" t="s">
         <v>1168</v>
       </c>
       <c r="E11" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="F11" s="194"/>
+      <c r="F11" s="256"/>
       <c r="G11" s="114" t="s">
         <v>840</v>
       </c>
       <c r="H11" s="114">
         <v>0.75647999999999993</v>
       </c>
-      <c r="I11" s="194"/>
+      <c r="I11" s="256"/>
       <c r="J11" s="114" t="s">
         <v>857</v>
       </c>
       <c r="K11" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="L11" s="221"/>
+      <c r="L11" s="245"/>
       <c r="M11" s="114" t="s">
         <v>974</v>
       </c>
       <c r="N11" s="114">
         <v>1.13472</v>
       </c>
-      <c r="O11" s="194"/>
+      <c r="O11" s="256"/>
       <c r="P11" s="114" t="s">
         <v>1007</v>
       </c>
@@ -40327,35 +40604,35 @@
       <c r="B12" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C12" s="194"/>
+      <c r="C12" s="256"/>
       <c r="D12" s="114" t="s">
         <v>1169</v>
       </c>
       <c r="E12" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="F12" s="194"/>
+      <c r="F12" s="256"/>
       <c r="G12" s="114" t="s">
         <v>842</v>
       </c>
       <c r="H12" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="I12" s="194"/>
+      <c r="I12" s="256"/>
       <c r="J12" s="114" t="s">
         <v>858</v>
       </c>
       <c r="K12" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="L12" s="221"/>
+      <c r="L12" s="245"/>
       <c r="M12" s="114" t="s">
         <v>975</v>
       </c>
       <c r="N12" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="O12" s="194"/>
+      <c r="O12" s="256"/>
       <c r="P12" s="114" t="s">
         <v>1008</v>
       </c>
@@ -40370,35 +40647,35 @@
       <c r="B13" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C13" s="194"/>
+      <c r="C13" s="256"/>
       <c r="D13" s="114" t="s">
         <v>1170</v>
       </c>
       <c r="E13" s="114">
         <v>0.4728</v>
       </c>
-      <c r="F13" s="194"/>
+      <c r="F13" s="256"/>
       <c r="G13" s="114" t="s">
         <v>944</v>
       </c>
       <c r="H13" s="114">
         <v>0.4728</v>
       </c>
-      <c r="I13" s="194"/>
+      <c r="I13" s="256"/>
       <c r="J13" s="114" t="s">
         <v>859</v>
       </c>
       <c r="K13" s="114">
         <v>1.7020799999999998</v>
       </c>
-      <c r="L13" s="221"/>
+      <c r="L13" s="245"/>
       <c r="M13" s="114" t="s">
         <v>977</v>
       </c>
       <c r="N13" s="114">
         <v>0.4728</v>
       </c>
-      <c r="O13" s="194"/>
+      <c r="O13" s="256"/>
       <c r="P13" s="114" t="s">
         <v>1009</v>
       </c>
@@ -40413,35 +40690,35 @@
       <c r="B14" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C14" s="194"/>
+      <c r="C14" s="256"/>
       <c r="D14" s="114" t="s">
         <v>1171</v>
       </c>
       <c r="E14" s="114">
         <v>0.4728</v>
       </c>
-      <c r="F14" s="194"/>
+      <c r="F14" s="256"/>
       <c r="G14" s="114" t="s">
         <v>945</v>
       </c>
       <c r="H14" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="I14" s="194"/>
+      <c r="I14" s="256"/>
       <c r="J14" s="114" t="s">
         <v>960</v>
       </c>
       <c r="K14" s="114">
         <v>0.4728</v>
       </c>
-      <c r="L14" s="221"/>
+      <c r="L14" s="245"/>
       <c r="M14" s="114" t="s">
         <v>978</v>
       </c>
       <c r="N14" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="O14" s="194"/>
+      <c r="O14" s="256"/>
       <c r="P14" s="114" t="s">
         <v>1010</v>
       </c>
@@ -40456,35 +40733,35 @@
       <c r="B15" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C15" s="194"/>
+      <c r="C15" s="256"/>
       <c r="D15" s="114" t="s">
         <v>1172</v>
       </c>
       <c r="E15" s="114">
         <v>0.9456</v>
       </c>
-      <c r="F15" s="194"/>
+      <c r="F15" s="256"/>
       <c r="G15" s="114" t="s">
         <v>946</v>
       </c>
       <c r="H15" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="I15" s="194"/>
+      <c r="I15" s="256"/>
       <c r="J15" s="114" t="s">
         <v>860</v>
       </c>
       <c r="K15" s="114">
         <v>1.7020799999999998</v>
       </c>
-      <c r="L15" s="221"/>
+      <c r="L15" s="245"/>
       <c r="M15" s="114" t="s">
         <v>979</v>
       </c>
       <c r="N15" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="O15" s="194"/>
+      <c r="O15" s="256"/>
       <c r="P15" s="114" t="s">
         <v>1011</v>
       </c>
@@ -40499,35 +40776,35 @@
       <c r="B16" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C16" s="194"/>
+      <c r="C16" s="256"/>
       <c r="D16" s="114" t="s">
         <v>1173</v>
       </c>
       <c r="E16" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="F16" s="194"/>
+      <c r="F16" s="256"/>
       <c r="G16" s="114" t="s">
         <v>844</v>
       </c>
       <c r="H16" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I16" s="194"/>
+      <c r="I16" s="256"/>
       <c r="J16" s="114" t="s">
         <v>861</v>
       </c>
       <c r="K16" s="114">
         <v>1.6075200000000001</v>
       </c>
-      <c r="L16" s="221"/>
+      <c r="L16" s="245"/>
       <c r="M16" s="114" t="s">
         <v>980</v>
       </c>
       <c r="N16" s="114">
         <v>1.13472</v>
       </c>
-      <c r="O16" s="194"/>
+      <c r="O16" s="256"/>
       <c r="P16" s="114" t="s">
         <v>1012</v>
       </c>
@@ -40542,35 +40819,35 @@
       <c r="B17" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C17" s="194"/>
+      <c r="C17" s="256"/>
       <c r="D17" s="114" t="s">
         <v>1174</v>
       </c>
       <c r="E17" s="114">
         <v>0.4728</v>
       </c>
-      <c r="F17" s="194"/>
+      <c r="F17" s="256"/>
       <c r="G17" s="114" t="s">
         <v>845</v>
       </c>
       <c r="H17" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I17" s="194"/>
+      <c r="I17" s="256"/>
       <c r="J17" s="114" t="s">
         <v>862</v>
       </c>
       <c r="K17" s="114">
         <v>1.04016</v>
       </c>
-      <c r="L17" s="221"/>
+      <c r="L17" s="245"/>
       <c r="M17" s="114" t="s">
         <v>981</v>
       </c>
       <c r="N17" s="114">
         <v>1.13472</v>
       </c>
-      <c r="O17" s="194"/>
+      <c r="O17" s="256"/>
       <c r="P17" s="114" t="s">
         <v>1013</v>
       </c>
@@ -40585,35 +40862,35 @@
       <c r="B18" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C18" s="194"/>
+      <c r="C18" s="256"/>
       <c r="D18" s="114" t="s">
         <v>1175</v>
       </c>
       <c r="E18" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="F18" s="194"/>
+      <c r="F18" s="256"/>
       <c r="G18" s="114" t="s">
         <v>846</v>
       </c>
       <c r="H18" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I18" s="194"/>
+      <c r="I18" s="256"/>
       <c r="J18" s="114" t="s">
         <v>863</v>
       </c>
       <c r="K18" s="114">
         <v>1.4183999999999999</v>
       </c>
-      <c r="L18" s="221"/>
+      <c r="L18" s="245"/>
       <c r="M18" s="114" t="s">
         <v>982</v>
       </c>
       <c r="N18" s="114">
         <v>2.0803199999999999</v>
       </c>
-      <c r="O18" s="194"/>
+      <c r="O18" s="256"/>
       <c r="P18" s="114" t="s">
         <v>1014</v>
       </c>
@@ -40628,35 +40905,35 @@
       <c r="B19" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C19" s="194"/>
+      <c r="C19" s="256"/>
       <c r="D19" s="114" t="s">
         <v>1176</v>
       </c>
       <c r="E19" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="F19" s="194"/>
+      <c r="F19" s="256"/>
       <c r="G19" s="114" t="s">
         <v>847</v>
       </c>
       <c r="H19" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I19" s="194"/>
+      <c r="I19" s="256"/>
       <c r="J19" s="114" t="s">
         <v>864</v>
       </c>
       <c r="K19" s="114">
         <v>1.04016</v>
       </c>
-      <c r="L19" s="221"/>
+      <c r="L19" s="245"/>
       <c r="M19" s="114" t="s">
         <v>983</v>
       </c>
       <c r="N19" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="O19" s="194"/>
+      <c r="O19" s="256"/>
       <c r="P19" s="114" t="s">
         <v>1015</v>
       </c>
@@ -40671,35 +40948,35 @@
       <c r="B20" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="C20" s="194"/>
+      <c r="C20" s="256"/>
       <c r="D20" s="114" t="s">
         <v>1177</v>
       </c>
       <c r="E20" s="114">
         <v>0.75647999999999993</v>
       </c>
-      <c r="F20" s="194"/>
+      <c r="F20" s="256"/>
       <c r="G20" s="114" t="s">
         <v>848</v>
       </c>
       <c r="H20" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I20" s="194"/>
+      <c r="I20" s="256"/>
       <c r="J20" s="114" t="s">
         <v>865</v>
       </c>
       <c r="K20" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="L20" s="221"/>
+      <c r="L20" s="245"/>
       <c r="M20" s="114" t="s">
         <v>984</v>
       </c>
       <c r="N20" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O20" s="194"/>
+      <c r="O20" s="256"/>
       <c r="P20" s="114" t="s">
         <v>1016</v>
       </c>
@@ -40714,7 +40991,7 @@
       <c r="B21" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C21" s="194"/>
+      <c r="C21" s="256"/>
       <c r="D21" s="166" t="s">
         <v>843</v>
       </c>
@@ -40722,28 +40999,28 @@
         <f>SUM(E8:E20)</f>
         <v>5.8627199999999995</v>
       </c>
-      <c r="F21" s="194"/>
+      <c r="F21" s="256"/>
       <c r="G21" s="114" t="s">
         <v>849</v>
       </c>
       <c r="H21" s="114">
         <v>1.2292799999999999</v>
       </c>
-      <c r="I21" s="194"/>
+      <c r="I21" s="256"/>
       <c r="J21" s="114" t="s">
         <v>962</v>
       </c>
       <c r="K21" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="L21" s="221"/>
+      <c r="L21" s="245"/>
       <c r="M21" s="114" t="s">
         <v>985</v>
       </c>
       <c r="N21" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="O21" s="194"/>
+      <c r="O21" s="256"/>
       <c r="P21" s="114" t="s">
         <v>1018</v>
       </c>
@@ -40758,31 +41035,31 @@
       <c r="B22" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C22" s="194"/>
-      <c r="D22" s="222"/>
-      <c r="E22" s="222"/>
-      <c r="F22" s="222"/>
+      <c r="C22" s="256"/>
+      <c r="D22" s="246"/>
+      <c r="E22" s="246"/>
+      <c r="F22" s="246"/>
       <c r="G22" s="114" t="s">
         <v>947</v>
       </c>
       <c r="H22" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="I22" s="194"/>
+      <c r="I22" s="256"/>
       <c r="J22" s="114" t="s">
         <v>963</v>
       </c>
       <c r="K22" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="L22" s="221"/>
+      <c r="L22" s="245"/>
       <c r="M22" s="114" t="s">
         <v>987</v>
       </c>
       <c r="N22" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="O22" s="194"/>
+      <c r="O22" s="256"/>
       <c r="P22" s="114" t="s">
         <v>1019</v>
       </c>
@@ -40797,31 +41074,31 @@
       <c r="B23" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C23" s="194"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
+      <c r="C23" s="256"/>
+      <c r="D23" s="246"/>
+      <c r="E23" s="246"/>
+      <c r="F23" s="246"/>
       <c r="G23" s="114" t="s">
         <v>949</v>
       </c>
       <c r="H23" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="I23" s="194"/>
+      <c r="I23" s="256"/>
       <c r="J23" s="114" t="s">
         <v>964</v>
       </c>
       <c r="K23" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="L23" s="221"/>
+      <c r="L23" s="245"/>
       <c r="M23" s="114" t="s">
         <v>988</v>
       </c>
       <c r="N23" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="O23" s="194"/>
+      <c r="O23" s="256"/>
       <c r="P23" s="114" t="s">
         <v>1020</v>
       </c>
@@ -40836,31 +41113,31 @@
       <c r="B24" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C24" s="194"/>
-      <c r="D24" s="222"/>
-      <c r="E24" s="222"/>
-      <c r="F24" s="222"/>
+      <c r="C24" s="256"/>
+      <c r="D24" s="246"/>
+      <c r="E24" s="246"/>
+      <c r="F24" s="246"/>
       <c r="G24" s="114" t="s">
         <v>950</v>
       </c>
       <c r="H24" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="I24" s="194"/>
+      <c r="I24" s="256"/>
       <c r="J24" s="114" t="s">
         <v>965</v>
       </c>
       <c r="K24" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="L24" s="221"/>
+      <c r="L24" s="245"/>
       <c r="M24" s="114" t="s">
         <v>989</v>
       </c>
       <c r="N24" s="114">
         <v>1.8912</v>
       </c>
-      <c r="O24" s="194"/>
+      <c r="O24" s="256"/>
       <c r="P24" s="114" t="s">
         <v>1021</v>
       </c>
@@ -40875,31 +41152,31 @@
       <c r="B25" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C25" s="194"/>
-      <c r="D25" s="222"/>
-      <c r="E25" s="222"/>
-      <c r="F25" s="222"/>
+      <c r="C25" s="256"/>
+      <c r="D25" s="246"/>
+      <c r="E25" s="246"/>
+      <c r="F25" s="246"/>
       <c r="G25" s="114" t="s">
         <v>850</v>
       </c>
       <c r="H25" s="114">
         <v>1.6075200000000001</v>
       </c>
-      <c r="I25" s="194"/>
+      <c r="I25" s="256"/>
       <c r="J25" s="114" t="s">
         <v>966</v>
       </c>
       <c r="K25" s="114">
         <v>0.56735999999999998</v>
       </c>
-      <c r="L25" s="221"/>
+      <c r="L25" s="245"/>
       <c r="M25" s="114" t="s">
         <v>991</v>
       </c>
       <c r="N25" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="O25" s="194"/>
+      <c r="O25" s="256"/>
       <c r="P25" s="114" t="s">
         <v>1023</v>
       </c>
@@ -40914,31 +41191,31 @@
       <c r="B26" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C26" s="194"/>
-      <c r="D26" s="222"/>
-      <c r="E26" s="222"/>
-      <c r="F26" s="222"/>
+      <c r="C26" s="256"/>
+      <c r="D26" s="246"/>
+      <c r="E26" s="246"/>
+      <c r="F26" s="246"/>
       <c r="G26" s="114" t="s">
         <v>851</v>
       </c>
       <c r="H26" s="114">
         <v>0.75647999999999993</v>
       </c>
-      <c r="I26" s="194"/>
+      <c r="I26" s="256"/>
       <c r="J26" s="114" t="s">
         <v>866</v>
       </c>
       <c r="K26" s="114">
         <v>1.04016</v>
       </c>
-      <c r="L26" s="221"/>
+      <c r="L26" s="245"/>
       <c r="M26" s="114" t="s">
         <v>992</v>
       </c>
       <c r="N26" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O26" s="194"/>
+      <c r="O26" s="256"/>
       <c r="P26" s="114" t="s">
         <v>1024</v>
       </c>
@@ -40953,31 +41230,31 @@
       <c r="B27" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C27" s="194"/>
-      <c r="D27" s="222"/>
-      <c r="E27" s="222"/>
-      <c r="F27" s="222"/>
+      <c r="C27" s="256"/>
+      <c r="D27" s="246"/>
+      <c r="E27" s="246"/>
+      <c r="F27" s="246"/>
       <c r="G27" s="114" t="s">
         <v>953</v>
       </c>
       <c r="H27" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="I27" s="194"/>
+      <c r="I27" s="256"/>
       <c r="J27" s="114" t="s">
         <v>867</v>
       </c>
       <c r="K27" s="114">
         <v>1.9857599999999997</v>
       </c>
-      <c r="L27" s="221"/>
+      <c r="L27" s="245"/>
       <c r="M27" s="114" t="s">
         <v>993</v>
       </c>
       <c r="N27" s="114">
         <v>1.5129599999999999</v>
       </c>
-      <c r="O27" s="194"/>
+      <c r="O27" s="256"/>
       <c r="P27" s="114" t="s">
         <v>1025</v>
       </c>
@@ -40992,31 +41269,31 @@
       <c r="B28" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C28" s="194"/>
-      <c r="D28" s="222"/>
-      <c r="E28" s="222"/>
-      <c r="F28" s="222"/>
+      <c r="C28" s="256"/>
+      <c r="D28" s="246"/>
+      <c r="E28" s="246"/>
+      <c r="F28" s="246"/>
       <c r="G28" s="114" t="s">
         <v>954</v>
       </c>
       <c r="H28" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="I28" s="194"/>
+      <c r="I28" s="256"/>
       <c r="J28" s="114" t="s">
         <v>868</v>
       </c>
       <c r="K28" s="114">
         <v>1.7020799999999998</v>
       </c>
-      <c r="L28" s="221"/>
+      <c r="L28" s="245"/>
       <c r="M28" s="114" t="s">
         <v>995</v>
       </c>
       <c r="N28" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="O28" s="194"/>
+      <c r="O28" s="256"/>
       <c r="P28" s="114" t="s">
         <v>1026</v>
       </c>
@@ -41031,31 +41308,31 @@
       <c r="B29" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C29" s="194"/>
-      <c r="D29" s="222"/>
-      <c r="E29" s="222"/>
-      <c r="F29" s="222"/>
+      <c r="C29" s="256"/>
+      <c r="D29" s="246"/>
+      <c r="E29" s="246"/>
+      <c r="F29" s="246"/>
       <c r="G29" s="114" t="s">
         <v>955</v>
       </c>
       <c r="H29" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="I29" s="194"/>
+      <c r="I29" s="256"/>
       <c r="J29" s="114" t="s">
         <v>869</v>
       </c>
       <c r="K29" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="L29" s="221"/>
+      <c r="L29" s="245"/>
       <c r="M29" s="114" t="s">
         <v>996</v>
       </c>
       <c r="N29" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="O29" s="194"/>
+      <c r="O29" s="256"/>
       <c r="P29" s="114" t="s">
         <v>1027</v>
       </c>
@@ -41070,31 +41347,31 @@
       <c r="B30" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C30" s="194"/>
-      <c r="D30" s="222"/>
-      <c r="E30" s="222"/>
-      <c r="F30" s="222"/>
+      <c r="C30" s="256"/>
+      <c r="D30" s="246"/>
+      <c r="E30" s="246"/>
+      <c r="F30" s="246"/>
       <c r="G30" s="114" t="s">
         <v>956</v>
       </c>
       <c r="H30" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="I30" s="194"/>
+      <c r="I30" s="256"/>
       <c r="J30" s="114" t="s">
         <v>970</v>
       </c>
       <c r="K30" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="L30" s="221"/>
+      <c r="L30" s="245"/>
       <c r="M30" s="114" t="s">
         <v>997</v>
       </c>
       <c r="N30" s="114">
         <v>1.13472</v>
       </c>
-      <c r="O30" s="194"/>
+      <c r="O30" s="256"/>
       <c r="P30" s="114" t="s">
         <v>1028</v>
       </c>
@@ -41109,31 +41386,31 @@
       <c r="B31" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C31" s="194"/>
-      <c r="D31" s="222"/>
-      <c r="E31" s="222"/>
-      <c r="F31" s="222"/>
+      <c r="C31" s="256"/>
+      <c r="D31" s="246"/>
+      <c r="E31" s="246"/>
+      <c r="F31" s="246"/>
       <c r="G31" s="114" t="s">
         <v>852</v>
       </c>
       <c r="H31" s="114">
         <v>0.75647999999999993</v>
       </c>
-      <c r="I31" s="194"/>
+      <c r="I31" s="256"/>
       <c r="J31" s="114" t="s">
         <v>870</v>
       </c>
       <c r="K31" s="114">
         <v>1.7020799999999998</v>
       </c>
-      <c r="L31" s="221"/>
+      <c r="L31" s="245"/>
       <c r="M31" s="114" t="s">
         <v>998</v>
       </c>
       <c r="N31" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O31" s="194"/>
+      <c r="O31" s="256"/>
       <c r="P31" s="114" t="s">
         <v>1032</v>
       </c>
@@ -41148,31 +41425,31 @@
       <c r="B32" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C32" s="194"/>
-      <c r="D32" s="222"/>
-      <c r="E32" s="222"/>
-      <c r="F32" s="222"/>
+      <c r="C32" s="256"/>
+      <c r="D32" s="246"/>
+      <c r="E32" s="246"/>
+      <c r="F32" s="246"/>
       <c r="G32" s="114" t="s">
         <v>853</v>
       </c>
       <c r="H32" s="114">
         <v>0.37823999999999997</v>
       </c>
-      <c r="I32" s="194"/>
+      <c r="I32" s="256"/>
       <c r="J32" s="114" t="s">
         <v>871</v>
       </c>
       <c r="K32" s="114">
         <v>1.8912</v>
       </c>
-      <c r="L32" s="221"/>
+      <c r="L32" s="245"/>
       <c r="M32" s="114" t="s">
         <v>999</v>
       </c>
       <c r="N32" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="O32" s="194"/>
+      <c r="O32" s="256"/>
       <c r="P32" s="114" t="s">
         <v>1033</v>
       </c>
@@ -41187,31 +41464,31 @@
       <c r="B33" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C33" s="194"/>
-      <c r="D33" s="222"/>
-      <c r="E33" s="222"/>
-      <c r="F33" s="222"/>
+      <c r="C33" s="256"/>
+      <c r="D33" s="246"/>
+      <c r="E33" s="246"/>
+      <c r="F33" s="246"/>
       <c r="G33" s="114" t="s">
         <v>854</v>
       </c>
       <c r="H33" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="I33" s="194"/>
+      <c r="I33" s="256"/>
       <c r="J33" s="114" t="s">
         <v>872</v>
       </c>
       <c r="K33" s="114">
         <v>1.6075200000000001</v>
       </c>
-      <c r="L33" s="221"/>
+      <c r="L33" s="245"/>
       <c r="M33" s="114" t="s">
         <v>1000</v>
       </c>
       <c r="N33" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O33" s="194"/>
+      <c r="O33" s="256"/>
       <c r="P33" s="114" t="s">
         <v>1034</v>
       </c>
@@ -41226,31 +41503,31 @@
       <c r="B34" s="114">
         <v>0.28367999999999999</v>
       </c>
-      <c r="C34" s="194"/>
-      <c r="D34" s="222"/>
-      <c r="E34" s="222"/>
-      <c r="F34" s="222"/>
+      <c r="C34" s="256"/>
+      <c r="D34" s="246"/>
+      <c r="E34" s="246"/>
+      <c r="F34" s="246"/>
       <c r="G34" s="114" t="s">
         <v>957</v>
       </c>
       <c r="H34" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="I34" s="194"/>
+      <c r="I34" s="256"/>
       <c r="J34" s="114" t="s">
         <v>1038</v>
       </c>
       <c r="K34" s="114">
         <v>0.4728</v>
       </c>
-      <c r="L34" s="221"/>
+      <c r="L34" s="245"/>
       <c r="M34" s="114" t="s">
         <v>1001</v>
       </c>
       <c r="N34" s="114">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O34" s="194"/>
+      <c r="O34" s="256"/>
       <c r="P34" s="114" t="s">
         <v>1035</v>
       </c>
@@ -41265,31 +41542,31 @@
       <c r="B35" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="C35" s="194"/>
-      <c r="D35" s="222"/>
-      <c r="E35" s="222"/>
-      <c r="F35" s="222"/>
+      <c r="C35" s="256"/>
+      <c r="D35" s="246"/>
+      <c r="E35" s="246"/>
+      <c r="F35" s="246"/>
       <c r="G35" s="114" t="s">
         <v>958</v>
       </c>
       <c r="H35" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="I35" s="194"/>
+      <c r="I35" s="256"/>
       <c r="J35" s="114" t="s">
         <v>873</v>
       </c>
       <c r="K35" s="114">
         <v>1.13472</v>
       </c>
-      <c r="L35" s="221"/>
+      <c r="L35" s="245"/>
       <c r="M35" s="169" t="s">
         <v>1002</v>
       </c>
       <c r="N35" s="169">
         <v>0.66192000000000006</v>
       </c>
-      <c r="O35" s="194"/>
+      <c r="O35" s="256"/>
       <c r="P35" s="166" t="s">
         <v>843</v>
       </c>
@@ -41305,17 +41582,17 @@
       <c r="B36" s="114">
         <v>0.18911999999999998</v>
       </c>
-      <c r="C36" s="194"/>
-      <c r="D36" s="222"/>
-      <c r="E36" s="222"/>
-      <c r="F36" s="222"/>
+      <c r="C36" s="256"/>
+      <c r="D36" s="246"/>
+      <c r="E36" s="246"/>
+      <c r="F36" s="246"/>
       <c r="G36" s="114" t="s">
         <v>959</v>
       </c>
       <c r="H36" s="114">
         <v>9.4559999999999991E-2</v>
       </c>
-      <c r="I36" s="194"/>
+      <c r="I36" s="256"/>
       <c r="J36" s="163" t="s">
         <v>843</v>
       </c>
@@ -41323,7 +41600,7 @@
         <f>SUM(K8:K35)</f>
         <v>26.665920000000003</v>
       </c>
-      <c r="L36" s="221"/>
+      <c r="L36" s="245"/>
       <c r="M36" s="166" t="s">
         <v>843</v>
       </c>
@@ -41331,9 +41608,9 @@
         <f>SUM(N8:N35)</f>
         <v>18.628319999999995</v>
       </c>
-      <c r="O36" s="222"/>
-      <c r="P36" s="207"/>
-      <c r="Q36" s="207"/>
+      <c r="O36" s="246"/>
+      <c r="P36" s="237"/>
+      <c r="Q36" s="237"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="166" t="s">
@@ -41343,10 +41620,10 @@
         <f>SUM(B8:B36)</f>
         <v>5.200800000000001</v>
       </c>
-      <c r="C37" s="194"/>
-      <c r="D37" s="222"/>
-      <c r="E37" s="222"/>
-      <c r="F37" s="222"/>
+      <c r="C37" s="256"/>
+      <c r="D37" s="246"/>
+      <c r="E37" s="246"/>
+      <c r="F37" s="246"/>
       <c r="G37" s="163" t="s">
         <v>843</v>
       </c>
@@ -41354,15 +41631,15 @@
         <f>SUM(H8:H36)</f>
         <v>14.089440000000002</v>
       </c>
-      <c r="I37" s="194"/>
-      <c r="J37" s="207"/>
-      <c r="K37" s="207"/>
-      <c r="L37" s="221"/>
-      <c r="M37" s="222"/>
-      <c r="N37" s="222"/>
-      <c r="O37" s="222"/>
-      <c r="P37" s="222"/>
-      <c r="Q37" s="222"/>
+      <c r="I37" s="256"/>
+      <c r="J37" s="237"/>
+      <c r="K37" s="237"/>
+      <c r="L37" s="245"/>
+      <c r="M37" s="246"/>
+      <c r="N37" s="246"/>
+      <c r="O37" s="246"/>
+      <c r="P37" s="246"/>
+      <c r="Q37" s="246"/>
     </row>
   </sheetData>
   <mergeCells count="16">
@@ -41405,27 +41682,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="154" t="s">
         <v>814</v>
       </c>
@@ -41440,12 +41717,12 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
-        <v>1215</v>
-      </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="B3" s="206" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="157" t="s">
         <v>1128</v>
       </c>
@@ -41461,12 +41738,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="206" t="s">
         <v>1119</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="206"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="207"/>
       <c r="F4" s="155" t="s">
         <v>1130</v>
       </c>
@@ -41482,12 +41759,12 @@
       <c r="A5" s="140">
         <v>3</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="206" t="s">
         <v>1119</v>
       </c>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="206"/>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="207"/>
       <c r="F5" s="155" t="s">
         <v>1129</v>
       </c>
@@ -41503,13 +41780,13 @@
       <c r="A6" s="140">
         <v>4</v>
       </c>
-      <c r="B6" s="205" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C6" s="234"/>
-      <c r="D6" s="234"/>
-      <c r="E6" s="206"/>
-      <c r="F6" s="192" t="s">
+      <c r="B6" s="206" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C6" s="260"/>
+      <c r="D6" s="260"/>
+      <c r="E6" s="207"/>
+      <c r="F6" s="189" t="s">
         <v>1128</v>
       </c>
       <c r="G6" s="115" t="s">
@@ -41521,14 +41798,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="201"/>
-      <c r="B7" s="201"/>
-      <c r="C7" s="201"/>
-      <c r="D7" s="201"/>
-      <c r="E7" s="201"/>
-      <c r="F7" s="201"/>
-      <c r="G7" s="201"/>
-      <c r="H7" s="201"/>
+      <c r="A7" s="257"/>
+      <c r="B7" s="257"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="257"/>
+      <c r="E7" s="257"/>
+      <c r="F7" s="257"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="257"/>
     </row>
     <row r="8" spans="1:8" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" s="114" t="s">
@@ -41546,9 +41823,9 @@
       <c r="E8" s="115" t="s">
         <v>1124</v>
       </c>
-      <c r="F8" s="194"/>
-      <c r="G8" s="195"/>
-      <c r="H8" s="195"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="114">
@@ -41567,9 +41844,9 @@
         <f>((0.7+(1.8*2))*0.2)*B9</f>
         <v>17.2</v>
       </c>
-      <c r="F9" s="194"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="195"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="114">
@@ -41588,9 +41865,9 @@
         <f t="shared" ref="E10:E11" si="0">((0.7+(1.8*2))*0.2)*B10</f>
         <v>15.48</v>
       </c>
-      <c r="F10" s="194"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="195"/>
+      <c r="F10" s="256"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="114">
@@ -41609,9 +41886,9 @@
         <f t="shared" si="0"/>
         <v>18.919999999999998</v>
       </c>
-      <c r="F11" s="194"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
+      <c r="F11" s="256"/>
+      <c r="G11" s="208"/>
+      <c r="H11" s="208"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="114"/>
@@ -41627,9 +41904,9 @@
         <f>SUM(E9:E11)</f>
         <v>51.599999999999994</v>
       </c>
-      <c r="F12" s="194"/>
-      <c r="G12" s="195"/>
-      <c r="H12" s="195"/>
+      <c r="F12" s="256"/>
+      <c r="G12" s="208"/>
+      <c r="H12" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -41664,27 +41941,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
+      <c r="H1" s="235"/>
     </row>
     <row r="2" spans="1:8" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="235"/>
-      <c r="D2" s="235"/>
-      <c r="E2" s="204"/>
+      <c r="C2" s="261"/>
+      <c r="D2" s="261"/>
+      <c r="E2" s="227"/>
       <c r="F2" s="154" t="s">
         <v>814</v>
       </c>
@@ -41699,12 +41976,12 @@
       <c r="A3" s="140">
         <v>1</v>
       </c>
-      <c r="B3" s="205" t="s">
+      <c r="B3" s="206" t="s">
         <v>1119</v>
       </c>
-      <c r="C3" s="234"/>
-      <c r="D3" s="234"/>
-      <c r="E3" s="206"/>
+      <c r="C3" s="260"/>
+      <c r="D3" s="260"/>
+      <c r="E3" s="207"/>
       <c r="F3" s="155" t="s">
         <v>1131</v>
       </c>
@@ -41720,12 +41997,12 @@
       <c r="A4" s="140">
         <v>2</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="206" t="s">
         <v>1119</v>
       </c>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="206"/>
+      <c r="C4" s="260"/>
+      <c r="D4" s="260"/>
+      <c r="E4" s="207"/>
       <c r="F4" s="155" t="s">
         <v>1132</v>
       </c>
@@ -41741,14 +42018,14 @@
       <c r="A5" s="140">
         <v>3</v>
       </c>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="206" t="s">
         <v>254</v>
       </c>
-      <c r="C5" s="234"/>
-      <c r="D5" s="234"/>
-      <c r="E5" s="206"/>
-      <c r="F5" s="192" t="s">
-        <v>1216</v>
+      <c r="C5" s="260"/>
+      <c r="D5" s="260"/>
+      <c r="E5" s="207"/>
+      <c r="F5" s="189" t="s">
+        <v>1202</v>
       </c>
       <c r="G5" s="115" t="s">
         <v>15</v>
@@ -41759,14 +42036,14 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="201"/>
-      <c r="B6" s="201"/>
-      <c r="C6" s="201"/>
-      <c r="D6" s="201"/>
-      <c r="E6" s="201"/>
-      <c r="F6" s="201"/>
-      <c r="G6" s="201"/>
-      <c r="H6" s="201"/>
+      <c r="A6" s="257"/>
+      <c r="B6" s="257"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="257"/>
+      <c r="E6" s="257"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="257"/>
     </row>
     <row r="7" spans="1:8" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="114" t="s">
@@ -41781,10 +42058,10 @@
       <c r="D7" s="115" t="s">
         <v>1124</v>
       </c>
-      <c r="E7" s="194"/>
-      <c r="F7" s="195"/>
-      <c r="G7" s="195"/>
-      <c r="H7" s="195"/>
+      <c r="E7" s="256"/>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
+      <c r="H7" s="208"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="114">
@@ -41800,10 +42077,10 @@
         <f>0.63*1.73*B8</f>
         <v>21.798000000000002</v>
       </c>
-      <c r="E8" s="194"/>
-      <c r="F8" s="195"/>
-      <c r="G8" s="195"/>
-      <c r="H8" s="195"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
+      <c r="H8" s="208"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="114">
@@ -41819,10 +42096,10 @@
         <f t="shared" ref="D9:D10" si="0">0.63*1.73*B9</f>
         <v>19.618200000000002</v>
       </c>
-      <c r="E9" s="194"/>
-      <c r="F9" s="195"/>
-      <c r="G9" s="195"/>
-      <c r="H9" s="195"/>
+      <c r="E9" s="256"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="208"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="114">
@@ -41838,10 +42115,10 @@
         <f t="shared" si="0"/>
         <v>23.977800000000002</v>
       </c>
-      <c r="E10" s="194"/>
-      <c r="F10" s="195"/>
-      <c r="G10" s="195"/>
-      <c r="H10" s="195"/>
+      <c r="E10" s="256"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="114"/>
@@ -41856,10 +42133,10 @@
         <f>SUM(D8:D10)</f>
         <v>65.394000000000005</v>
       </c>
-      <c r="E11" s="194"/>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
-      <c r="H11" s="195"/>
+      <c r="E11" s="256"/>
+      <c r="F11" s="208"/>
+      <c r="G11" s="208"/>
+      <c r="H11" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -41878,7 +42155,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.44140625" style="153" customWidth="1"/>
@@ -41892,28 +42169,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="219" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="219"/>
-      <c r="E1" s="219"/>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
+      <c r="A1" s="235" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7" s="119" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="118" t="s">
         <v>829</v>
       </c>
-      <c r="B2" s="199" t="s">
+      <c r="B2" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="199"/>
-      <c r="D2" s="199" t="s">
+      <c r="C2" s="224"/>
+      <c r="D2" s="224" t="s">
         <v>814</v>
       </c>
-      <c r="E2" s="199"/>
+      <c r="E2" s="224"/>
       <c r="F2" s="37" t="s">
         <v>10</v>
       </c>
@@ -41925,166 +42202,146 @@
       <c r="A3" s="114">
         <v>1</v>
       </c>
-      <c r="B3" s="200" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C3" s="200"/>
-      <c r="D3" s="200" t="s">
+      <c r="B3" s="205" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C3" s="205"/>
+      <c r="D3" s="205" t="s">
         <v>1186</v>
       </c>
-      <c r="E3" s="200"/>
+      <c r="E3" s="205"/>
       <c r="F3" s="115" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="116">
-        <v>20.85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="114">
-        <v>2</v>
-      </c>
-      <c r="B4" s="200" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C4" s="200"/>
-      <c r="D4" s="200" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E4" s="200"/>
-      <c r="F4" s="115" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="116">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="201"/>
-      <c r="B5" s="201"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="201"/>
-      <c r="E5" s="201"/>
-      <c r="F5" s="201"/>
-      <c r="G5" s="201"/>
+        <f>E10</f>
+        <v>12.66696</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="257"/>
+      <c r="B4" s="257"/>
+      <c r="C4" s="257"/>
+      <c r="D4" s="257"/>
+      <c r="E4" s="257"/>
+      <c r="F4" s="257"/>
+      <c r="G4" s="257"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="236" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B5" s="236"/>
+      <c r="C5" s="236"/>
+      <c r="D5" s="236"/>
+      <c r="E5" s="236"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="220" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B6" s="220"/>
-      <c r="C6" s="220"/>
-      <c r="D6" s="220"/>
-      <c r="E6" s="220"/>
-      <c r="F6" s="195"/>
-      <c r="G6" s="195"/>
+      <c r="A6" s="167" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B6" s="172" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C6" s="172" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D6" s="172" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E6" s="172" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F6" s="208"/>
+      <c r="G6" s="208"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="167" t="s">
-        <v>1054</v>
-      </c>
-      <c r="B7" s="172" t="s">
-        <v>1108</v>
-      </c>
-      <c r="C7" s="172" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D7" s="172" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E7" s="172" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F7" s="195"/>
-      <c r="G7" s="195"/>
+      <c r="A7" s="114">
+        <v>1</v>
+      </c>
+      <c r="B7" s="139">
+        <v>20</v>
+      </c>
+      <c r="C7" s="139">
+        <v>0.155</v>
+      </c>
+      <c r="D7" s="139">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="E7" s="135">
+        <f>C7*D7*B7</f>
+        <v>3.5029999999999992</v>
+      </c>
+      <c r="F7" s="208"/>
+      <c r="G7" s="208"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B8" s="139">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C8" s="139">
-        <v>0.18</v>
+        <v>0.189</v>
       </c>
       <c r="D8" s="139">
-        <v>1.1261000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="E8" s="135">
-        <f>C8*D8*B8</f>
-        <v>8.7160140000000013</v>
-      </c>
-      <c r="F8" s="195"/>
-      <c r="G8" s="195"/>
+        <f t="shared" ref="E8:E9" si="0">C8*D8*B8</f>
+        <v>3.4398</v>
+      </c>
+      <c r="F8" s="208"/>
+      <c r="G8" s="208"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B9" s="139">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="139">
-        <v>0.2</v>
+        <v>0.17199999999999999</v>
       </c>
       <c r="D9" s="139">
-        <v>1.129</v>
+        <v>1.28</v>
       </c>
       <c r="E9" s="135">
-        <f t="shared" ref="E9:E10" si="0">C9*D9*B9</f>
-        <v>6.0966000000000005</v>
-      </c>
-      <c r="F9" s="195"/>
-      <c r="G9" s="195"/>
+        <f t="shared" si="0"/>
+        <v>5.7241599999999995</v>
+      </c>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="114">
-        <v>3</v>
-      </c>
-      <c r="B10" s="139">
-        <v>28</v>
-      </c>
-      <c r="C10" s="139">
-        <v>0.2</v>
-      </c>
-      <c r="D10" s="139">
-        <v>1.1200000000000001</v>
-      </c>
+      <c r="A10" s="262" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B10" s="263"/>
+      <c r="C10" s="263"/>
+      <c r="D10" s="264"/>
       <c r="E10" s="135">
-        <f t="shared" si="0"/>
-        <v>6.2720000000000011</v>
-      </c>
-      <c r="F10" s="195"/>
-      <c r="G10" s="195"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="236" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B11" s="237"/>
-      <c r="C11" s="237"/>
-      <c r="D11" s="238"/>
-      <c r="E11" s="135">
-        <f>SUM(E8:E10)</f>
-        <v>21.084614000000002</v>
-      </c>
-      <c r="F11" s="195"/>
-      <c r="G11" s="195"/>
+        <f>SUM(E7:E9)</f>
+        <v>12.66696</v>
+      </c>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="F6:G11"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A11:D11"/>
+  <mergeCells count="9">
+    <mergeCell ref="F5:G10"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A10:D10"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A4:G4"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="D3:E3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
